--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:HX16"/>
+  <dimension ref="A1:HX18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69e82c68836d7d05c9a03f19</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69e82c68836d7d05c9a03f4a</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4177</t>
+          <t>69e82c68836d7d05c9a03f74</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69e82c68836d7d05c9a03fbd</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69e82c68836d7d05c9a03ff5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>commercial.dat</t>
+          <t>837P-X298-all-fields.dat</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2006-10-15T10:23:00</t>
+          <t>2012-03-15T10:23:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>CHARGEABLE</t>
+          <t>REPORTING</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -3231,26 +3231,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
       <c r="R6"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -3269,7 +3253,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Ben Kildare Service</t>
+          <t>PHYSICIAN CLINIC</t>
         </is>
       </c>
       <c r="W6"/>
@@ -3297,7 +3281,7 @@
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>103G00000X</t>
+          <t>207Q00000X</t>
         </is>
       </c>
       <c r="AE6"/>
@@ -3316,21 +3300,13 @@
       <c r="AR6"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>UNCONFIRMED</t>
         </is>
       </c>
       <c r="AT6"/>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="AU6"/>
       <c r="AV6"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
+      <c r="AW6"/>
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -3344,12 +3320,12 @@
       <c r="AZ6"/>
       <c r="BA6" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>JANE</t>
         </is>
       </c>
       <c r="BC6"/>
@@ -3361,45 +3337,41 @@
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF6"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="BG6"/>
-      <c r="BH6"/>
-      <c r="BI6"/>
-      <c r="BJ6"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="BK6"/>
       <c r="BL6"/>
       <c r="BM6"/>
-      <c r="BN6" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="BO6" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
+      <c r="BN6"/>
+      <c r="BO6"/>
       <c r="BP6"/>
-      <c r="BQ6" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
+      <c r="BQ6"/>
       <c r="BR6"/>
       <c r="BS6"/>
       <c r="BT6"/>
       <c r="BU6"/>
       <c r="BV6"/>
-      <c r="BW6" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX6" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW6"/>
+      <c r="BX6"/>
       <c r="BY6"/>
       <c r="BZ6"/>
       <c r="CA6" s="3" t="inlineStr">
@@ -3409,12 +3381,12 @@
       </c>
       <c r="CB6" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="CD6"/>
@@ -3451,10 +3423,10 @@
       <c r="CM6"/>
       <c r="CN6"/>
       <c r="CO6" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="CP6" s="4" t="n">
-        <v>39000.0</v>
+        <v>40943.0</v>
       </c>
       <c r="CQ6"/>
       <c r="CR6"/>
@@ -3472,12 +3444,12 @@
       <c r="DD6"/>
       <c r="DE6"/>
       <c r="DF6"/>
-      <c r="DG6"/>
-      <c r="DH6" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DG6" s="3" t="inlineStr">
+        <is>
+          <t>20121092600001</t>
+        </is>
+      </c>
+      <c r="DH6"/>
       <c r="DI6"/>
       <c r="DJ6"/>
       <c r="DK6"/>
@@ -3485,12 +3457,12 @@
       <c r="DM6"/>
       <c r="DN6" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
+          <t>M25375</t>
         </is>
       </c>
       <c r="DO6" s="3" t="inlineStr">
         <is>
-          <t>Z1159</t>
+          <t>M19072</t>
         </is>
       </c>
       <c r="DP6"/>
@@ -3517,22 +3489,58 @@
       <c r="EK6"/>
       <c r="EL6"/>
       <c r="EM6"/>
-      <c r="EN6"/>
-      <c r="EO6"/>
-      <c r="EP6"/>
+      <c r="EN6" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="EO6" s="3" t="inlineStr">
+        <is>
+          <t>JONES</t>
+        </is>
+      </c>
+      <c r="EP6" s="3" t="inlineStr">
+        <is>
+          <t>BARNABY</t>
+        </is>
+      </c>
       <c r="EQ6"/>
       <c r="ER6"/>
       <c r="ES6"/>
       <c r="ET6"/>
       <c r="EU6"/>
       <c r="EV6"/>
-      <c r="EW6"/>
-      <c r="EX6"/>
-      <c r="EY6"/>
+      <c r="EW6" s="3" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="EX6" s="3" t="inlineStr">
+        <is>
+          <t>PHYSICIAN CLINIC</t>
+        </is>
+      </c>
+      <c r="EY6" s="3" t="inlineStr">
+        <is>
+          <t>234 SEAWAY ST</t>
+        </is>
+      </c>
       <c r="EZ6"/>
-      <c r="FA6"/>
-      <c r="FB6"/>
-      <c r="FC6"/>
+      <c r="FA6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC6" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD6"/>
       <c r="FE6"/>
       <c r="FF6"/>
@@ -3561,22 +3569,70 @@
       <c r="GC6"/>
       <c r="GD6"/>
       <c r="GE6"/>
-      <c r="GF6"/>
-      <c r="GG6"/>
-      <c r="GH6"/>
+      <c r="GF6" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="GG6" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="GH6" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="GI6"/>
-      <c r="GJ6"/>
-      <c r="GK6"/>
-      <c r="GL6"/>
+      <c r="GJ6" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="GK6" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL6" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223333</t>
+        </is>
+      </c>
       <c r="GM6"/>
-      <c r="GN6"/>
-      <c r="GO6"/>
+      <c r="GN6" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO6" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
       <c r="GP6"/>
-      <c r="GQ6"/>
+      <c r="GQ6" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR6"/>
-      <c r="GS6"/>
-      <c r="GT6"/>
-      <c r="GU6"/>
+      <c r="GS6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU6" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="GV6"/>
       <c r="GW6"/>
       <c r="GX6"/>
@@ -3589,14 +3645,32 @@
       <c r="HE6"/>
       <c r="HF6"/>
       <c r="HG6"/>
-      <c r="HH6"/>
+      <c r="HH6" s="1" t="n">
+        <v>75.0</v>
+      </c>
       <c r="HI6"/>
       <c r="HJ6"/>
-      <c r="HK6"/>
-      <c r="HL6"/>
-      <c r="HM6"/>
+      <c r="HK6" s="3" t="inlineStr">
+        <is>
+          <t>20121092600001</t>
+        </is>
+      </c>
+      <c r="HL6" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM6" s="3" t="inlineStr">
+        <is>
+          <t>59999</t>
+        </is>
+      </c>
       <c r="HN6"/>
-      <c r="HO6"/>
+      <c r="HO6" s="3" t="inlineStr">
+        <is>
+          <t>ABC PLAN</t>
+        </is>
+      </c>
       <c r="HP6"/>
       <c r="HQ6"/>
       <c r="HR6"/>
@@ -3610,7 +3684,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69e82c68836d7d05c9a04024</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3620,7 +3694,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>multi-tran.dat</t>
+          <t>commercial.dat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3635,7 +3709,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3645,12 +3719,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>REPORTING</t>
+          <t>CHARGEABLE</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
@@ -3709,7 +3783,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>Ben Kildare Service</t>
         </is>
       </c>
       <c r="W7"/>
@@ -3737,7 +3811,7 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>103GC0700X</t>
+          <t>103G00000X</t>
         </is>
       </c>
       <c r="AE7"/>
@@ -3759,20 +3833,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
+      <c r="AT7"/>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>12312-A</t>
+          <t>2222-SJ</t>
         </is>
       </c>
       <c r="AV7"/>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>HM</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -3782,18 +3852,18 @@
       </c>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>00221111</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ7"/>
       <c r="BA7" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="BC7"/>
@@ -3802,30 +3872,14 @@
       </c>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF7"/>
       <c r="BG7"/>
-      <c r="BH7" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="BI7" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BJ7" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
       <c r="BK7"/>
       <c r="BL7"/>
       <c r="BM7"/>
@@ -3836,13 +3890,13 @@
       </c>
       <c r="BO7" s="3" t="inlineStr">
         <is>
-          <t>741234</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="3" t="inlineStr">
         <is>
-          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
+          <t>KEY INSURANCE COMPANY</t>
         </is>
       </c>
       <c r="BR7"/>
@@ -3850,21 +3904,63 @@
       <c r="BT7"/>
       <c r="BU7"/>
       <c r="BV7"/>
-      <c r="BW7"/>
-      <c r="BX7"/>
+      <c r="BW7" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX7" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY7"/>
       <c r="BZ7"/>
-      <c r="CA7"/>
-      <c r="CB7"/>
-      <c r="CC7"/>
+      <c r="CA7" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB7" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="CC7" s="3" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
       <c r="CD7"/>
-      <c r="CE7"/>
-      <c r="CF7"/>
-      <c r="CG7"/>
+      <c r="CE7" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF7" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG7" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH7"/>
-      <c r="CI7"/>
-      <c r="CJ7"/>
-      <c r="CK7"/>
+      <c r="CI7" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ7" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK7" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL7"/>
       <c r="CM7"/>
       <c r="CN7"/>
@@ -3874,9 +3970,7 @@
       <c r="CP7" s="4" t="n">
         <v>39000.0</v>
       </c>
-      <c r="CQ7" s="4" t="n">
-        <v>36071.0</v>
-      </c>
+      <c r="CQ7"/>
       <c r="CR7"/>
       <c r="CS7"/>
       <c r="CT7"/>
@@ -3905,7 +3999,7 @@
       <c r="DM7"/>
       <c r="DN7" s="3" t="inlineStr">
         <is>
-          <t>G35</t>
+          <t>J020</t>
         </is>
       </c>
       <c r="DO7" s="3" t="inlineStr">
@@ -3946,37 +4040,13 @@
       <c r="ET7"/>
       <c r="EU7"/>
       <c r="EV7"/>
-      <c r="EW7" s="3" t="inlineStr">
-        <is>
-          <t>5812345679</t>
-        </is>
-      </c>
-      <c r="EX7" s="3" t="inlineStr">
-        <is>
-          <t>KILDARE ASSOCIATES</t>
-        </is>
-      </c>
-      <c r="EY7" s="3" t="inlineStr">
-        <is>
-          <t>2345 OCEAN BLVD</t>
-        </is>
-      </c>
+      <c r="EW7"/>
+      <c r="EX7"/>
+      <c r="EY7"/>
       <c r="EZ7"/>
-      <c r="FA7" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="FB7" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="FC7" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="FA7"/>
+      <c r="FB7"/>
+      <c r="FC7"/>
       <c r="FD7"/>
       <c r="FE7"/>
       <c r="FF7"/>
@@ -4054,7 +4124,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4267</t>
+          <t>69e82c68836d7d05c9a0409b</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4069,7 +4139,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4079,26 +4149,26 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>007227</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2005-02-15T07:54:20</t>
+          <t>2006-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>CHARGEABLE</t>
+          <t>REPORTING</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>145.5</v>
+        <v>100.0</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -4132,7 +4202,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R8"/>
@@ -4143,66 +4213,50 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>GREENE</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>BEN KILDARE SERVICE</t>
+        </is>
+      </c>
+      <c r="W8"/>
+      <c r="X8"/>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>1264 OAKWOOD AVE</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z8"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>21236</t>
-        </is>
-      </c>
-      <c r="AD8"/>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG8" s="3" t="inlineStr">
-        <is>
-          <t>4105551212</t>
-        </is>
-      </c>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>103GC0700X</t>
+        </is>
+      </c>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
       <c r="AH8"/>
       <c r="AI8"/>
       <c r="AJ8"/>
@@ -4224,11 +4278,15 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU8"/>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>12312-A</t>
+        </is>
+      </c>
       <c r="AV8"/>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>HM</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -4238,27 +4296,23 @@
       </c>
       <c r="AY8" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>00221111</t>
         </is>
       </c>
       <c r="AZ8"/>
       <c r="BA8" s="3" t="inlineStr">
         <is>
-          <t>WILLIAMSON</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>MATTHEW</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="BC8"/>
       <c r="BD8" s="4" t="n">
-        <v>9142.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE8" s="3" t="inlineStr">
         <is>
@@ -4267,23 +4321,23 @@
       </c>
       <c r="BF8" s="3" t="inlineStr">
         <is>
-          <t>128 BROADCREEK</t>
+          <t>236 N MAIN ST</t>
         </is>
       </c>
       <c r="BG8"/>
       <c r="BH8" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="BI8" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="BJ8" s="3" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="BK8"/>
@@ -4296,13 +4350,13 @@
       </c>
       <c r="BO8" s="3" t="inlineStr">
         <is>
-          <t>C12345</t>
+          <t>741234</t>
         </is>
       </c>
       <c r="BP8"/>
       <c r="BQ8" s="3" t="inlineStr">
         <is>
-          <t>MEDICARE PART B MARYLAND</t>
+          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
         </is>
       </c>
       <c r="BR8"/>
@@ -4329,24 +4383,20 @@
       <c r="CM8"/>
       <c r="CN8"/>
       <c r="CO8" s="4" t="n">
-        <v>38398.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP8" s="4" t="n">
-        <v>38398.0</v>
-      </c>
-      <c r="CQ8"/>
-      <c r="CR8" s="4" t="n">
-        <v>38367.0</v>
-      </c>
+        <v>39000.0</v>
+      </c>
+      <c r="CQ8" s="4" t="n">
+        <v>36071.0</v>
+      </c>
+      <c r="CR8"/>
       <c r="CS8"/>
-      <c r="CT8" s="4" t="n">
-        <v>38362.0</v>
-      </c>
+      <c r="CT8"/>
       <c r="CU8"/>
       <c r="CV8"/>
-      <c r="CW8" s="4" t="n">
-        <v>38365.0</v>
-      </c>
+      <c r="CW8"/>
       <c r="CX8"/>
       <c r="CY8"/>
       <c r="CZ8"/>
@@ -4357,7 +4407,11 @@
       <c r="DE8"/>
       <c r="DF8"/>
       <c r="DG8"/>
-      <c r="DH8"/>
+      <c r="DH8" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI8"/>
       <c r="DJ8"/>
       <c r="DK8"/>
@@ -4365,10 +4419,14 @@
       <c r="DM8"/>
       <c r="DN8" s="3" t="inlineStr">
         <is>
-          <t>M4820</t>
-        </is>
-      </c>
-      <c r="DO8"/>
+          <t>G35</t>
+        </is>
+      </c>
+      <c r="DO8" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP8"/>
       <c r="DQ8"/>
       <c r="DR8"/>
@@ -4402,13 +4460,37 @@
       <c r="ET8"/>
       <c r="EU8"/>
       <c r="EV8"/>
-      <c r="EW8"/>
-      <c r="EX8"/>
-      <c r="EY8"/>
+      <c r="EW8" s="3" t="inlineStr">
+        <is>
+          <t>5812345679</t>
+        </is>
+      </c>
+      <c r="EX8" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="EY8" s="3" t="inlineStr">
+        <is>
+          <t>2345 OCEAN BLVD</t>
+        </is>
+      </c>
       <c r="EZ8"/>
-      <c r="FA8"/>
-      <c r="FB8"/>
-      <c r="FC8"/>
+      <c r="FA8" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB8" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC8" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD8"/>
       <c r="FE8"/>
       <c r="FF8"/>
@@ -4486,7 +4568,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69e82c68836d7d05c9a0409c</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4501,7 +4583,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4511,12 +4593,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>007227</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2005-02-15T07:54:20</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -4526,20 +4608,20 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>827.0</v>
+        <v>145.5</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4575,46 +4657,66 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
-        </is>
-      </c>
-      <c r="W9"/>
-      <c r="X9"/>
+          <t>GREENE</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>1264 OAKWOOD AVE</t>
         </is>
       </c>
       <c r="Z9"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="AD9"/>
-      <c r="AE9"/>
-      <c r="AF9"/>
-      <c r="AG9"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>4105551212</t>
+        </is>
+      </c>
       <c r="AH9"/>
       <c r="AI9"/>
       <c r="AJ9"/>
@@ -4656,42 +4758,46 @@
       <c r="AZ9"/>
       <c r="BA9" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>WILLIAMSON</t>
         </is>
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
-        </is>
-      </c>
-      <c r="BC9"/>
+          <t>MATTHEW</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="BD9" s="4" t="n">
-        <v>27091.0</v>
+        <v>9142.0</v>
       </c>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF9" s="3" t="inlineStr">
         <is>
-          <t>123 RAINBOW ROAD</t>
+          <t>128 BROADCREEK</t>
         </is>
       </c>
       <c r="BG9"/>
       <c r="BH9" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="BI9" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="BJ9" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="BK9"/>
@@ -4704,13 +4810,13 @@
       </c>
       <c r="BO9" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>C12345</t>
         </is>
       </c>
       <c r="BP9"/>
       <c r="BQ9" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>MEDICARE PART B MARYLAND</t>
         </is>
       </c>
       <c r="BR9"/>
@@ -4737,18 +4843,24 @@
       <c r="CM9"/>
       <c r="CN9"/>
       <c r="CO9" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="CP9" s="4" t="n">
-        <v>38365.0</v>
+        <v>38398.0</v>
       </c>
       <c r="CQ9"/>
-      <c r="CR9"/>
+      <c r="CR9" s="4" t="n">
+        <v>38367.0</v>
+      </c>
       <c r="CS9"/>
-      <c r="CT9"/>
+      <c r="CT9" s="4" t="n">
+        <v>38362.0</v>
+      </c>
       <c r="CU9"/>
       <c r="CV9"/>
-      <c r="CW9"/>
+      <c r="CW9" s="4" t="n">
+        <v>38365.0</v>
+      </c>
       <c r="CX9"/>
       <c r="CY9"/>
       <c r="CZ9"/>
@@ -4767,7 +4879,7 @@
       <c r="DM9"/>
       <c r="DN9" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>M4820</t>
         </is>
       </c>
       <c r="DO9"/>
@@ -4795,74 +4907,22 @@
       <c r="EK9"/>
       <c r="EL9"/>
       <c r="EM9"/>
-      <c r="EN9" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO9" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP9" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ9" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER9" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES9" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET9" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN9"/>
+      <c r="EO9"/>
+      <c r="EP9"/>
+      <c r="EQ9"/>
+      <c r="ER9"/>
+      <c r="ES9"/>
+      <c r="ET9"/>
       <c r="EU9"/>
       <c r="EV9"/>
-      <c r="EW9" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX9" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY9" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW9"/>
+      <c r="EX9"/>
+      <c r="EY9"/>
       <c r="EZ9"/>
-      <c r="FA9" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB9" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC9" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA9"/>
+      <c r="FB9"/>
+      <c r="FC9"/>
       <c r="FD9"/>
       <c r="FE9"/>
       <c r="FF9"/>
@@ -4940,7 +5000,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69e82c68836d7d05c9a0409d</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4950,12 +5010,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>commercial-replacement.dat</t>
+          <t>multi-tran.dat</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -4965,12 +5025,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2006-11-15T10:23:00</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -4980,25 +5040,25 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>100.0</v>
+        <v>827.0</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -5018,7 +5078,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R10"/>
@@ -5029,47 +5089,43 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>PROVIDER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="W10"/>
       <c r="X10"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z10"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>103GC0700X</t>
-        </is>
-      </c>
+          <t>37232</t>
+        </is>
+      </c>
+      <c r="AD10"/>
       <c r="AE10"/>
       <c r="AF10"/>
       <c r="AG10"/>
@@ -5089,16 +5145,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT10"/>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -5108,34 +5164,50 @@
       </c>
       <c r="AY10" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ10"/>
       <c r="BA10" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>MARGARET</t>
         </is>
       </c>
       <c r="BC10"/>
       <c r="BD10" s="4" t="n">
-        <v>15827.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF10"/>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>123 RAINBOW ROAD</t>
+        </is>
+      </c>
       <c r="BG10"/>
-      <c r="BH10"/>
-      <c r="BI10"/>
-      <c r="BJ10"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="BK10"/>
       <c r="BL10"/>
       <c r="BM10"/>
@@ -5146,13 +5218,13 @@
       </c>
       <c r="BO10" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP10"/>
       <c r="BQ10" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCECOMPANY</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR10"/>
@@ -5160,71 +5232,29 @@
       <c r="BT10"/>
       <c r="BU10"/>
       <c r="BV10"/>
-      <c r="BW10" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX10" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW10"/>
+      <c r="BX10"/>
       <c r="BY10"/>
       <c r="BZ10"/>
-      <c r="CA10" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB10" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC10" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA10"/>
+      <c r="CB10"/>
+      <c r="CC10"/>
       <c r="CD10"/>
-      <c r="CE10" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF10" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG10" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE10"/>
+      <c r="CF10"/>
+      <c r="CG10"/>
       <c r="CH10"/>
-      <c r="CI10" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ10" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK10" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI10"/>
+      <c r="CJ10"/>
+      <c r="CK10"/>
       <c r="CL10"/>
       <c r="CM10"/>
       <c r="CN10"/>
       <c r="CO10" s="4" t="n">
-        <v>38993.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP10" s="4" t="n">
-        <v>39000.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ10"/>
       <c r="CR10"/>
@@ -5243,11 +5273,7 @@
       <c r="DE10"/>
       <c r="DF10"/>
       <c r="DG10"/>
-      <c r="DH10" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DH10"/>
       <c r="DI10"/>
       <c r="DJ10"/>
       <c r="DK10"/>
@@ -5255,14 +5281,10 @@
       <c r="DM10"/>
       <c r="DN10" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
-        </is>
-      </c>
-      <c r="DO10" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="DO10"/>
       <c r="DP10"/>
       <c r="DQ10"/>
       <c r="DR10"/>
@@ -5287,22 +5309,74 @@
       <c r="EK10"/>
       <c r="EL10"/>
       <c r="EM10"/>
-      <c r="EN10"/>
-      <c r="EO10"/>
-      <c r="EP10"/>
-      <c r="EQ10"/>
-      <c r="ER10"/>
-      <c r="ES10"/>
-      <c r="ET10"/>
+      <c r="EN10" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO10" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP10" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ10" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER10" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES10" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET10" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU10"/>
       <c r="EV10"/>
-      <c r="EW10"/>
-      <c r="EX10"/>
-      <c r="EY10"/>
+      <c r="EW10" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX10" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY10" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ10"/>
-      <c r="FA10"/>
-      <c r="FB10"/>
-      <c r="FC10"/>
+      <c r="FA10" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB10" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC10" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD10"/>
       <c r="FE10"/>
       <c r="FF10"/>
@@ -5380,7 +5454,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69e82c68836d7d05c9a040d0</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5390,12 +5464,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>anesthesia.dat</t>
+          <t>commercial-replacement.dat</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5405,12 +5479,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2006-11-15T10:23:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5420,25 +5494,25 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>827.0</v>
+        <v>100.0</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -5458,7 +5532,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R11"/>
@@ -5469,43 +5543,47 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
+          <t>BEN KILDARE SERVICE</t>
         </is>
       </c>
       <c r="W11"/>
       <c r="X11"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z11"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
-        </is>
-      </c>
-      <c r="AD11"/>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>103GC0700X</t>
+        </is>
+      </c>
       <c r="AE11"/>
       <c r="AF11"/>
       <c r="AG11"/>
@@ -5525,16 +5603,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU11"/>
+      <c r="AT11"/>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="AV11"/>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -5544,50 +5622,34 @@
       </c>
       <c r="AY11" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ11"/>
       <c r="BA11" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
+          <t>JANE</t>
         </is>
       </c>
       <c r="BC11"/>
       <c r="BD11" s="4" t="n">
-        <v>27091.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>123 RAINBOW ROAD</t>
-        </is>
-      </c>
+      <c r="BF11"/>
       <c r="BG11"/>
-      <c r="BH11" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="BI11" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="BJ11" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
       <c r="BK11"/>
       <c r="BL11"/>
       <c r="BM11"/>
@@ -5598,13 +5660,13 @@
       </c>
       <c r="BO11" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP11"/>
       <c r="BQ11" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>KEY INSURANCECOMPANY</t>
         </is>
       </c>
       <c r="BR11"/>
@@ -5612,29 +5674,71 @@
       <c r="BT11"/>
       <c r="BU11"/>
       <c r="BV11"/>
-      <c r="BW11"/>
-      <c r="BX11"/>
+      <c r="BW11" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX11" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY11"/>
       <c r="BZ11"/>
-      <c r="CA11"/>
-      <c r="CB11"/>
-      <c r="CC11"/>
+      <c r="CA11" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB11" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC11" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD11"/>
-      <c r="CE11"/>
-      <c r="CF11"/>
-      <c r="CG11"/>
+      <c r="CE11" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF11" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG11" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH11"/>
-      <c r="CI11"/>
-      <c r="CJ11"/>
-      <c r="CK11"/>
+      <c r="CI11" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ11" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK11" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL11"/>
       <c r="CM11"/>
       <c r="CN11"/>
       <c r="CO11" s="4" t="n">
-        <v>38364.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP11" s="4" t="n">
-        <v>38365.0</v>
+        <v>39000.0</v>
       </c>
       <c r="CQ11"/>
       <c r="CR11"/>
@@ -5653,7 +5757,11 @@
       <c r="DE11"/>
       <c r="DF11"/>
       <c r="DG11"/>
-      <c r="DH11"/>
+      <c r="DH11" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI11"/>
       <c r="DJ11"/>
       <c r="DK11"/>
@@ -5661,10 +5769,14 @@
       <c r="DM11"/>
       <c r="DN11" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="DO11"/>
+          <t>J020</t>
+        </is>
+      </c>
+      <c r="DO11" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP11"/>
       <c r="DQ11"/>
       <c r="DR11"/>
@@ -5689,74 +5801,22 @@
       <c r="EK11"/>
       <c r="EL11"/>
       <c r="EM11"/>
-      <c r="EN11" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO11" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP11" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ11" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER11" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES11" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET11" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN11"/>
+      <c r="EO11"/>
+      <c r="EP11"/>
+      <c r="EQ11"/>
+      <c r="ER11"/>
+      <c r="ES11"/>
+      <c r="ET11"/>
       <c r="EU11"/>
       <c r="EV11"/>
-      <c r="EW11" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX11" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY11" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW11"/>
+      <c r="EX11"/>
+      <c r="EY11"/>
       <c r="EZ11"/>
-      <c r="FA11" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB11" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC11" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA11"/>
+      <c r="FB11"/>
+      <c r="FC11"/>
       <c r="FD11"/>
       <c r="FE11"/>
       <c r="FF11"/>
@@ -5834,7 +5894,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42f6</t>
+          <t>69e82c68836d7d05c9a040fd</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5844,12 +5904,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>wheelchair.dat</t>
+          <t>anesthesia.dat</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5859,12 +5919,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2005-03-26T10:36:00</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5874,20 +5934,20 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>75.0</v>
+        <v>827.0</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -5923,40 +5983,40 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>7778889999</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>123567989</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>XYZ WHEELCHAIR INC</t>
+          <t>PROVIDER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="W12"/>
       <c r="X12"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>1440 NORTH STREET</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z12"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>LAFAYETTE</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="AD12"/>
@@ -5970,16 +6030,8 @@
       <c r="AL12"/>
       <c r="AM12"/>
       <c r="AN12"/>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>0426960001</t>
-        </is>
-      </c>
+      <c r="AO12"/>
+      <c r="AP12"/>
       <c r="AQ12"/>
       <c r="AR12"/>
       <c r="AS12" s="3" t="inlineStr">
@@ -6006,54 +6058,52 @@
       </c>
       <c r="AY12" s="3" t="inlineStr">
         <is>
-          <t>987654321A</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ12"/>
       <c r="BA12" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>JAMES</t>
+          <t>MARGARET</t>
         </is>
       </c>
       <c r="BC12"/>
       <c r="BD12" s="4" t="n">
-        <v>7602.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE12" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="BF12" s="3" t="inlineStr">
         <is>
-          <t>12 MAIN ST</t>
+          <t>123 RAINBOW ROAD</t>
         </is>
       </c>
       <c r="BG12"/>
       <c r="BH12" s="3" t="inlineStr">
         <is>
-          <t>FRANKFORT</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="BI12" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="BJ12" s="3" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="BK12"/>
-      <c r="BL12" t="n">
-        <v>155.0</v>
-      </c>
+      <c r="BL12"/>
       <c r="BM12"/>
       <c r="BN12" s="3" t="inlineStr">
         <is>
@@ -6062,13 +6112,13 @@
       </c>
       <c r="BO12" s="3" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP12"/>
       <c r="BQ12" s="3" t="inlineStr">
         <is>
-          <t>DMERC CARRIER</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR12"/>
@@ -6095,10 +6145,10 @@
       <c r="CM12"/>
       <c r="CN12"/>
       <c r="CO12" s="4" t="n">
-        <v>38432.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP12" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ12"/>
       <c r="CR12"/>
@@ -6125,14 +6175,10 @@
       <c r="DM12"/>
       <c r="DN12" s="3" t="inlineStr">
         <is>
-          <t>I6789</t>
-        </is>
-      </c>
-      <c r="DO12" s="3" t="inlineStr">
-        <is>
-          <t>G839</t>
-        </is>
-      </c>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="DO12"/>
       <c r="DP12"/>
       <c r="DQ12"/>
       <c r="DR12"/>
@@ -6157,22 +6203,74 @@
       <c r="EK12"/>
       <c r="EL12"/>
       <c r="EM12"/>
-      <c r="EN12"/>
-      <c r="EO12"/>
-      <c r="EP12"/>
-      <c r="EQ12"/>
-      <c r="ER12"/>
-      <c r="ES12"/>
-      <c r="ET12"/>
+      <c r="EN12" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO12" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP12" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ12" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER12" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES12" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET12" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU12"/>
       <c r="EV12"/>
-      <c r="EW12"/>
-      <c r="EX12"/>
-      <c r="EY12"/>
+      <c r="EW12" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX12" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY12" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ12"/>
-      <c r="FA12"/>
-      <c r="FB12"/>
-      <c r="FC12"/>
+      <c r="FA12" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB12" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC12" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD12"/>
       <c r="FE12"/>
       <c r="FF12"/>
@@ -6250,7 +6348,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69e82c68836d7d05c9a04138</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6260,12 +6358,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ppo-repriced.dat</t>
+          <t>wheelchair.dat</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6275,12 +6373,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2005-06-20T09:46:00</t>
+          <t>2005-03-26T10:36:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -6290,20 +6388,20 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>28.75</v>
+        <v>75.0</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -6339,30 +6437,30 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>7778889999</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>555512345</t>
+          <t>123567989</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>HAPPY DOCTORS GROUP PRACTICE</t>
+          <t>XYZ WHEELCHAIR INC</t>
         </is>
       </c>
       <c r="W13"/>
       <c r="X13"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>P O BOX 123</t>
+          <t>1440 NORTH STREET</t>
         </is>
       </c>
       <c r="Z13"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>FORT WAYNE</t>
+          <t>LAFAYETTE</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
@@ -6372,25 +6470,13 @@
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>462540000</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="AD13"/>
-      <c r="AE13" s="3" t="inlineStr">
-        <is>
-          <t>SUE BILLINGSWORTH</t>
-        </is>
-      </c>
-      <c r="AF13" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG13" s="3" t="inlineStr">
-        <is>
-          <t>8881231234</t>
-        </is>
-      </c>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
       <c r="AH13"/>
       <c r="AI13"/>
       <c r="AJ13"/>
@@ -6398,8 +6484,16 @@
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
-      <c r="AO13"/>
-      <c r="AP13"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>0426960001</t>
+        </is>
+      </c>
       <c r="AQ13"/>
       <c r="AR13"/>
       <c r="AS13" s="3" t="inlineStr">
@@ -6412,15 +6506,11 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>123XYZ</t>
-        </is>
-      </c>
+      <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -6430,42 +6520,38 @@
       </c>
       <c r="AY13" s="3" t="inlineStr">
         <is>
-          <t>00124A089</t>
+          <t>987654321A</t>
         </is>
       </c>
       <c r="AZ13"/>
       <c r="BA13" s="3" t="inlineStr">
         <is>
-          <t>RING</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>DIAMOND</t>
-        </is>
-      </c>
-      <c r="BC13" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="BC13"/>
       <c r="BD13" s="4" t="n">
-        <v>14974.0</v>
+        <v>7602.0</v>
       </c>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF13" s="3" t="inlineStr">
         <is>
-          <t>123 EXAMPLE DRIVE</t>
+          <t>12 MAIN ST</t>
         </is>
       </c>
       <c r="BG13"/>
       <c r="BH13" s="3" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS</t>
+          <t>FRANKFORT</t>
         </is>
       </c>
       <c r="BI13" s="3" t="inlineStr">
@@ -6475,11 +6561,13 @@
       </c>
       <c r="BJ13" s="3" t="inlineStr">
         <is>
-          <t>462290000</t>
+          <t>46209</t>
         </is>
       </c>
       <c r="BK13"/>
-      <c r="BL13"/>
+      <c r="BL13" t="n">
+        <v>155.0</v>
+      </c>
       <c r="BM13"/>
       <c r="BN13" s="3" t="inlineStr">
         <is>
@@ -6488,13 +6576,13 @@
       </c>
       <c r="BO13" s="3" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="BP13"/>
       <c r="BQ13" s="3" t="inlineStr">
         <is>
-          <t>EXTRA HEALTHY INSURANCE</t>
+          <t>DMERC CARRIER</t>
         </is>
       </c>
       <c r="BR13"/>
@@ -6521,10 +6609,10 @@
       <c r="CM13"/>
       <c r="CN13"/>
       <c r="CO13" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CP13" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CQ13"/>
       <c r="CR13"/>
@@ -6543,28 +6631,20 @@
       <c r="DE13"/>
       <c r="DF13"/>
       <c r="DG13"/>
-      <c r="DH13" s="3" t="inlineStr">
-        <is>
-          <t>061505501749388</t>
-        </is>
-      </c>
-      <c r="DI13" s="3" t="inlineStr">
-        <is>
-          <t>0902352342</t>
-        </is>
-      </c>
+      <c r="DH13"/>
+      <c r="DI13"/>
       <c r="DJ13"/>
       <c r="DK13"/>
       <c r="DL13"/>
       <c r="DM13"/>
       <c r="DN13" s="3" t="inlineStr">
         <is>
-          <t>J449</t>
+          <t>I6789</t>
         </is>
       </c>
       <c r="DO13" s="3" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>G839</t>
         </is>
       </c>
       <c r="DP13"/>
@@ -6583,78 +6663,30 @@
       <c r="EC13"/>
       <c r="ED13"/>
       <c r="EE13"/>
-      <c r="EF13" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="EG13" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH13" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="EF13"/>
+      <c r="EG13"/>
+      <c r="EH13"/>
       <c r="EI13"/>
       <c r="EJ13"/>
       <c r="EK13"/>
       <c r="EL13"/>
       <c r="EM13"/>
-      <c r="EN13" s="3" t="inlineStr">
-        <is>
-          <t>1122334455</t>
-        </is>
-      </c>
-      <c r="EO13" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="EP13" s="3" t="inlineStr">
-        <is>
-          <t>SUSAN</t>
-        </is>
-      </c>
-      <c r="EQ13" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="EN13"/>
+      <c r="EO13"/>
+      <c r="EP13"/>
+      <c r="EQ13"/>
       <c r="ER13"/>
       <c r="ES13"/>
       <c r="ET13"/>
       <c r="EU13"/>
       <c r="EV13"/>
       <c r="EW13"/>
-      <c r="EX13" s="3" t="inlineStr">
-        <is>
-          <t>HAPPY DOCTORS GROUP</t>
-        </is>
-      </c>
-      <c r="EY13" s="3" t="inlineStr">
-        <is>
-          <t>123 FEEL GOOD ROAD</t>
-        </is>
-      </c>
+      <c r="EX13"/>
+      <c r="EY13"/>
       <c r="EZ13"/>
-      <c r="FA13" s="3" t="inlineStr">
-        <is>
-          <t>WASHINGTON</t>
-        </is>
-      </c>
-      <c r="FB13" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="FC13" s="3" t="inlineStr">
-        <is>
-          <t>475010000</t>
-        </is>
-      </c>
+      <c r="FA13"/>
+      <c r="FB13"/>
+      <c r="FC13"/>
       <c r="FD13"/>
       <c r="FE13"/>
       <c r="FF13"/>
@@ -6732,7 +6764,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69e82c68836d7d05c9a04168</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6742,12 +6774,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>cob-prov-payera.dat</t>
+          <t>ppo-repriced.dat</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -6757,12 +6789,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2005-10-15T10:23:00</t>
+          <t>2005-06-20T09:46:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6772,11 +6804,11 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>79.04</v>
+        <v>28.75</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -6810,7 +6842,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R14"/>
@@ -6821,50 +6853,46 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1999996666</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>555512345</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
+          <t>HAPPY DOCTORS GROUP PRACTICE</t>
+        </is>
+      </c>
+      <c r="W14"/>
       <c r="X14"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>1234 SEAWAY ST</t>
+          <t>P O BOX 123</t>
         </is>
       </c>
       <c r="Z14"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>FORT WAYNE</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>462540000</t>
         </is>
       </c>
       <c r="AD14"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>CONNIE</t>
+          <t>SUE BILLINGSWORTH</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -6874,7 +6902,7 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>3055551234</t>
+          <t>8881231234</t>
         </is>
       </c>
       <c r="AH14"/>
@@ -6893,10 +6921,22 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT14"/>
-      <c r="AU14"/>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>123XYZ</t>
+        </is>
+      </c>
       <c r="AV14"/>
-      <c r="AW14"/>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
       <c r="AX14" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6904,34 +6944,54 @@
       </c>
       <c r="AY14" s="3" t="inlineStr">
         <is>
-          <t>111223333</t>
+          <t>00124A089</t>
         </is>
       </c>
       <c r="AZ14"/>
       <c r="BA14" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>RING</t>
         </is>
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="BC14"/>
+          <t>DIAMOND</t>
+        </is>
+      </c>
+      <c r="BC14" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="BD14" s="4" t="n">
-        <v>15827.0</v>
+        <v>14974.0</v>
       </c>
       <c r="BE14" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF14"/>
+      <c r="BF14" s="3" t="inlineStr">
+        <is>
+          <t>123 EXAMPLE DRIVE</t>
+        </is>
+      </c>
       <c r="BG14"/>
-      <c r="BH14"/>
-      <c r="BI14"/>
-      <c r="BJ14"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>INDIANAPOLIS</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="inlineStr">
+        <is>
+          <t>462290000</t>
+        </is>
+      </c>
       <c r="BK14"/>
       <c r="BL14"/>
       <c r="BM14"/>
@@ -6942,101 +7002,43 @@
       </c>
       <c r="BO14" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="BP14"/>
       <c r="BQ14" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
-      <c r="BR14" s="3" t="inlineStr">
-        <is>
-          <t>3333OCEAN ST</t>
-        </is>
-      </c>
+          <t>EXTRA HEALTHY INSURANCE</t>
+        </is>
+      </c>
+      <c r="BR14"/>
       <c r="BS14"/>
-      <c r="BT14" s="3" t="inlineStr">
-        <is>
-          <t>SOUTH MIAMI</t>
-        </is>
-      </c>
-      <c r="BU14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BV14" s="3" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="BW14" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX14" s="3" t="inlineStr">
-        <is>
-          <t>PBS3334</t>
-        </is>
-      </c>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
       <c r="BY14"/>
       <c r="BZ14"/>
-      <c r="CA14" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB14" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC14" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA14"/>
+      <c r="CB14"/>
+      <c r="CC14"/>
       <c r="CD14"/>
-      <c r="CE14" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF14" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG14" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE14"/>
+      <c r="CF14"/>
+      <c r="CG14"/>
       <c r="CH14"/>
-      <c r="CI14" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK14" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI14"/>
+      <c r="CJ14"/>
+      <c r="CK14"/>
       <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14"/>
       <c r="CO14" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CP14" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -7055,27 +7057,31 @@
       <c r="DE14"/>
       <c r="DF14"/>
       <c r="DG14"/>
-      <c r="DH14"/>
-      <c r="DI14"/>
+      <c r="DH14" s="3" t="inlineStr">
+        <is>
+          <t>061505501749388</t>
+        </is>
+      </c>
+      <c r="DI14" s="3" t="inlineStr">
+        <is>
+          <t>0902352342</t>
+        </is>
+      </c>
       <c r="DJ14"/>
       <c r="DK14"/>
       <c r="DL14"/>
       <c r="DM14"/>
       <c r="DN14" s="3" t="inlineStr">
         <is>
-          <t>J309</t>
+          <t>J449</t>
         </is>
       </c>
       <c r="DO14" s="3" t="inlineStr">
         <is>
-          <t>E785</t>
-        </is>
-      </c>
-      <c r="DP14" s="3" t="inlineStr">
-        <is>
-          <t>E663</t>
-        </is>
-      </c>
+          <t>E119</t>
+        </is>
+      </c>
+      <c r="DP14"/>
       <c r="DQ14"/>
       <c r="DR14"/>
       <c r="DS14"/>
@@ -7091,9 +7097,21 @@
       <c r="EC14"/>
       <c r="ED14"/>
       <c r="EE14"/>
-      <c r="EF14"/>
-      <c r="EG14"/>
-      <c r="EH14"/>
+      <c r="EF14" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="EG14" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH14" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="EI14"/>
       <c r="EJ14"/>
       <c r="EK14"/>
@@ -7101,66 +7119,54 @@
       <c r="EM14"/>
       <c r="EN14" s="3" t="inlineStr">
         <is>
-          <t>1999996666</t>
+          <t>1122334455</t>
         </is>
       </c>
       <c r="EO14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE</t>
+          <t>ANTHONY</t>
         </is>
       </c>
       <c r="EP14" s="3" t="inlineStr">
         <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="EQ14"/>
-      <c r="ER14" s="3" t="inlineStr">
-        <is>
-          <t>204C00000X</t>
-        </is>
-      </c>
-      <c r="ES14" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET14" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+          <t>SUSAN</t>
+        </is>
+      </c>
+      <c r="EQ14" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ER14"/>
+      <c r="ES14"/>
+      <c r="ET14"/>
       <c r="EU14"/>
       <c r="EV14"/>
-      <c r="EW14" s="3" t="inlineStr">
-        <is>
-          <t>1581234567</t>
-        </is>
-      </c>
+      <c r="EW14"/>
       <c r="EX14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE ASSOCIATES</t>
+          <t>HAPPY DOCTORS GROUP</t>
         </is>
       </c>
       <c r="EY14" s="3" t="inlineStr">
         <is>
-          <t>2345 OCEAN BLVD</t>
+          <t>123 FEEL GOOD ROAD</t>
         </is>
       </c>
       <c r="EZ14"/>
       <c r="FA14" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>WASHINGTON</t>
         </is>
       </c>
       <c r="FB14" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="FC14" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>475010000</t>
         </is>
       </c>
       <c r="FD14"/>
@@ -7191,66 +7197,22 @@
       <c r="GC14"/>
       <c r="GD14"/>
       <c r="GE14"/>
-      <c r="GF14" s="3" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="GG14" s="3" t="inlineStr">
-        <is>
-          <t>SPOUSE</t>
-        </is>
-      </c>
+      <c r="GF14"/>
+      <c r="GG14"/>
       <c r="GH14"/>
       <c r="GI14"/>
-      <c r="GJ14" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="GK14" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL14" s="3" t="inlineStr">
-        <is>
-          <t>T55TY666</t>
-        </is>
-      </c>
+      <c r="GJ14"/>
+      <c r="GK14"/>
+      <c r="GL14"/>
       <c r="GM14"/>
-      <c r="GN14" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO14" s="3" t="inlineStr">
-        <is>
-          <t>JACK</t>
-        </is>
-      </c>
+      <c r="GN14"/>
+      <c r="GO14"/>
       <c r="GP14"/>
-      <c r="GQ14" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ14"/>
       <c r="GR14"/>
-      <c r="GS14" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU14" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="GS14"/>
+      <c r="GT14"/>
+      <c r="GU14"/>
       <c r="GV14"/>
       <c r="GW14"/>
       <c r="GX14"/>
@@ -7267,22 +7229,10 @@
       <c r="HI14"/>
       <c r="HJ14"/>
       <c r="HK14"/>
-      <c r="HL14" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM14" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
+      <c r="HL14"/>
+      <c r="HM14"/>
       <c r="HN14"/>
-      <c r="HO14" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
+      <c r="HO14"/>
       <c r="HP14"/>
       <c r="HQ14"/>
       <c r="HR14"/>
@@ -7296,7 +7246,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a041a3</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7306,12 +7256,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>home-infusion-ndc.dat</t>
+          <t>cob-prov-payera.dat</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0711</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7321,12 +7271,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2004-03-01T12:00:00</t>
+          <t>2005-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -7336,20 +7286,20 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2232.93</v>
+        <v>79.04</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -7374,7 +7324,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R15"/>
@@ -7385,46 +7335,50 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>1234567893</t>
+          <t>1999996666</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>10-1234567</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Professional Home IV, LLC</t>
-        </is>
-      </c>
-      <c r="W15"/>
+          <t>KILDARE</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
       <c r="X15"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>1500 Industrial Drive</t>
+          <t>1234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z15"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>Libertyville</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="AD15"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>Brenda Holly</t>
+          <t>CONNIE</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -7434,7 +7388,7 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>8019999999</t>
+          <t>3055551234</t>
         </is>
       </c>
       <c r="AH15"/>
@@ -7453,22 +7407,10 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>GRP01020102</t>
-        </is>
-      </c>
+      <c r="AT15"/>
+      <c r="AU15"/>
       <c r="AV15"/>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
+      <c r="AW15"/>
       <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -7476,101 +7418,139 @@
       </c>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>MBRID01234</t>
+          <t>111223333</t>
         </is>
       </c>
       <c r="AZ15"/>
       <c r="BA15" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC15"/>
       <c r="BD15" s="4" t="n">
         <v>15827.0</v>
       </c>
       <c r="BE15" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr">
-        <is>
-          <t>15210 Juliet Lane</t>
-        </is>
-      </c>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF15"/>
       <c r="BG15"/>
-      <c r="BH15" s="3" t="inlineStr">
-        <is>
-          <t>Libertyville</t>
-        </is>
-      </c>
-      <c r="BI15" s="3" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="BJ15" s="3" t="inlineStr">
-        <is>
-          <t>60048</t>
-        </is>
-      </c>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
       <c r="BK15"/>
       <c r="BL15"/>
       <c r="BM15"/>
       <c r="BN15" s="3" t="inlineStr">
         <is>
-          <t>CMS_PLAN_ID</t>
+          <t>PAYOR_ID</t>
         </is>
       </c>
       <c r="BO15" s="3" t="inlineStr">
         <is>
-          <t>PLANID12345</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP15"/>
       <c r="BQ15" s="3" t="inlineStr">
         <is>
-          <t>R&amp;R Health Plan</t>
-        </is>
-      </c>
-      <c r="BR15"/>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
+      <c r="BR15" s="3" t="inlineStr">
+        <is>
+          <t>3333OCEAN ST</t>
+        </is>
+      </c>
       <c r="BS15"/>
-      <c r="BT15"/>
-      <c r="BU15"/>
-      <c r="BV15"/>
-      <c r="BW15"/>
-      <c r="BX15"/>
+      <c r="BT15" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH MIAMI</t>
+        </is>
+      </c>
+      <c r="BU15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV15" s="3" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="BW15" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX15" s="3" t="inlineStr">
+        <is>
+          <t>PBS3334</t>
+        </is>
+      </c>
       <c r="BY15"/>
       <c r="BZ15"/>
-      <c r="CA15"/>
-      <c r="CB15"/>
-      <c r="CC15"/>
+      <c r="CA15" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB15" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC15" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD15"/>
-      <c r="CE15"/>
-      <c r="CF15"/>
-      <c r="CG15"/>
+      <c r="CE15" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF15" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG15" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH15"/>
-      <c r="CI15"/>
-      <c r="CJ15"/>
-      <c r="CK15"/>
+      <c r="CI15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK15" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15"/>
       <c r="CO15" s="4" t="n">
-        <v>38018.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CP15" s="4" t="n">
-        <v>38024.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CQ15"/>
       <c r="CR15"/>
@@ -7597,11 +7577,19 @@
       <c r="DM15"/>
       <c r="DN15" s="3" t="inlineStr">
         <is>
-          <t>J069</t>
-        </is>
-      </c>
-      <c r="DO15"/>
-      <c r="DP15"/>
+          <t>J309</t>
+        </is>
+      </c>
+      <c r="DO15" s="3" t="inlineStr">
+        <is>
+          <t>E785</t>
+        </is>
+      </c>
+      <c r="DP15" s="3" t="inlineStr">
+        <is>
+          <t>E663</t>
+        </is>
+      </c>
       <c r="DQ15"/>
       <c r="DR15"/>
       <c r="DS15"/>
@@ -7625,22 +7613,70 @@
       <c r="EK15"/>
       <c r="EL15"/>
       <c r="EM15"/>
-      <c r="EN15"/>
-      <c r="EO15"/>
-      <c r="EP15"/>
+      <c r="EN15" s="3" t="inlineStr">
+        <is>
+          <t>1999996666</t>
+        </is>
+      </c>
+      <c r="EO15" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE</t>
+        </is>
+      </c>
+      <c r="EP15" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
       <c r="EQ15"/>
-      <c r="ER15"/>
-      <c r="ES15"/>
-      <c r="ET15"/>
+      <c r="ER15" s="3" t="inlineStr">
+        <is>
+          <t>204C00000X</t>
+        </is>
+      </c>
+      <c r="ES15" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET15" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="EU15"/>
       <c r="EV15"/>
-      <c r="EW15"/>
-      <c r="EX15"/>
-      <c r="EY15"/>
+      <c r="EW15" s="3" t="inlineStr">
+        <is>
+          <t>1581234567</t>
+        </is>
+      </c>
+      <c r="EX15" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="EY15" s="3" t="inlineStr">
+        <is>
+          <t>2345 OCEAN BLVD</t>
+        </is>
+      </c>
       <c r="EZ15"/>
-      <c r="FA15"/>
-      <c r="FB15"/>
-      <c r="FC15"/>
+      <c r="FA15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC15" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD15"/>
       <c r="FE15"/>
       <c r="FF15"/>
@@ -7669,22 +7705,66 @@
       <c r="GC15"/>
       <c r="GD15"/>
       <c r="GE15"/>
-      <c r="GF15"/>
-      <c r="GG15"/>
+      <c r="GF15" s="3" t="inlineStr">
+        <is>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="GG15" s="3" t="inlineStr">
+        <is>
+          <t>SPOUSE</t>
+        </is>
+      </c>
       <c r="GH15"/>
       <c r="GI15"/>
-      <c r="GJ15"/>
-      <c r="GK15"/>
-      <c r="GL15"/>
+      <c r="GJ15" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="GK15" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL15" s="3" t="inlineStr">
+        <is>
+          <t>T55TY666</t>
+        </is>
+      </c>
       <c r="GM15"/>
-      <c r="GN15"/>
-      <c r="GO15"/>
+      <c r="GN15" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO15" s="3" t="inlineStr">
+        <is>
+          <t>JACK</t>
+        </is>
+      </c>
       <c r="GP15"/>
-      <c r="GQ15"/>
+      <c r="GQ15" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR15"/>
-      <c r="GS15"/>
-      <c r="GT15"/>
-      <c r="GU15"/>
+      <c r="GS15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU15" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="GV15"/>
       <c r="GW15"/>
       <c r="GX15"/>
@@ -7701,10 +7781,22 @@
       <c r="HI15"/>
       <c r="HJ15"/>
       <c r="HK15"/>
-      <c r="HL15"/>
-      <c r="HM15"/>
+      <c r="HL15" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM15" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
       <c r="HN15"/>
-      <c r="HO15"/>
+      <c r="HO15" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
       <c r="HP15"/>
       <c r="HQ15"/>
       <c r="HR15"/>
@@ -7718,7 +7810,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69e82c68836d7d05c9a041c7</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7728,12 +7820,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>837P-all-fields.dat</t>
+          <t>837P-minimal.dat</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0031</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -7743,7 +7835,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0031</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -7758,7 +7850,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>36463774</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
@@ -7796,14 +7888,10 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R16"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
           <t>NPI</t>
@@ -7821,7 +7909,7 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>Ben Kildare Service</t>
         </is>
       </c>
       <c r="W16"/>
@@ -7847,51 +7935,19 @@
           <t>33111</t>
         </is>
       </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>203BF0100Y</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr">
-        <is>
-          <t>JOHN SMITH</t>
-        </is>
-      </c>
-      <c r="AF16" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG16" s="3" t="inlineStr">
-        <is>
-          <t>5555551234</t>
-        </is>
-      </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="AI16" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
       <c r="AJ16"/>
       <c r="AK16"/>
       <c r="AL16"/>
       <c r="AM16"/>
       <c r="AN16"/>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>STATE_LICENSE_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>654321</t>
-        </is>
-      </c>
+      <c r="AO16"/>
+      <c r="AP16"/>
       <c r="AQ16"/>
       <c r="AR16"/>
       <c r="AS16" s="3" t="inlineStr">
@@ -7899,10 +7955,14 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT16"/>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2222-SJ</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="AV16"/>
@@ -7921,39 +7981,25 @@
           <t>JS00111223333</t>
         </is>
       </c>
-      <c r="AZ16" s="3" t="inlineStr">
-        <is>
-          <t>123450000</t>
-        </is>
-      </c>
+      <c r="AZ16"/>
       <c r="BA16" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="BC16"/>
-      <c r="BD16" s="4" t="n">
-        <v>15827.0</v>
-      </c>
-      <c r="BE16" s="3" t="inlineStr">
-        <is>
-          <t>FEMALE</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="BD16"/>
+      <c r="BE16"/>
+      <c r="BF16"/>
       <c r="BG16"/>
       <c r="BH16" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>MAIMI</t>
         </is>
       </c>
       <c r="BI16" s="3" t="inlineStr">
@@ -7963,20 +8009,12 @@
       </c>
       <c r="BJ16" s="3" t="inlineStr">
         <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="BK16" s="4" t="n">
-        <v>32905.0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>176.0</v>
-      </c>
-      <c r="BM16" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
       <c r="BN16" s="3" t="inlineStr">
         <is>
           <t>PAYOR_ID</t>
@@ -7987,25 +8025,17 @@
           <t>999996666</t>
         </is>
       </c>
-      <c r="BP16" s="3" t="inlineStr">
-        <is>
-          <t>435261708</t>
-        </is>
-      </c>
+      <c r="BP16"/>
       <c r="BQ16" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCECOMPANY</t>
-        </is>
-      </c>
-      <c r="BR16" s="3" t="inlineStr">
-        <is>
-          <t>P.O. BOX 569008</t>
-        </is>
-      </c>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
+      <c r="BR16"/>
       <c r="BS16"/>
       <c r="BT16" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>MAIMI</t>
         </is>
       </c>
       <c r="BU16" s="3" t="inlineStr">
@@ -8015,173 +8045,63 @@
       </c>
       <c r="BV16" s="3" t="inlineStr">
         <is>
-          <t>332560000</t>
-        </is>
-      </c>
-      <c r="BW16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="BW16"/>
+      <c r="BX16"/>
       <c r="BY16"/>
       <c r="BZ16"/>
-      <c r="CA16" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB16" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC16" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA16"/>
+      <c r="CB16"/>
+      <c r="CC16"/>
       <c r="CD16"/>
-      <c r="CE16" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF16" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG16" s="3" t="inlineStr">
-        <is>
-          <t>237 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE16"/>
+      <c r="CF16"/>
+      <c r="CG16"/>
       <c r="CH16"/>
-      <c r="CI16" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK16" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="CL16" s="4" t="n">
-        <v>35503.0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>156.0</v>
-      </c>
-      <c r="CN16" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="CI16"/>
+      <c r="CJ16"/>
+      <c r="CK16"/>
+      <c r="CL16"/>
+      <c r="CM16"/>
+      <c r="CN16"/>
       <c r="CO16" s="4" t="n">
-        <v>38425.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP16" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="CQ16" s="4" t="n">
-        <v>43171.0</v>
-      </c>
-      <c r="CR16" s="4" t="n">
-        <v>43160.0</v>
-      </c>
-      <c r="CS16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CT16" s="4" t="n">
-        <v>43161.0</v>
-      </c>
-      <c r="CU16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CV16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CW16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
+        <v>38993.0</v>
+      </c>
+      <c r="CQ16"/>
+      <c r="CR16"/>
+      <c r="CS16"/>
+      <c r="CT16"/>
+      <c r="CU16"/>
+      <c r="CV16"/>
+      <c r="CW16"/>
       <c r="CX16"/>
-      <c r="CY16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="CZ16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DA16" s="4" t="n">
-        <v>38480.0</v>
-      </c>
-      <c r="DB16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DC16" s="1" t="n">
-        <v>152.45</v>
-      </c>
-      <c r="DD16" s="3" t="inlineStr">
-        <is>
-          <t>ServiceAuthorizationExceptionCode</t>
-        </is>
-      </c>
-      <c r="DE16" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNum</t>
-        </is>
-      </c>
-      <c r="DF16" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuth</t>
-        </is>
-      </c>
-      <c r="DG16" s="3" t="inlineStr">
-        <is>
-          <t>PayerClaimControlNum</t>
-        </is>
-      </c>
+      <c r="CY16"/>
+      <c r="CZ16"/>
+      <c r="DA16"/>
+      <c r="DB16"/>
+      <c r="DC16"/>
+      <c r="DD16"/>
+      <c r="DE16"/>
+      <c r="DF16"/>
+      <c r="DG16"/>
       <c r="DH16" s="3" t="inlineStr">
         <is>
-          <t>ClaimIdForTransm</t>
-        </is>
-      </c>
-      <c r="DI16" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="DJ16" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="DK16" s="3" t="inlineStr">
-        <is>
-          <t>MedicalRecordNum</t>
-        </is>
-      </c>
-      <c r="DL16" s="3" t="inlineStr">
-        <is>
-          <t>DemonstrProjectId</t>
-        </is>
-      </c>
-      <c r="DM16" s="3" t="inlineStr">
-        <is>
-          <t>SURGERY WAS UNUSUALLY LONG</t>
-        </is>
-      </c>
+          <t>17312345600006351</t>
+        </is>
+      </c>
+      <c r="DI16"/>
+      <c r="DJ16"/>
+      <c r="DK16"/>
+      <c r="DL16"/>
+      <c r="DM16"/>
       <c r="DN16" s="3" t="inlineStr">
         <is>
-          <t>J0300</t>
+          <t>J020</t>
         </is>
       </c>
       <c r="DO16" s="3" t="inlineStr">
@@ -8192,190 +8112,58 @@
       <c r="DP16"/>
       <c r="DQ16"/>
       <c r="DR16"/>
-      <c r="DS16" s="3" t="inlineStr">
-        <is>
-          <t>33414</t>
-        </is>
-      </c>
-      <c r="DT16" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="DU16" s="3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+      <c r="DS16"/>
+      <c r="DT16"/>
+      <c r="DU16"/>
       <c r="DV16"/>
-      <c r="DW16" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="DX16" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="DY16" s="3" t="inlineStr">
-        <is>
-          <t>DMN0012</t>
-        </is>
-      </c>
+      <c r="DW16"/>
+      <c r="DX16"/>
+      <c r="DY16"/>
       <c r="DZ16"/>
       <c r="EA16"/>
       <c r="EB16"/>
       <c r="EC16"/>
       <c r="ED16"/>
       <c r="EE16"/>
-      <c r="EF16" s="3" t="inlineStr">
-        <is>
-          <t>5234567805</t>
-        </is>
-      </c>
-      <c r="EG16" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH16" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="EI16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EJ16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="EK16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="EF16"/>
+      <c r="EG16"/>
+      <c r="EH16"/>
+      <c r="EI16"/>
+      <c r="EJ16"/>
+      <c r="EK16"/>
       <c r="EL16"/>
       <c r="EM16"/>
-      <c r="EN16" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="EO16" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EP16" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="EQ16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="ER16" s="3" t="inlineStr">
-        <is>
-          <t>000000000X</t>
-        </is>
-      </c>
-      <c r="ES16" s="3" t="inlineStr">
-        <is>
-          <t>LOCATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="EN16"/>
+      <c r="EO16"/>
+      <c r="EP16"/>
+      <c r="EQ16"/>
+      <c r="ER16"/>
+      <c r="ES16"/>
+      <c r="ET16"/>
       <c r="EU16"/>
       <c r="EV16"/>
-      <c r="EW16" s="3" t="inlineStr">
-        <is>
-          <t>000000004</t>
-        </is>
-      </c>
-      <c r="EX16" s="3" t="inlineStr">
-        <is>
-          <t>Service Facility</t>
-        </is>
-      </c>
-      <c r="EY16" s="3" t="inlineStr">
-        <is>
-          <t>123 FAKE STREET</t>
-        </is>
-      </c>
+      <c r="EW16"/>
+      <c r="EX16"/>
+      <c r="EY16"/>
       <c r="EZ16"/>
-      <c r="FA16" s="3" t="inlineStr">
-        <is>
-          <t>CITY</t>
-        </is>
-      </c>
-      <c r="FB16" s="3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="FC16" s="3" t="inlineStr">
-        <is>
-          <t>123459999</t>
-        </is>
-      </c>
+      <c r="FA16"/>
+      <c r="FB16"/>
+      <c r="FC16"/>
       <c r="FD16"/>
       <c r="FE16"/>
       <c r="FF16"/>
       <c r="FG16"/>
       <c r="FH16"/>
-      <c r="FI16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FJ16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="FI16"/>
+      <c r="FJ16"/>
       <c r="FK16"/>
       <c r="FL16"/>
-      <c r="FM16" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="FN16" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="FO16" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="FP16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="FQ16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FR16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="FM16"/>
+      <c r="FN16"/>
+      <c r="FO16"/>
+      <c r="FP16"/>
+      <c r="FQ16"/>
+      <c r="FR16"/>
       <c r="FS16"/>
       <c r="FT16"/>
       <c r="FU16"/>
@@ -8389,189 +8177,1333 @@
       <c r="GC16"/>
       <c r="GD16"/>
       <c r="GE16"/>
-      <c r="GF16" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="GG16" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="GH16" s="3" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="GI16" s="3" t="inlineStr">
-        <is>
-          <t>PLAN NAME</t>
-        </is>
-      </c>
-      <c r="GJ16" s="3" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="GK16" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL16" s="3" t="inlineStr">
-        <is>
-          <t>JS00111223999</t>
-        </is>
-      </c>
+      <c r="GF16"/>
+      <c r="GG16"/>
+      <c r="GH16"/>
+      <c r="GI16"/>
+      <c r="GJ16"/>
+      <c r="GK16"/>
+      <c r="GL16"/>
       <c r="GM16"/>
-      <c r="GN16" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO16" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="GN16"/>
+      <c r="GO16"/>
       <c r="GP16"/>
-      <c r="GQ16" s="3" t="inlineStr">
-        <is>
-          <t>239 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ16"/>
       <c r="GR16"/>
-      <c r="GS16" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU16" s="3" t="inlineStr">
-        <is>
-          <t>33415</t>
-        </is>
-      </c>
-      <c r="GV16" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="GW16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="GX16" s="1" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="GS16"/>
+      <c r="GT16"/>
+      <c r="GU16"/>
+      <c r="GV16"/>
+      <c r="GW16"/>
+      <c r="GX16"/>
       <c r="GY16"/>
-      <c r="GZ16" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="HA16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="HB16" s="1" t="n">
-        <v>15.0</v>
-      </c>
+      <c r="GZ16"/>
+      <c r="HA16"/>
+      <c r="HB16"/>
       <c r="HC16"/>
-      <c r="HD16" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="HE16" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="HF16" s="1" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="HG16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="HH16" s="1" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="HI16" s="1" t="n">
-        <v>273.0</v>
-      </c>
-      <c r="HJ16" s="1" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="HK16" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM99</t>
-        </is>
-      </c>
-      <c r="HL16" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM16" s="3" t="inlineStr">
-        <is>
-          <t>OTP</t>
-        </is>
-      </c>
-      <c r="HN16" s="3" t="inlineStr">
-        <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="HO16" s="3" t="inlineStr">
-        <is>
-          <t>OTHER PAYER</t>
-        </is>
-      </c>
-      <c r="HP16" s="3" t="inlineStr">
-        <is>
-          <t>PO BOX 7901</t>
-        </is>
-      </c>
-      <c r="HQ16" s="3" t="inlineStr">
-        <is>
-          <t>DEP 2</t>
-        </is>
-      </c>
-      <c r="HR16" s="3" t="inlineStr">
-        <is>
-          <t>MADISON</t>
-        </is>
-      </c>
-      <c r="HS16" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="HT16" s="3" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="HU16" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM_OFFICE_NUMBER</t>
-        </is>
-      </c>
-      <c r="HV16" s="3" t="inlineStr">
-        <is>
-          <t>98765</t>
-        </is>
-      </c>
+      <c r="HD16"/>
+      <c r="HE16"/>
+      <c r="HF16"/>
+      <c r="HG16"/>
+      <c r="HH16"/>
+      <c r="HI16"/>
+      <c r="HJ16"/>
+      <c r="HK16"/>
+      <c r="HL16"/>
+      <c r="HM16"/>
+      <c r="HN16"/>
+      <c r="HO16"/>
+      <c r="HP16"/>
+      <c r="HQ16"/>
+      <c r="HR16"/>
+      <c r="HS16"/>
+      <c r="HT16"/>
+      <c r="HU16"/>
+      <c r="HV16"/>
       <c r="HW16"/>
       <c r="HX16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>69e82c68836d7d05c9a0420f</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>837P</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>home-infusion-ndc.dat</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>0711</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>0013</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2004-03-01T12:00:00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>CHARGEABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>CLMNO12345</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>2232.93</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R17"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>1234567893</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>10-1234567</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Professional Home IV, LLC</t>
+        </is>
+      </c>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>1500 Industrial Drive</t>
+        </is>
+      </c>
+      <c r="Z17"/>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Libertyville</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>60048</t>
+        </is>
+      </c>
+      <c r="AD17"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Brenda Holly</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>8019999999</t>
+        </is>
+      </c>
+      <c r="AH17"/>
+      <c r="AI17"/>
+      <c r="AJ17"/>
+      <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>GRP01020102</t>
+        </is>
+      </c>
+      <c r="AV17"/>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="AY17" s="3" t="inlineStr">
+        <is>
+          <t>MBRID01234</t>
+        </is>
+      </c>
+      <c r="AZ17"/>
+      <c r="BA17" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="BB17" s="3" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="BC17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD17" s="4" t="n">
+        <v>15827.0</v>
+      </c>
+      <c r="BE17" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="BF17" s="3" t="inlineStr">
+        <is>
+          <t>15210 Juliet Lane</t>
+        </is>
+      </c>
+      <c r="BG17"/>
+      <c r="BH17" s="3" t="inlineStr">
+        <is>
+          <t>Libertyville</t>
+        </is>
+      </c>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="BJ17" s="3" t="inlineStr">
+        <is>
+          <t>60048</t>
+        </is>
+      </c>
+      <c r="BK17"/>
+      <c r="BL17"/>
+      <c r="BM17"/>
+      <c r="BN17" s="3" t="inlineStr">
+        <is>
+          <t>CMS_PLAN_ID</t>
+        </is>
+      </c>
+      <c r="BO17" s="3" t="inlineStr">
+        <is>
+          <t>PLANID12345</t>
+        </is>
+      </c>
+      <c r="BP17"/>
+      <c r="BQ17" s="3" t="inlineStr">
+        <is>
+          <t>R&amp;R Health Plan</t>
+        </is>
+      </c>
+      <c r="BR17"/>
+      <c r="BS17"/>
+      <c r="BT17"/>
+      <c r="BU17"/>
+      <c r="BV17"/>
+      <c r="BW17"/>
+      <c r="BX17"/>
+      <c r="BY17"/>
+      <c r="BZ17"/>
+      <c r="CA17"/>
+      <c r="CB17"/>
+      <c r="CC17"/>
+      <c r="CD17"/>
+      <c r="CE17"/>
+      <c r="CF17"/>
+      <c r="CG17"/>
+      <c r="CH17"/>
+      <c r="CI17"/>
+      <c r="CJ17"/>
+      <c r="CK17"/>
+      <c r="CL17"/>
+      <c r="CM17"/>
+      <c r="CN17"/>
+      <c r="CO17" s="4" t="n">
+        <v>38018.0</v>
+      </c>
+      <c r="CP17" s="4" t="n">
+        <v>38024.0</v>
+      </c>
+      <c r="CQ17"/>
+      <c r="CR17"/>
+      <c r="CS17"/>
+      <c r="CT17"/>
+      <c r="CU17"/>
+      <c r="CV17"/>
+      <c r="CW17"/>
+      <c r="CX17"/>
+      <c r="CY17"/>
+      <c r="CZ17"/>
+      <c r="DA17"/>
+      <c r="DB17"/>
+      <c r="DC17"/>
+      <c r="DD17"/>
+      <c r="DE17"/>
+      <c r="DF17"/>
+      <c r="DG17"/>
+      <c r="DH17"/>
+      <c r="DI17"/>
+      <c r="DJ17"/>
+      <c r="DK17"/>
+      <c r="DL17"/>
+      <c r="DM17"/>
+      <c r="DN17" s="3" t="inlineStr">
+        <is>
+          <t>J069</t>
+        </is>
+      </c>
+      <c r="DO17"/>
+      <c r="DP17"/>
+      <c r="DQ17"/>
+      <c r="DR17"/>
+      <c r="DS17"/>
+      <c r="DT17"/>
+      <c r="DU17"/>
+      <c r="DV17"/>
+      <c r="DW17"/>
+      <c r="DX17"/>
+      <c r="DY17"/>
+      <c r="DZ17"/>
+      <c r="EA17"/>
+      <c r="EB17"/>
+      <c r="EC17"/>
+      <c r="ED17"/>
+      <c r="EE17"/>
+      <c r="EF17"/>
+      <c r="EG17"/>
+      <c r="EH17"/>
+      <c r="EI17"/>
+      <c r="EJ17"/>
+      <c r="EK17"/>
+      <c r="EL17"/>
+      <c r="EM17"/>
+      <c r="EN17"/>
+      <c r="EO17"/>
+      <c r="EP17"/>
+      <c r="EQ17"/>
+      <c r="ER17"/>
+      <c r="ES17"/>
+      <c r="ET17"/>
+      <c r="EU17"/>
+      <c r="EV17"/>
+      <c r="EW17"/>
+      <c r="EX17"/>
+      <c r="EY17"/>
+      <c r="EZ17"/>
+      <c r="FA17"/>
+      <c r="FB17"/>
+      <c r="FC17"/>
+      <c r="FD17"/>
+      <c r="FE17"/>
+      <c r="FF17"/>
+      <c r="FG17"/>
+      <c r="FH17"/>
+      <c r="FI17"/>
+      <c r="FJ17"/>
+      <c r="FK17"/>
+      <c r="FL17"/>
+      <c r="FM17"/>
+      <c r="FN17"/>
+      <c r="FO17"/>
+      <c r="FP17"/>
+      <c r="FQ17"/>
+      <c r="FR17"/>
+      <c r="FS17"/>
+      <c r="FT17"/>
+      <c r="FU17"/>
+      <c r="FV17"/>
+      <c r="FW17"/>
+      <c r="FX17"/>
+      <c r="FY17"/>
+      <c r="FZ17"/>
+      <c r="GA17"/>
+      <c r="GB17"/>
+      <c r="GC17"/>
+      <c r="GD17"/>
+      <c r="GE17"/>
+      <c r="GF17"/>
+      <c r="GG17"/>
+      <c r="GH17"/>
+      <c r="GI17"/>
+      <c r="GJ17"/>
+      <c r="GK17"/>
+      <c r="GL17"/>
+      <c r="GM17"/>
+      <c r="GN17"/>
+      <c r="GO17"/>
+      <c r="GP17"/>
+      <c r="GQ17"/>
+      <c r="GR17"/>
+      <c r="GS17"/>
+      <c r="GT17"/>
+      <c r="GU17"/>
+      <c r="GV17"/>
+      <c r="GW17"/>
+      <c r="GX17"/>
+      <c r="GY17"/>
+      <c r="GZ17"/>
+      <c r="HA17"/>
+      <c r="HB17"/>
+      <c r="HC17"/>
+      <c r="HD17"/>
+      <c r="HE17"/>
+      <c r="HF17"/>
+      <c r="HG17"/>
+      <c r="HH17"/>
+      <c r="HI17"/>
+      <c r="HJ17"/>
+      <c r="HK17"/>
+      <c r="HL17"/>
+      <c r="HM17"/>
+      <c r="HN17"/>
+      <c r="HO17"/>
+      <c r="HP17"/>
+      <c r="HQ17"/>
+      <c r="HR17"/>
+      <c r="HS17"/>
+      <c r="HT17"/>
+      <c r="HU17"/>
+      <c r="HV17"/>
+      <c r="HW17"/>
+      <c r="HX17"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>69e82c68836d7d05c9a042cd</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>837P</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>837P-all-fields.dat</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>2006-10-15T10:23:00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>CHARGEABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>36463774</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>587654321</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>BEN KILDARE SERVICE</t>
+        </is>
+      </c>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>234 SEAWAY ST</t>
+        </is>
+      </c>
+      <c r="Z18"/>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr">
+        <is>
+          <t>203BF0100Y</t>
+        </is>
+      </c>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>JOHN SMITH</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>5555551234</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>STATE_LICENSE_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>654321</t>
+        </is>
+      </c>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="AT18"/>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
+      <c r="AV18"/>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="AY18" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223333</t>
+        </is>
+      </c>
+      <c r="AZ18" s="3" t="inlineStr">
+        <is>
+          <t>123450000</t>
+        </is>
+      </c>
+      <c r="BA18" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="BB18" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC18"/>
+      <c r="BD18" s="4" t="n">
+        <v>15827.0</v>
+      </c>
+      <c r="BE18" s="3" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF18" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="BG18"/>
+      <c r="BH18" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BI18" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ18" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="BK18" s="4" t="n">
+        <v>32905.0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>176.0</v>
+      </c>
+      <c r="BM18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BN18" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="BO18" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
+      <c r="BP18" s="3" t="inlineStr">
+        <is>
+          <t>435261708</t>
+        </is>
+      </c>
+      <c r="BQ18" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCECOMPANY</t>
+        </is>
+      </c>
+      <c r="BR18" s="3" t="inlineStr">
+        <is>
+          <t>P.O. BOX 569008</t>
+        </is>
+      </c>
+      <c r="BS18"/>
+      <c r="BT18" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BU18" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV18" s="3" t="inlineStr">
+        <is>
+          <t>332560000</t>
+        </is>
+      </c>
+      <c r="BW18" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX18" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="BY18"/>
+      <c r="BZ18"/>
+      <c r="CA18" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB18" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC18" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="CD18"/>
+      <c r="CE18" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF18" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG18" s="3" t="inlineStr">
+        <is>
+          <t>237 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="CH18"/>
+      <c r="CI18" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ18" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK18" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="CL18" s="4" t="n">
+        <v>35503.0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="CN18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="CO18" s="4" t="n">
+        <v>38425.0</v>
+      </c>
+      <c r="CP18" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="CQ18" s="4" t="n">
+        <v>43171.0</v>
+      </c>
+      <c r="CR18" s="4" t="n">
+        <v>43160.0</v>
+      </c>
+      <c r="CS18" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CT18" s="4" t="n">
+        <v>43161.0</v>
+      </c>
+      <c r="CU18" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CV18" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CW18" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CX18" s="4" t="n">
+        <v>38473.0</v>
+      </c>
+      <c r="CY18" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="CZ18" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DA18" s="4" t="n">
+        <v>38480.0</v>
+      </c>
+      <c r="DB18" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DC18" s="1" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="DD18" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="DE18" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNum</t>
+        </is>
+      </c>
+      <c r="DF18" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuth</t>
+        </is>
+      </c>
+      <c r="DG18" s="3" t="inlineStr">
+        <is>
+          <t>PayerClaimControlNum</t>
+        </is>
+      </c>
+      <c r="DH18" s="3" t="inlineStr">
+        <is>
+          <t>ClaimIdForTransm</t>
+        </is>
+      </c>
+      <c r="DI18" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="DJ18" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="DK18" s="3" t="inlineStr">
+        <is>
+          <t>MedicalRecordNum</t>
+        </is>
+      </c>
+      <c r="DL18" s="3" t="inlineStr">
+        <is>
+          <t>DemonstrProjectId</t>
+        </is>
+      </c>
+      <c r="DM18" s="3" t="inlineStr">
+        <is>
+          <t>SURGERY WAS UNUSUALLY LONG</t>
+        </is>
+      </c>
+      <c r="DN18" s="3" t="inlineStr">
+        <is>
+          <t>J0300</t>
+        </is>
+      </c>
+      <c r="DO18" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
+      <c r="DP18"/>
+      <c r="DQ18"/>
+      <c r="DR18"/>
+      <c r="DS18" s="3" t="inlineStr">
+        <is>
+          <t>33414</t>
+        </is>
+      </c>
+      <c r="DT18" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="DU18" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="DV18"/>
+      <c r="DW18" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="DX18" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="DY18" s="3" t="inlineStr">
+        <is>
+          <t>DMN0012</t>
+        </is>
+      </c>
+      <c r="DZ18"/>
+      <c r="EA18"/>
+      <c r="EB18"/>
+      <c r="EC18"/>
+      <c r="ED18"/>
+      <c r="EE18"/>
+      <c r="EF18" s="3" t="inlineStr">
+        <is>
+          <t>5234567805</t>
+        </is>
+      </c>
+      <c r="EG18" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH18" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="EI18" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EJ18" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="EK18" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="EL18"/>
+      <c r="EM18"/>
+      <c r="EN18" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="EO18" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EP18" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="EQ18" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER18" s="3" t="inlineStr">
+        <is>
+          <t>000000000X</t>
+        </is>
+      </c>
+      <c r="ES18" s="3" t="inlineStr">
+        <is>
+          <t>LOCATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET18" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="EU18"/>
+      <c r="EV18"/>
+      <c r="EW18" s="3" t="inlineStr">
+        <is>
+          <t>000000004</t>
+        </is>
+      </c>
+      <c r="EX18" s="3" t="inlineStr">
+        <is>
+          <t>Service Facility</t>
+        </is>
+      </c>
+      <c r="EY18" s="3" t="inlineStr">
+        <is>
+          <t>123 FAKE STREET</t>
+        </is>
+      </c>
+      <c r="EZ18"/>
+      <c r="FA18" s="3" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="FB18" s="3" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="FC18" s="3" t="inlineStr">
+        <is>
+          <t>123459999</t>
+        </is>
+      </c>
+      <c r="FD18"/>
+      <c r="FE18"/>
+      <c r="FF18"/>
+      <c r="FG18"/>
+      <c r="FH18"/>
+      <c r="FI18" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FJ18" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="FK18"/>
+      <c r="FL18"/>
+      <c r="FM18" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="FN18" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="FO18" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="FP18" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ18" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FR18" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="FS18"/>
+      <c r="FT18"/>
+      <c r="FU18"/>
+      <c r="FV18"/>
+      <c r="FW18"/>
+      <c r="FX18"/>
+      <c r="FY18"/>
+      <c r="FZ18"/>
+      <c r="GA18"/>
+      <c r="GB18"/>
+      <c r="GC18"/>
+      <c r="GD18"/>
+      <c r="GE18"/>
+      <c r="GF18" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="GG18" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="GH18" s="3" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="GI18" s="3" t="inlineStr">
+        <is>
+          <t>PLAN NAME</t>
+        </is>
+      </c>
+      <c r="GJ18" s="3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="GK18" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL18" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223999</t>
+        </is>
+      </c>
+      <c r="GM18"/>
+      <c r="GN18" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO18" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="GP18"/>
+      <c r="GQ18" s="3" t="inlineStr">
+        <is>
+          <t>239 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="GR18"/>
+      <c r="GS18" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT18" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU18" s="3" t="inlineStr">
+        <is>
+          <t>33415</t>
+        </is>
+      </c>
+      <c r="GV18" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="GW18" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="GX18" s="1" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="GY18"/>
+      <c r="GZ18" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="HA18" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="HB18" s="1" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="HC18"/>
+      <c r="HD18" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="HE18" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="HF18" s="1" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="HG18" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HH18" s="1" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="HI18" s="1" t="n">
+        <v>273.0</v>
+      </c>
+      <c r="HJ18" s="1" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="HK18" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM99</t>
+        </is>
+      </c>
+      <c r="HL18" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM18" s="3" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="HN18" s="3" t="inlineStr">
+        <is>
+          <t>987654321</t>
+        </is>
+      </c>
+      <c r="HO18" s="3" t="inlineStr">
+        <is>
+          <t>OTHER PAYER</t>
+        </is>
+      </c>
+      <c r="HP18" s="3" t="inlineStr">
+        <is>
+          <t>PO BOX 7901</t>
+        </is>
+      </c>
+      <c r="HQ18" s="3" t="inlineStr">
+        <is>
+          <t>DEP 2</t>
+        </is>
+      </c>
+      <c r="HR18" s="3" t="inlineStr">
+        <is>
+          <t>MADISON</t>
+        </is>
+      </c>
+      <c r="HS18" s="3" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="HT18" s="3" t="inlineStr">
+        <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="HU18" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM_OFFICE_NUMBER</t>
+        </is>
+      </c>
+      <c r="HV18" s="3" t="inlineStr">
+        <is>
+          <t>98765</t>
+        </is>
+      </c>
+      <c r="HW18"/>
+      <c r="HX18"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8580,7 +9512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:DS45"/>
+  <dimension ref="A1:DS47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -9203,7 +10135,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69e82c68836d7d05c9a03f19</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -9406,7 +10338,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69e82c68836d7d05c9a03f19</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9573,7 +10505,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69e82c68836d7d05c9a03f19</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -9740,7 +10672,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69e82c68836d7d05c9a03f19</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9907,7 +10839,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69e82c68836d7d05c9a03f4a</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10062,7 +10994,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69e82c68836d7d05c9a03f4a</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -10217,7 +11149,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69e82c68836d7d05c9a03f4a</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -10372,7 +11304,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69e82c68836d7d05c9a03f4a</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -10527,7 +11459,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4177</t>
+          <t>69e82c68836d7d05c9a03f74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -10682,7 +11614,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69e82c68836d7d05c9a03fbd</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -10841,7 +11773,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69e82c68836d7d05c9a03fbd</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -10998,7 +11930,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69e82c68836d7d05c9a03fbd</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -11155,7 +12087,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69e82c68836d7d05c9a03ff5</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11179,7 +12111,7 @@
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" s="1" t="n">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -11189,22 +12121,42 @@
       <c r="L14" t="n">
         <v>1.0</v>
       </c>
-      <c r="M14"/>
-      <c r="N14"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
-      <c r="R14"/>
-      <c r="S14"/>
-      <c r="T14"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="U14"/>
       <c r="V14" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="X14"/>
       <c r="Y14"/>
@@ -11310,7 +12262,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69e82c68836d7d05c9a04024</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11320,12 +12272,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E15"/>
@@ -11334,7 +12286,7 @@
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -11465,7 +12417,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69e82c68836d7d05c9a04024</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -11475,12 +12427,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E16"/>
@@ -11489,7 +12441,7 @@
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -11502,7 +12454,7 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
@@ -11511,10 +12463,10 @@
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X16"/>
       <c r="Y16"/>
@@ -11620,22 +12572,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69e82c68836d7d05c9a04024</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E17"/>
@@ -11644,7 +12596,7 @@
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" s="1" t="n">
-        <v>40.0</v>
+        <v>35.0</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -11657,7 +12609,7 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
@@ -11666,10 +12618,10 @@
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X17"/>
       <c r="Y17"/>
@@ -11775,7 +12727,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69e82c68836d7d05c9a0409b</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -11785,12 +12737,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E18"/>
@@ -11799,7 +12751,7 @@
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -11930,7 +12882,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69e82c68836d7d05c9a0409b</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -11940,12 +12892,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E19"/>
@@ -11954,7 +12906,7 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -11967,7 +12919,7 @@
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
@@ -11976,10 +12928,10 @@
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X19"/>
       <c r="Y19"/>
@@ -12085,7 +13037,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69e82c68836d7d05c9a0409b</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12095,12 +13047,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E20"/>
@@ -12109,7 +13061,7 @@
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" s="1" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -12240,22 +13192,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4267</t>
+          <t>69e82c68836d7d05c9a0409b</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E21"/>
@@ -12264,7 +13216,7 @@
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" s="1" t="n">
-        <v>145.5</v>
+        <v>10.0</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -12277,7 +13229,7 @@
       <c r="M21"/>
       <c r="N21"/>
       <c r="O21" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -12286,10 +13238,10 @@
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21" s="4" t="n">
-        <v>38398.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>38398.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X21"/>
       <c r="Y21"/>
@@ -12395,51 +13347,39 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69e82c68836d7d05c9a0409c</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="E22"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>QK</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22"/>
       <c r="J22" s="1" t="n">
-        <v>827.0</v>
+        <v>145.5</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
@@ -12453,10 +13393,10 @@
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="X22"/>
       <c r="Y22"/>
@@ -12562,7 +13502,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69e82c68836d7d05c9a0409d</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -12572,7 +13512,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -12620,10 +13560,10 @@
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X23"/>
       <c r="Y23"/>
@@ -12729,39 +13669,51 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69e82c68836d7d05c9a0409d</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="I24"/>
       <c r="J24" s="1" t="n">
-        <v>40.0</v>
+        <v>827.0</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -12775,10 +13727,10 @@
       <c r="T24"/>
       <c r="U24"/>
       <c r="V24" s="4" t="n">
-        <v>38993.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>38993.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X24"/>
       <c r="Y24"/>
@@ -12884,7 +13836,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69e82c68836d7d05c9a040d0</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -12894,12 +13846,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E25"/>
@@ -12908,7 +13860,7 @@
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -13039,7 +13991,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69e82c68836d7d05c9a040d0</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -13049,12 +14001,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E26"/>
@@ -13063,7 +14015,7 @@
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -13076,7 +14028,7 @@
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
@@ -13085,10 +14037,10 @@
       <c r="T26"/>
       <c r="U26"/>
       <c r="V26" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X26"/>
       <c r="Y26"/>
@@ -13194,7 +14146,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69e82c68836d7d05c9a040d0</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -13204,12 +14156,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E27"/>
@@ -13218,7 +14170,7 @@
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" s="1" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -13349,56 +14301,44 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69e82c68836d7d05c9a040d0</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E28"/>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>QK</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
       <c r="I28"/>
       <c r="J28" s="1" t="n">
-        <v>827.0</v>
+        <v>10.0</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
@@ -13407,10 +14347,10 @@
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28" s="4" t="n">
-        <v>38364.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>38364.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X28"/>
       <c r="Y28"/>
@@ -13516,7 +14456,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69e82c68836d7d05c9a040fd</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -13526,7 +14466,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -13574,10 +14514,10 @@
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X29"/>
       <c r="Y29"/>
@@ -13683,75 +14623,71 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42f6</t>
+          <t>69e82c68836d7d05c9a040fd</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>K0001</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E30"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>QK</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I30"/>
       <c r="J30" s="1" t="n">
-        <v>75.0</v>
+        <v>827.0</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M30"/>
       <c r="N30"/>
       <c r="O30" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P30" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X30"/>
-      <c r="Y30" s="4" t="n">
-        <v>38067.0</v>
-      </c>
+      <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
       <c r="AB30"/>
@@ -13766,16 +14702,8 @@
       <c r="AK30"/>
       <c r="AL30"/>
       <c r="AM30"/>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
+      <c r="AN30"/>
+      <c r="AO30"/>
       <c r="AP30"/>
       <c r="AQ30"/>
       <c r="AR30"/>
@@ -13829,70 +14757,22 @@
       <c r="CN30"/>
       <c r="CO30"/>
       <c r="CP30"/>
-      <c r="CQ30" s="3" t="inlineStr">
-        <is>
-          <t>1111155555</t>
-        </is>
-      </c>
-      <c r="CR30" s="3" t="inlineStr">
-        <is>
-          <t>WILSON</t>
-        </is>
-      </c>
-      <c r="CS30" s="3" t="inlineStr">
-        <is>
-          <t>RANDALL</t>
-        </is>
-      </c>
+      <c r="CQ30"/>
+      <c r="CR30"/>
+      <c r="CS30"/>
       <c r="CT30"/>
-      <c r="CU30" s="3" t="inlineStr">
-        <is>
-          <t>1226 WEST RAILROAD STREET</t>
-        </is>
-      </c>
+      <c r="CU30"/>
       <c r="CV30"/>
-      <c r="CW30" s="3" t="inlineStr">
-        <is>
-          <t>LAFAYETTE</t>
-        </is>
-      </c>
-      <c r="CX30" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="CY30" s="3" t="inlineStr">
-        <is>
-          <t>47905</t>
-        </is>
-      </c>
-      <c r="CZ30" s="3" t="inlineStr">
-        <is>
-          <t>LEE</t>
-        </is>
-      </c>
-      <c r="DA30" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="DB30" s="3" t="inlineStr">
-        <is>
-          <t>7659259999</t>
-        </is>
-      </c>
+      <c r="CW30"/>
+      <c r="CX30"/>
+      <c r="CY30"/>
+      <c r="CZ30"/>
+      <c r="DA30"/>
+      <c r="DB30"/>
       <c r="DC30"/>
       <c r="DD30"/>
-      <c r="DE30" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DF30" s="3" t="inlineStr">
-        <is>
-          <t>M12345</t>
-        </is>
-      </c>
+      <c r="DE30"/>
+      <c r="DF30"/>
       <c r="DG30"/>
       <c r="DH30"/>
       <c r="DI30"/>
@@ -13910,12 +14790,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69e82c68836d7d05c9a04138</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -13925,7 +14805,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>E0570</t>
+          <t>K0001</t>
         </is>
       </c>
       <c r="E31"/>
@@ -13934,11 +14814,19 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="G31"/>
-      <c r="H31"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="I31"/>
       <c r="J31" s="1" t="n">
-        <v>25.0</v>
+        <v>75.0</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -13962,23 +14850,21 @@
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="X31"/>
-      <c r="Y31"/>
+      <c r="Y31" s="4" t="n">
+        <v>38067.0</v>
+      </c>
       <c r="Z31"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31"/>
-      <c r="AE31" s="3" t="inlineStr">
-        <is>
-          <t>V123456</t>
-        </is>
-      </c>
+      <c r="AE31"/>
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
@@ -13987,8 +14873,16 @@
       <c r="AK31"/>
       <c r="AL31"/>
       <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
       <c r="AP31"/>
       <c r="AQ31"/>
       <c r="AR31"/>
@@ -14034,42 +14928,78 @@
       <c r="CF31"/>
       <c r="CG31"/>
       <c r="CH31"/>
-      <c r="CI31" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="CJ31" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CK31" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="CI31"/>
+      <c r="CJ31"/>
+      <c r="CK31"/>
       <c r="CL31"/>
       <c r="CM31"/>
       <c r="CN31"/>
       <c r="CO31"/>
       <c r="CP31"/>
-      <c r="CQ31"/>
-      <c r="CR31"/>
-      <c r="CS31"/>
+      <c r="CQ31" s="3" t="inlineStr">
+        <is>
+          <t>1111155555</t>
+        </is>
+      </c>
+      <c r="CR31" s="3" t="inlineStr">
+        <is>
+          <t>WILSON</t>
+        </is>
+      </c>
+      <c r="CS31" s="3" t="inlineStr">
+        <is>
+          <t>RANDALL</t>
+        </is>
+      </c>
       <c r="CT31"/>
-      <c r="CU31"/>
+      <c r="CU31" s="3" t="inlineStr">
+        <is>
+          <t>1226 WEST RAILROAD STREET</t>
+        </is>
+      </c>
       <c r="CV31"/>
-      <c r="CW31"/>
-      <c r="CX31"/>
-      <c r="CY31"/>
-      <c r="CZ31"/>
-      <c r="DA31"/>
-      <c r="DB31"/>
+      <c r="CW31" s="3" t="inlineStr">
+        <is>
+          <t>LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="CX31" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="CY31" s="3" t="inlineStr">
+        <is>
+          <t>47905</t>
+        </is>
+      </c>
+      <c r="CZ31" s="3" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="DA31" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="DB31" s="3" t="inlineStr">
+        <is>
+          <t>7659259999</t>
+        </is>
+      </c>
       <c r="DC31"/>
       <c r="DD31"/>
-      <c r="DE31"/>
-      <c r="DF31"/>
+      <c r="DE31" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="DF31" s="3" t="inlineStr">
+        <is>
+          <t>M12345</t>
+        </is>
+      </c>
       <c r="DG31"/>
       <c r="DH31"/>
       <c r="DI31"/>
@@ -14087,7 +15017,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69e82c68836d7d05c9a04168</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -14097,25 +15027,25 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>A7003</t>
+          <t>E0570</t>
         </is>
       </c>
       <c r="E32"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" s="1" t="n">
-        <v>3.75</v>
+        <v>25.0</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -14130,7 +15060,9 @@
       <c r="O32" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P32"/>
+      <c r="P32" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
@@ -14149,7 +15081,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32"/>
-      <c r="AE32"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>V123456</t>
+        </is>
+      </c>
       <c r="AF32"/>
       <c r="AG32"/>
       <c r="AH32"/>
@@ -14205,9 +15141,21 @@
       <c r="CF32"/>
       <c r="CG32"/>
       <c r="CH32"/>
-      <c r="CI32"/>
-      <c r="CJ32"/>
-      <c r="CK32"/>
+      <c r="CI32" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="CJ32" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK32" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="CL32"/>
       <c r="CM32"/>
       <c r="CN32"/>
@@ -14246,31 +15194,35 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69e82c68836d7d05c9a04168</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>A7003</t>
         </is>
       </c>
       <c r="E33"/>
-      <c r="F33"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" s="1" t="n">
-        <v>43.0</v>
+        <v>3.75</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -14285,21 +15237,17 @@
       <c r="O33" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P33" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>3.0</v>
-      </c>
+      <c r="P33"/>
+      <c r="Q33"/>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33"/>
       <c r="U33"/>
       <c r="V33" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="X33"/>
       <c r="Y33"/>
@@ -14405,7 +15353,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69e82c68836d7d05c9a041a3</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14415,12 +15363,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E34"/>
@@ -14429,7 +15377,7 @@
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" s="1" t="n">
-        <v>15.0</v>
+        <v>43.0</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -14447,7 +15395,9 @@
       <c r="P34" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Q34"/>
+      <c r="Q34" s="2" t="n">
+        <v>3.0</v>
+      </c>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34"/>
@@ -14562,7 +15512,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69e82c68836d7d05c9a041a3</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -14572,12 +15522,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>J3301</t>
+          <t>96372</t>
         </is>
       </c>
       <c r="E35"/>
@@ -14586,7 +15536,7 @@
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" s="1" t="n">
-        <v>21.04</v>
+        <v>15.0</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -14719,22 +15669,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a041a3</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>S9500</t>
+          <t>J3301</t>
         </is>
       </c>
       <c r="E36"/>
@@ -14743,7 +15693,7 @@
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" s="1" t="n">
-        <v>1400.0</v>
+        <v>21.04</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -14751,32 +15701,26 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="M36"/>
+      <c r="N36"/>
       <c r="O36" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P36"/>
+      <c r="P36" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
       <c r="V36" s="4" t="n">
-        <v>38018.0</v>
+        <v>38628.0</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>38024.0</v>
+        <v>38628.0</v>
       </c>
       <c r="X36"/>
       <c r="Y36"/>
@@ -14849,21 +15793,9 @@
       <c r="CN36"/>
       <c r="CO36"/>
       <c r="CP36"/>
-      <c r="CQ36" s="3" t="inlineStr">
-        <is>
-          <t>1112223338</t>
-        </is>
-      </c>
-      <c r="CR36" s="3" t="inlineStr">
-        <is>
-          <t>Welby</t>
-        </is>
-      </c>
-      <c r="CS36" s="3" t="inlineStr">
-        <is>
-          <t>Marcus</t>
-        </is>
-      </c>
+      <c r="CQ36"/>
+      <c r="CR36"/>
+      <c r="CS36"/>
       <c r="CT36"/>
       <c r="CU36"/>
       <c r="CV36"/>
@@ -14894,22 +15826,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a041c7</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>S5001</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E37"/>
@@ -14918,7 +15850,7 @@
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" s="1" t="n">
-        <v>682.5</v>
+        <v>40.0</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -14926,18 +15858,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="M37"/>
+      <c r="N37"/>
       <c r="O37" s="2" t="n">
         <v>1.0</v>
       </c>
@@ -14948,14 +15872,12 @@
       <c r="T37"/>
       <c r="U37"/>
       <c r="V37" s="4" t="n">
-        <v>38018.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>38024.0</v>
-      </c>
-      <c r="X37" s="4" t="n">
-        <v>38016.0</v>
-      </c>
+        <v>38993.0</v>
+      </c>
+      <c r="X37"/>
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
@@ -14967,24 +15889,10 @@
       <c r="AG37"/>
       <c r="AH37"/>
       <c r="AI37"/>
-      <c r="AJ37" s="3" t="inlineStr">
-        <is>
-          <t>00003161201</t>
-        </is>
-      </c>
-      <c r="AK37" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="AL37" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2530001</t>
-        </is>
-      </c>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
       <c r="AN37"/>
       <c r="AO37"/>
       <c r="AP37"/>
@@ -15040,21 +15948,9 @@
       <c r="CN37"/>
       <c r="CO37"/>
       <c r="CP37"/>
-      <c r="CQ37" s="3" t="inlineStr">
-        <is>
-          <t>1112223338</t>
-        </is>
-      </c>
-      <c r="CR37" s="3" t="inlineStr">
-        <is>
-          <t>Welby</t>
-        </is>
-      </c>
-      <c r="CS37" s="3" t="inlineStr">
-        <is>
-          <t>Marcus</t>
-        </is>
-      </c>
+      <c r="CQ37"/>
+      <c r="CR37"/>
+      <c r="CS37"/>
       <c r="CT37"/>
       <c r="CU37"/>
       <c r="CV37"/>
@@ -15085,7 +15981,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -15095,12 +15991,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>S5000</t>
+          <t>S9500</t>
         </is>
       </c>
       <c r="E38"/>
@@ -15109,7 +16005,7 @@
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" s="1" t="n">
-        <v>15.12</v>
+        <v>1400.0</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -15117,7 +16013,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -15144,9 +16040,7 @@
       <c r="W38" s="4" t="n">
         <v>38024.0</v>
       </c>
-      <c r="X38" s="4" t="n">
-        <v>38016.0</v>
-      </c>
+      <c r="X38"/>
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
@@ -15158,24 +16052,10 @@
       <c r="AG38"/>
       <c r="AH38"/>
       <c r="AI38"/>
-      <c r="AJ38" s="3" t="inlineStr">
-        <is>
-          <t>63323025510</t>
-        </is>
-      </c>
-      <c r="AK38" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="AL38" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2530001</t>
-        </is>
-      </c>
+      <c r="AJ38"/>
+      <c r="AK38"/>
+      <c r="AL38"/>
+      <c r="AM38"/>
       <c r="AN38"/>
       <c r="AO38"/>
       <c r="AP38"/>
@@ -15276,7 +16156,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -15286,12 +16166,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>S5000</t>
+          <t>S5001</t>
         </is>
       </c>
       <c r="E39"/>
@@ -15300,7 +16180,7 @@
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" s="1" t="n">
-        <v>67.69</v>
+        <v>682.5</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -15351,7 +16231,7 @@
       <c r="AI39"/>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>00338004938</t>
+          <t>00003161201</t>
         </is>
       </c>
       <c r="AK39" t="n">
@@ -15467,7 +16347,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -15477,7 +16357,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -15491,7 +16371,7 @@
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" s="1" t="n">
-        <v>57.12</v>
+        <v>15.12</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -15542,7 +16422,7 @@
       <c r="AI40"/>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>08290326810</t>
+          <t>63323025510</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -15555,7 +16435,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2530002</t>
+          <t>2530001</t>
         </is>
       </c>
       <c r="AN40"/>
@@ -15658,7 +16538,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -15668,7 +16548,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -15682,7 +16562,7 @@
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" s="1" t="n">
-        <v>10.5</v>
+        <v>67.69</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -15733,7 +16613,7 @@
       <c r="AI41"/>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>829080357005</t>
+          <t>00338004938</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -15746,7 +16626,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2530003</t>
+          <t>2530001</t>
         </is>
       </c>
       <c r="AN41"/>
@@ -15849,47 +16729,31 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>36463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>99299</t>
+          <t>S5000</t>
         </is>
       </c>
       <c r="E42"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
       <c r="J42" s="1" t="n">
-        <v>40.0</v>
+        <v>57.12</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -15897,104 +16761,54 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O42" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P42" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P42"/>
       <c r="Q42"/>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42"/>
       <c r="V42" s="4" t="n">
-        <v>38425.0</v>
+        <v>38018.0</v>
       </c>
       <c r="W42" s="4" t="n">
-        <v>38436.0</v>
+        <v>38024.0</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="Y42" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="AA42" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
+        <v>38016.0</v>
+      </c>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
+      <c r="AB42"/>
       <c r="AC42"/>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuthorization</t>
-        </is>
-      </c>
-      <c r="AE42" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNumber</t>
-        </is>
-      </c>
-      <c r="AF42" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="AG42" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
-        </is>
-      </c>
-      <c r="AI42" s="3" t="inlineStr">
-        <is>
-          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
-        </is>
-      </c>
+      <c r="AD42"/>
+      <c r="AE42"/>
+      <c r="AF42"/>
+      <c r="AG42"/>
+      <c r="AH42"/>
+      <c r="AI42"/>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>00002143481</t>
+          <t>08290326810</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>1.01</v>
+        <v>14.0</v>
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
@@ -16003,78 +16817,30 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>Line123</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
+          <t>2530002</t>
+        </is>
+      </c>
+      <c r="AN42"/>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
       <c r="AS42"/>
       <c r="AT42"/>
       <c r="AU42"/>
       <c r="AV42"/>
-      <c r="AW42" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>DOE LINE</t>
-        </is>
-      </c>
-      <c r="AY42" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="AZ42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="AW42"/>
+      <c r="AX42"/>
+      <c r="AY42"/>
+      <c r="AZ42"/>
       <c r="BA42"/>
       <c r="BB42"/>
       <c r="BC42"/>
       <c r="BD42"/>
       <c r="BE42"/>
-      <c r="BF42" s="3" t="inlineStr">
-        <is>
-          <t>1234567809</t>
-        </is>
-      </c>
-      <c r="BG42" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BH42" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="BF42"/>
+      <c r="BG42"/>
+      <c r="BH42"/>
       <c r="BI42"/>
       <c r="BJ42"/>
       <c r="BK42"/>
@@ -16093,36 +16859,12 @@
       <c r="BX42"/>
       <c r="BY42"/>
       <c r="BZ42"/>
-      <c r="CA42" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="CB42" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="CC42" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="CD42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CE42" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="CF42" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="CA42"/>
+      <c r="CB42"/>
+      <c r="CC42"/>
+      <c r="CD42"/>
+      <c r="CE42"/>
+      <c r="CF42"/>
       <c r="CG42"/>
       <c r="CH42"/>
       <c r="CI42"/>
@@ -16133,9 +16875,21 @@
       <c r="CN42"/>
       <c r="CO42"/>
       <c r="CP42"/>
-      <c r="CQ42"/>
-      <c r="CR42"/>
-      <c r="CS42"/>
+      <c r="CQ42" s="3" t="inlineStr">
+        <is>
+          <t>1112223338</t>
+        </is>
+      </c>
+      <c r="CR42" s="3" t="inlineStr">
+        <is>
+          <t>Welby</t>
+        </is>
+      </c>
+      <c r="CS42" s="3" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
       <c r="CT42"/>
       <c r="CU42"/>
       <c r="CV42"/>
@@ -16166,22 +16920,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69e82c68836d7d05c9a0420f</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>36463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>S5000</t>
         </is>
       </c>
       <c r="E43"/>
@@ -16190,7 +16944,7 @@
       <c r="H43"/>
       <c r="I43"/>
       <c r="J43" s="1" t="n">
-        <v>15.0</v>
+        <v>10.5</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -16198,10 +16952,18 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M43"/>
-      <c r="N43"/>
+        <v>7.0</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n">
         <v>1.0</v>
       </c>
@@ -16212,12 +16974,14 @@
       <c r="T43"/>
       <c r="U43"/>
       <c r="V43" s="4" t="n">
-        <v>38993.0</v>
+        <v>38018.0</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>38993.0</v>
-      </c>
-      <c r="X43"/>
+        <v>38024.0</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>38016.0</v>
+      </c>
       <c r="Y43"/>
       <c r="Z43"/>
       <c r="AA43"/>
@@ -16229,10 +16993,24 @@
       <c r="AG43"/>
       <c r="AH43"/>
       <c r="AI43"/>
-      <c r="AJ43"/>
-      <c r="AK43"/>
-      <c r="AL43"/>
-      <c r="AM43"/>
+      <c r="AJ43" s="3" t="inlineStr">
+        <is>
+          <t>829080357005</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2530003</t>
+        </is>
+      </c>
       <c r="AN43"/>
       <c r="AO43"/>
       <c r="AP43"/>
@@ -16288,9 +17066,21 @@
       <c r="CN43"/>
       <c r="CO43"/>
       <c r="CP43"/>
-      <c r="CQ43"/>
-      <c r="CR43"/>
-      <c r="CS43"/>
+      <c r="CQ43" s="3" t="inlineStr">
+        <is>
+          <t>1112223338</t>
+        </is>
+      </c>
+      <c r="CR43" s="3" t="inlineStr">
+        <is>
+          <t>Welby</t>
+        </is>
+      </c>
+      <c r="CS43" s="3" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
       <c r="CT43"/>
       <c r="CU43"/>
       <c r="CV43"/>
@@ -16321,7 +17111,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69e82c68836d7d05c9a042cd</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -16331,21 +17121,37 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>99299</t>
         </is>
       </c>
       <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
-      <c r="I44"/>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="J44" s="1" t="n">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -16355,60 +17161,182 @@
       <c r="L44" t="n">
         <v>1.0</v>
       </c>
-      <c r="M44"/>
-      <c r="N44"/>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="P44" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="P44"/>
       <c r="Q44"/>
-      <c r="R44"/>
-      <c r="S44"/>
-      <c r="T44"/>
-      <c r="U44"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V44" s="4" t="n">
-        <v>39000.0</v>
+        <v>38425.0</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="X44"/>
-      <c r="Y44"/>
-      <c r="Z44"/>
-      <c r="AA44"/>
-      <c r="AB44"/>
+        <v>38436.0</v>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="Z44" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="AA44" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="AB44" s="4" t="n">
+        <v>38360.0</v>
+      </c>
       <c r="AC44"/>
-      <c r="AD44"/>
-      <c r="AE44"/>
-      <c r="AF44"/>
-      <c r="AG44"/>
-      <c r="AH44"/>
-      <c r="AI44"/>
-      <c r="AJ44"/>
-      <c r="AK44"/>
-      <c r="AL44"/>
-      <c r="AM44"/>
-      <c r="AN44"/>
-      <c r="AO44"/>
-      <c r="AP44"/>
-      <c r="AQ44"/>
-      <c r="AR44"/>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuthorization</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNumber</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr">
+        <is>
+          <t>00002143481</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>Line123</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="AS44"/>
       <c r="AT44"/>
       <c r="AU44"/>
       <c r="AV44"/>
-      <c r="AW44"/>
-      <c r="AX44"/>
-      <c r="AY44"/>
-      <c r="AZ44"/>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>DOE LINE</t>
+        </is>
+      </c>
+      <c r="AY44" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="AZ44" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="BA44"/>
       <c r="BB44"/>
       <c r="BC44"/>
       <c r="BD44"/>
       <c r="BE44"/>
-      <c r="BF44"/>
-      <c r="BG44"/>
-      <c r="BH44"/>
+      <c r="BF44" s="3" t="inlineStr">
+        <is>
+          <t>1234567809</t>
+        </is>
+      </c>
+      <c r="BG44" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BH44" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="BI44"/>
       <c r="BJ44"/>
       <c r="BK44"/>
@@ -16427,12 +17355,36 @@
       <c r="BX44"/>
       <c r="BY44"/>
       <c r="BZ44"/>
-      <c r="CA44"/>
-      <c r="CB44"/>
-      <c r="CC44"/>
-      <c r="CD44"/>
-      <c r="CE44"/>
-      <c r="CF44"/>
+      <c r="CA44" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="CB44" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="CC44" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="CD44" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CE44" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="CF44" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="CG44"/>
       <c r="CH44"/>
       <c r="CI44"/>
@@ -16476,7 +17428,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69e82c68836d7d05c9a042cd</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -16486,12 +17438,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="E45"/>
@@ -16500,7 +17452,7 @@
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" s="1" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -16513,7 +17465,7 @@
       <c r="M45"/>
       <c r="N45"/>
       <c r="O45" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P45"/>
       <c r="Q45"/>
@@ -16522,10 +17474,10 @@
       <c r="T45"/>
       <c r="U45"/>
       <c r="V45" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X45"/>
       <c r="Y45"/>
@@ -16539,11 +17491,7 @@
       <c r="AG45"/>
       <c r="AH45"/>
       <c r="AI45"/>
-      <c r="AJ45" s="3" t="inlineStr">
-        <is>
-          <t>01234567891</t>
-        </is>
-      </c>
+      <c r="AJ45"/>
       <c r="AK45"/>
       <c r="AL45"/>
       <c r="AM45"/>
@@ -16632,6 +17580,326 @@
       <c r="DR45"/>
       <c r="DS45"/>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>69e82c68836d7d05c9a042cd</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>36463774</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>99214</t>
+        </is>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46" s="1" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46" s="4" t="n">
+        <v>38993.0</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>38993.0</v>
+      </c>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
+      <c r="AJ46"/>
+      <c r="AK46"/>
+      <c r="AL46"/>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
+      <c r="AS46"/>
+      <c r="AT46"/>
+      <c r="AU46"/>
+      <c r="AV46"/>
+      <c r="AW46"/>
+      <c r="AX46"/>
+      <c r="AY46"/>
+      <c r="AZ46"/>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46"/>
+      <c r="BD46"/>
+      <c r="BE46"/>
+      <c r="BF46"/>
+      <c r="BG46"/>
+      <c r="BH46"/>
+      <c r="BI46"/>
+      <c r="BJ46"/>
+      <c r="BK46"/>
+      <c r="BL46"/>
+      <c r="BM46"/>
+      <c r="BN46"/>
+      <c r="BO46"/>
+      <c r="BP46"/>
+      <c r="BQ46"/>
+      <c r="BR46"/>
+      <c r="BS46"/>
+      <c r="BT46"/>
+      <c r="BU46"/>
+      <c r="BV46"/>
+      <c r="BW46"/>
+      <c r="BX46"/>
+      <c r="BY46"/>
+      <c r="BZ46"/>
+      <c r="CA46"/>
+      <c r="CB46"/>
+      <c r="CC46"/>
+      <c r="CD46"/>
+      <c r="CE46"/>
+      <c r="CF46"/>
+      <c r="CG46"/>
+      <c r="CH46"/>
+      <c r="CI46"/>
+      <c r="CJ46"/>
+      <c r="CK46"/>
+      <c r="CL46"/>
+      <c r="CM46"/>
+      <c r="CN46"/>
+      <c r="CO46"/>
+      <c r="CP46"/>
+      <c r="CQ46"/>
+      <c r="CR46"/>
+      <c r="CS46"/>
+      <c r="CT46"/>
+      <c r="CU46"/>
+      <c r="CV46"/>
+      <c r="CW46"/>
+      <c r="CX46"/>
+      <c r="CY46"/>
+      <c r="CZ46"/>
+      <c r="DA46"/>
+      <c r="DB46"/>
+      <c r="DC46"/>
+      <c r="DD46"/>
+      <c r="DE46"/>
+      <c r="DF46"/>
+      <c r="DG46"/>
+      <c r="DH46"/>
+      <c r="DI46"/>
+      <c r="DJ46"/>
+      <c r="DK46"/>
+      <c r="DL46"/>
+      <c r="DM46"/>
+      <c r="DN46"/>
+      <c r="DO46"/>
+      <c r="DP46"/>
+      <c r="DQ46"/>
+      <c r="DR46"/>
+      <c r="DS46"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>69e82c68836d7d05c9a042cd</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>36463774</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>86663</t>
+        </is>
+      </c>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="I47"/>
+      <c r="J47" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47"/>
+      <c r="U47"/>
+      <c r="V47" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="W47" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="X47"/>
+      <c r="Y47"/>
+      <c r="Z47"/>
+      <c r="AA47"/>
+      <c r="AB47"/>
+      <c r="AC47"/>
+      <c r="AD47"/>
+      <c r="AE47"/>
+      <c r="AF47"/>
+      <c r="AG47"/>
+      <c r="AH47"/>
+      <c r="AI47"/>
+      <c r="AJ47" s="3" t="inlineStr">
+        <is>
+          <t>01234567891</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM47"/>
+      <c r="AN47"/>
+      <c r="AO47"/>
+      <c r="AP47"/>
+      <c r="AQ47"/>
+      <c r="AR47"/>
+      <c r="AS47"/>
+      <c r="AT47"/>
+      <c r="AU47"/>
+      <c r="AV47"/>
+      <c r="AW47"/>
+      <c r="AX47"/>
+      <c r="AY47"/>
+      <c r="AZ47"/>
+      <c r="BA47"/>
+      <c r="BB47"/>
+      <c r="BC47"/>
+      <c r="BD47"/>
+      <c r="BE47"/>
+      <c r="BF47"/>
+      <c r="BG47"/>
+      <c r="BH47"/>
+      <c r="BI47"/>
+      <c r="BJ47"/>
+      <c r="BK47"/>
+      <c r="BL47"/>
+      <c r="BM47"/>
+      <c r="BN47"/>
+      <c r="BO47"/>
+      <c r="BP47"/>
+      <c r="BQ47"/>
+      <c r="BR47"/>
+      <c r="BS47"/>
+      <c r="BT47"/>
+      <c r="BU47"/>
+      <c r="BV47"/>
+      <c r="BW47"/>
+      <c r="BX47"/>
+      <c r="BY47"/>
+      <c r="BZ47"/>
+      <c r="CA47"/>
+      <c r="CB47"/>
+      <c r="CC47"/>
+      <c r="CD47"/>
+      <c r="CE47"/>
+      <c r="CF47"/>
+      <c r="CG47"/>
+      <c r="CH47"/>
+      <c r="CI47"/>
+      <c r="CJ47"/>
+      <c r="CK47"/>
+      <c r="CL47"/>
+      <c r="CM47"/>
+      <c r="CN47"/>
+      <c r="CO47"/>
+      <c r="CP47"/>
+      <c r="CQ47"/>
+      <c r="CR47"/>
+      <c r="CS47"/>
+      <c r="CT47"/>
+      <c r="CU47"/>
+      <c r="CV47"/>
+      <c r="CW47"/>
+      <c r="CX47"/>
+      <c r="CY47"/>
+      <c r="CZ47"/>
+      <c r="DA47"/>
+      <c r="DB47"/>
+      <c r="DC47"/>
+      <c r="DD47"/>
+      <c r="DE47"/>
+      <c r="DF47"/>
+      <c r="DG47"/>
+      <c r="DH47"/>
+      <c r="DI47"/>
+      <c r="DJ47"/>
+      <c r="DK47"/>
+      <c r="DL47"/>
+      <c r="DM47"/>
+      <c r="DN47"/>
+      <c r="DO47"/>
+      <c r="DP47"/>
+      <c r="DQ47"/>
+      <c r="DR47"/>
+      <c r="DS47"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:HX16"/>
+  <dimension ref="A1:HX17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69efef05ad4799caa7f5cc98</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69efef05ad4799caa7f5ccc9</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4177</t>
+          <t>69efef05ad4799caa7f5ccf3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69efef05ad4799caa7f5cd3c</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69efef05ad4799caa7f5cd74</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>commercial.dat</t>
+          <t>837P-X298-all-fields.dat</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2006-10-15T10:23:00</t>
+          <t>2012-03-15T10:23:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>CHARGEABLE</t>
+          <t>REPORTING</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -3231,26 +3231,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
       <c r="R6"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -3269,7 +3253,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>Ben Kildare Service</t>
+          <t>PHYSICIAN CLINIC</t>
         </is>
       </c>
       <c r="W6"/>
@@ -3297,7 +3281,7 @@
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>103G00000X</t>
+          <t>207Q00000X</t>
         </is>
       </c>
       <c r="AE6"/>
@@ -3316,21 +3300,13 @@
       <c r="AR6"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY</t>
+          <t>UNCONFIRMED</t>
         </is>
       </c>
       <c r="AT6"/>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="AU6"/>
       <c r="AV6"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
+      <c r="AW6"/>
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -3344,12 +3320,12 @@
       <c r="AZ6"/>
       <c r="BA6" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>JANE</t>
         </is>
       </c>
       <c r="BC6"/>
@@ -3361,45 +3337,41 @@
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF6"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="BG6"/>
-      <c r="BH6"/>
-      <c r="BI6"/>
-      <c r="BJ6"/>
+      <c r="BH6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="BK6"/>
       <c r="BL6"/>
       <c r="BM6"/>
-      <c r="BN6" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="BO6" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
+      <c r="BN6"/>
+      <c r="BO6"/>
       <c r="BP6"/>
-      <c r="BQ6" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
+      <c r="BQ6"/>
       <c r="BR6"/>
       <c r="BS6"/>
       <c r="BT6"/>
       <c r="BU6"/>
       <c r="BV6"/>
-      <c r="BW6" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX6" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW6"/>
+      <c r="BX6"/>
       <c r="BY6"/>
       <c r="BZ6"/>
       <c r="CA6" s="3" t="inlineStr">
@@ -3409,12 +3381,12 @@
       </c>
       <c r="CB6" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="CD6"/>
@@ -3451,10 +3423,10 @@
       <c r="CM6"/>
       <c r="CN6"/>
       <c r="CO6" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="CP6" s="4" t="n">
-        <v>39000.0</v>
+        <v>40943.0</v>
       </c>
       <c r="CQ6"/>
       <c r="CR6"/>
@@ -3472,12 +3444,12 @@
       <c r="DD6"/>
       <c r="DE6"/>
       <c r="DF6"/>
-      <c r="DG6"/>
-      <c r="DH6" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DG6" s="3" t="inlineStr">
+        <is>
+          <t>20121092600001</t>
+        </is>
+      </c>
+      <c r="DH6"/>
       <c r="DI6"/>
       <c r="DJ6"/>
       <c r="DK6"/>
@@ -3485,12 +3457,12 @@
       <c r="DM6"/>
       <c r="DN6" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
+          <t>M25375</t>
         </is>
       </c>
       <c r="DO6" s="3" t="inlineStr">
         <is>
-          <t>Z1159</t>
+          <t>M19072</t>
         </is>
       </c>
       <c r="DP6"/>
@@ -3517,22 +3489,58 @@
       <c r="EK6"/>
       <c r="EL6"/>
       <c r="EM6"/>
-      <c r="EN6"/>
-      <c r="EO6"/>
-      <c r="EP6"/>
+      <c r="EN6" s="3" t="inlineStr">
+        <is>
+          <t>1234567890</t>
+        </is>
+      </c>
+      <c r="EO6" s="3" t="inlineStr">
+        <is>
+          <t>JONES</t>
+        </is>
+      </c>
+      <c r="EP6" s="3" t="inlineStr">
+        <is>
+          <t>BARNABY</t>
+        </is>
+      </c>
       <c r="EQ6"/>
       <c r="ER6"/>
       <c r="ES6"/>
       <c r="ET6"/>
       <c r="EU6"/>
       <c r="EV6"/>
-      <c r="EW6"/>
-      <c r="EX6"/>
-      <c r="EY6"/>
+      <c r="EW6" s="3" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="EX6" s="3" t="inlineStr">
+        <is>
+          <t>PHYSICIAN CLINIC</t>
+        </is>
+      </c>
+      <c r="EY6" s="3" t="inlineStr">
+        <is>
+          <t>234 SEAWAY ST</t>
+        </is>
+      </c>
       <c r="EZ6"/>
-      <c r="FA6"/>
-      <c r="FB6"/>
-      <c r="FC6"/>
+      <c r="FA6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC6" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD6"/>
       <c r="FE6"/>
       <c r="FF6"/>
@@ -3561,22 +3569,70 @@
       <c r="GC6"/>
       <c r="GD6"/>
       <c r="GE6"/>
-      <c r="GF6"/>
-      <c r="GG6"/>
-      <c r="GH6"/>
+      <c r="GF6" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="GG6" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="GH6" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="GI6"/>
-      <c r="GJ6"/>
-      <c r="GK6"/>
-      <c r="GL6"/>
+      <c r="GJ6" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="GK6" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL6" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223333</t>
+        </is>
+      </c>
       <c r="GM6"/>
-      <c r="GN6"/>
-      <c r="GO6"/>
+      <c r="GN6" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO6" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
       <c r="GP6"/>
-      <c r="GQ6"/>
+      <c r="GQ6" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR6"/>
-      <c r="GS6"/>
-      <c r="GT6"/>
-      <c r="GU6"/>
+      <c r="GS6" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT6" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU6" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="GV6"/>
       <c r="GW6"/>
       <c r="GX6"/>
@@ -3589,14 +3645,32 @@
       <c r="HE6"/>
       <c r="HF6"/>
       <c r="HG6"/>
-      <c r="HH6"/>
+      <c r="HH6" s="1" t="n">
+        <v>75.0</v>
+      </c>
       <c r="HI6"/>
       <c r="HJ6"/>
-      <c r="HK6"/>
-      <c r="HL6"/>
-      <c r="HM6"/>
+      <c r="HK6" s="3" t="inlineStr">
+        <is>
+          <t>20121092600001</t>
+        </is>
+      </c>
+      <c r="HL6" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM6" s="3" t="inlineStr">
+        <is>
+          <t>59999</t>
+        </is>
+      </c>
       <c r="HN6"/>
-      <c r="HO6"/>
+      <c r="HO6" s="3" t="inlineStr">
+        <is>
+          <t>ABC PLAN</t>
+        </is>
+      </c>
       <c r="HP6"/>
       <c r="HQ6"/>
       <c r="HR6"/>
@@ -3610,7 +3684,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69efef05ad4799caa7f5cdaa</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3620,7 +3694,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>multi-tran.dat</t>
+          <t>commercial.dat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3635,7 +3709,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3645,12 +3719,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>REPORTING</t>
+          <t>CHARGEABLE</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
@@ -3709,7 +3783,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>Ben Kildare Service</t>
         </is>
       </c>
       <c r="W7"/>
@@ -3737,7 +3811,7 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>103GC0700X</t>
+          <t>103G00000X</t>
         </is>
       </c>
       <c r="AE7"/>
@@ -3759,20 +3833,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
+      <c r="AT7"/>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>12312-A</t>
+          <t>2222-SJ</t>
         </is>
       </c>
       <c r="AV7"/>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>HM</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -3782,18 +3852,18 @@
       </c>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>00221111</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ7"/>
       <c r="BA7" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="BC7"/>
@@ -3802,18 +3872,14 @@
       </c>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF7"/>
       <c r="BG7"/>
       <c r="BH7" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>MAIMI</t>
         </is>
       </c>
       <c r="BI7" s="3" t="inlineStr">
@@ -3823,7 +3889,7 @@
       </c>
       <c r="BJ7" s="3" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="BK7"/>
@@ -3836,35 +3902,89 @@
       </c>
       <c r="BO7" s="3" t="inlineStr">
         <is>
-          <t>741234</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="3" t="inlineStr">
         <is>
-          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
+          <t>KEY INSURANCE COMPANY</t>
         </is>
       </c>
       <c r="BR7"/>
       <c r="BS7"/>
-      <c r="BT7"/>
-      <c r="BU7"/>
-      <c r="BV7"/>
-      <c r="BW7"/>
-      <c r="BX7"/>
+      <c r="BT7" s="3" t="inlineStr">
+        <is>
+          <t>MAIMI</t>
+        </is>
+      </c>
+      <c r="BU7" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV7" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="BW7" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX7" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY7"/>
       <c r="BZ7"/>
-      <c r="CA7"/>
-      <c r="CB7"/>
-      <c r="CC7"/>
+      <c r="CA7" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB7" s="3" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="CC7" s="3" t="inlineStr">
+        <is>
+          <t>Ted</t>
+        </is>
+      </c>
       <c r="CD7"/>
-      <c r="CE7"/>
-      <c r="CF7"/>
-      <c r="CG7"/>
+      <c r="CE7" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF7" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG7" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH7"/>
-      <c r="CI7"/>
-      <c r="CJ7"/>
-      <c r="CK7"/>
+      <c r="CI7" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ7" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK7" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL7"/>
       <c r="CM7"/>
       <c r="CN7"/>
@@ -3874,9 +3994,7 @@
       <c r="CP7" s="4" t="n">
         <v>39000.0</v>
       </c>
-      <c r="CQ7" s="4" t="n">
-        <v>36071.0</v>
-      </c>
+      <c r="CQ7"/>
       <c r="CR7"/>
       <c r="CS7"/>
       <c r="CT7"/>
@@ -3905,7 +4023,7 @@
       <c r="DM7"/>
       <c r="DN7" s="3" t="inlineStr">
         <is>
-          <t>G35</t>
+          <t>J020</t>
         </is>
       </c>
       <c r="DO7" s="3" t="inlineStr">
@@ -3946,37 +4064,13 @@
       <c r="ET7"/>
       <c r="EU7"/>
       <c r="EV7"/>
-      <c r="EW7" s="3" t="inlineStr">
-        <is>
-          <t>5812345679</t>
-        </is>
-      </c>
-      <c r="EX7" s="3" t="inlineStr">
-        <is>
-          <t>KILDARE ASSOCIATES</t>
-        </is>
-      </c>
-      <c r="EY7" s="3" t="inlineStr">
-        <is>
-          <t>2345 OCEAN BLVD</t>
-        </is>
-      </c>
+      <c r="EW7"/>
+      <c r="EX7"/>
+      <c r="EY7"/>
       <c r="EZ7"/>
-      <c r="FA7" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="FB7" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="FC7" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="FA7"/>
+      <c r="FB7"/>
+      <c r="FC7"/>
       <c r="FD7"/>
       <c r="FE7"/>
       <c r="FF7"/>
@@ -4054,7 +4148,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4267</t>
+          <t>69efef05ad4799caa7f5ce21</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4069,7 +4163,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4079,26 +4173,26 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>007227</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2005-02-15T07:54:20</t>
+          <t>2006-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>CHARGEABLE</t>
+          <t>REPORTING</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>145.5</v>
+        <v>100.0</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -4132,7 +4226,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R8"/>
@@ -4143,66 +4237,50 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>GREENE</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>BEN KILDARE SERVICE</t>
+        </is>
+      </c>
+      <c r="W8"/>
+      <c r="X8"/>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>1264 OAKWOOD AVE</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z8"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>21236</t>
-        </is>
-      </c>
-      <c r="AD8"/>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG8" s="3" t="inlineStr">
-        <is>
-          <t>4105551212</t>
-        </is>
-      </c>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>103GC0700X</t>
+        </is>
+      </c>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
       <c r="AH8"/>
       <c r="AI8"/>
       <c r="AJ8"/>
@@ -4224,11 +4302,15 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU8"/>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>12312-A</t>
+        </is>
+      </c>
       <c r="AV8"/>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>HM</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -4238,27 +4320,23 @@
       </c>
       <c r="AY8" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>00221111</t>
         </is>
       </c>
       <c r="AZ8"/>
       <c r="BA8" s="3" t="inlineStr">
         <is>
-          <t>WILLIAMSON</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>MATTHEW</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="BC8"/>
       <c r="BD8" s="4" t="n">
-        <v>9142.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE8" s="3" t="inlineStr">
         <is>
@@ -4267,23 +4345,23 @@
       </c>
       <c r="BF8" s="3" t="inlineStr">
         <is>
-          <t>128 BROADCREEK</t>
+          <t>236 N MAIN ST</t>
         </is>
       </c>
       <c r="BG8"/>
       <c r="BH8" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="BI8" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="BJ8" s="3" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="BK8"/>
@@ -4296,13 +4374,13 @@
       </c>
       <c r="BO8" s="3" t="inlineStr">
         <is>
-          <t>C12345</t>
+          <t>741234</t>
         </is>
       </c>
       <c r="BP8"/>
       <c r="BQ8" s="3" t="inlineStr">
         <is>
-          <t>MEDICARE PART B MARYLAND</t>
+          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
         </is>
       </c>
       <c r="BR8"/>
@@ -4329,24 +4407,20 @@
       <c r="CM8"/>
       <c r="CN8"/>
       <c r="CO8" s="4" t="n">
-        <v>38398.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP8" s="4" t="n">
-        <v>38398.0</v>
-      </c>
-      <c r="CQ8"/>
-      <c r="CR8" s="4" t="n">
-        <v>38367.0</v>
-      </c>
+        <v>39000.0</v>
+      </c>
+      <c r="CQ8" s="4" t="n">
+        <v>36071.0</v>
+      </c>
+      <c r="CR8"/>
       <c r="CS8"/>
-      <c r="CT8" s="4" t="n">
-        <v>38362.0</v>
-      </c>
+      <c r="CT8"/>
       <c r="CU8"/>
       <c r="CV8"/>
-      <c r="CW8" s="4" t="n">
-        <v>38365.0</v>
-      </c>
+      <c r="CW8"/>
       <c r="CX8"/>
       <c r="CY8"/>
       <c r="CZ8"/>
@@ -4357,7 +4431,11 @@
       <c r="DE8"/>
       <c r="DF8"/>
       <c r="DG8"/>
-      <c r="DH8"/>
+      <c r="DH8" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI8"/>
       <c r="DJ8"/>
       <c r="DK8"/>
@@ -4365,10 +4443,14 @@
       <c r="DM8"/>
       <c r="DN8" s="3" t="inlineStr">
         <is>
-          <t>M4820</t>
-        </is>
-      </c>
-      <c r="DO8"/>
+          <t>G35</t>
+        </is>
+      </c>
+      <c r="DO8" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP8"/>
       <c r="DQ8"/>
       <c r="DR8"/>
@@ -4402,13 +4484,37 @@
       <c r="ET8"/>
       <c r="EU8"/>
       <c r="EV8"/>
-      <c r="EW8"/>
-      <c r="EX8"/>
-      <c r="EY8"/>
+      <c r="EW8" s="3" t="inlineStr">
+        <is>
+          <t>5812345679</t>
+        </is>
+      </c>
+      <c r="EX8" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="EY8" s="3" t="inlineStr">
+        <is>
+          <t>2345 OCEAN BLVD</t>
+        </is>
+      </c>
       <c r="EZ8"/>
-      <c r="FA8"/>
-      <c r="FB8"/>
-      <c r="FC8"/>
+      <c r="FA8" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB8" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC8" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD8"/>
       <c r="FE8"/>
       <c r="FF8"/>
@@ -4486,7 +4592,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69efef05ad4799caa7f5ce22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4501,7 +4607,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4511,12 +4617,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>007227</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2005-02-15T07:54:20</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -4526,20 +4632,20 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>827.0</v>
+        <v>145.5</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4575,46 +4681,66 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
-        </is>
-      </c>
-      <c r="W9"/>
-      <c r="X9"/>
+          <t>GREENE</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>1264 OAKWOOD AVE</t>
         </is>
       </c>
       <c r="Z9"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="AD9"/>
-      <c r="AE9"/>
-      <c r="AF9"/>
-      <c r="AG9"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>4105551212</t>
+        </is>
+      </c>
       <c r="AH9"/>
       <c r="AI9"/>
       <c r="AJ9"/>
@@ -4656,42 +4782,46 @@
       <c r="AZ9"/>
       <c r="BA9" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>WILLIAMSON</t>
         </is>
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
-        </is>
-      </c>
-      <c r="BC9"/>
+          <t>MATTHEW</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="BD9" s="4" t="n">
-        <v>27091.0</v>
+        <v>9142.0</v>
       </c>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF9" s="3" t="inlineStr">
         <is>
-          <t>123 RAINBOW ROAD</t>
+          <t>128 BROADCREEK</t>
         </is>
       </c>
       <c r="BG9"/>
       <c r="BH9" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="BI9" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="BJ9" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="BK9"/>
@@ -4704,13 +4834,13 @@
       </c>
       <c r="BO9" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>C12345</t>
         </is>
       </c>
       <c r="BP9"/>
       <c r="BQ9" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>MEDICARE PART B MARYLAND</t>
         </is>
       </c>
       <c r="BR9"/>
@@ -4737,18 +4867,24 @@
       <c r="CM9"/>
       <c r="CN9"/>
       <c r="CO9" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="CP9" s="4" t="n">
-        <v>38365.0</v>
+        <v>38398.0</v>
       </c>
       <c r="CQ9"/>
-      <c r="CR9"/>
+      <c r="CR9" s="4" t="n">
+        <v>38367.0</v>
+      </c>
       <c r="CS9"/>
-      <c r="CT9"/>
+      <c r="CT9" s="4" t="n">
+        <v>38362.0</v>
+      </c>
       <c r="CU9"/>
       <c r="CV9"/>
-      <c r="CW9"/>
+      <c r="CW9" s="4" t="n">
+        <v>38365.0</v>
+      </c>
       <c r="CX9"/>
       <c r="CY9"/>
       <c r="CZ9"/>
@@ -4767,7 +4903,7 @@
       <c r="DM9"/>
       <c r="DN9" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
+          <t>M4820</t>
         </is>
       </c>
       <c r="DO9"/>
@@ -4795,74 +4931,22 @@
       <c r="EK9"/>
       <c r="EL9"/>
       <c r="EM9"/>
-      <c r="EN9" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO9" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP9" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ9" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER9" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES9" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET9" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN9"/>
+      <c r="EO9"/>
+      <c r="EP9"/>
+      <c r="EQ9"/>
+      <c r="ER9"/>
+      <c r="ES9"/>
+      <c r="ET9"/>
       <c r="EU9"/>
       <c r="EV9"/>
-      <c r="EW9" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX9" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY9" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW9"/>
+      <c r="EX9"/>
+      <c r="EY9"/>
       <c r="EZ9"/>
-      <c r="FA9" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB9" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC9" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA9"/>
+      <c r="FB9"/>
+      <c r="FC9"/>
       <c r="FD9"/>
       <c r="FE9"/>
       <c r="FF9"/>
@@ -4940,7 +5024,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69efef05ad4799caa7f5ce23</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4950,12 +5034,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>commercial-replacement.dat</t>
+          <t>multi-tran.dat</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -4965,12 +5049,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2006-11-15T10:23:00</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -4980,25 +5064,25 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>100.0</v>
+        <v>827.0</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -5018,7 +5102,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R10"/>
@@ -5029,47 +5113,43 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>PROVIDER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="W10"/>
       <c r="X10"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z10"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>103GC0700X</t>
-        </is>
-      </c>
+          <t>37232</t>
+        </is>
+      </c>
+      <c r="AD10"/>
       <c r="AE10"/>
       <c r="AF10"/>
       <c r="AG10"/>
@@ -5089,16 +5169,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT10"/>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU10"/>
       <c r="AV10"/>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -5108,34 +5188,50 @@
       </c>
       <c r="AY10" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ10"/>
       <c r="BA10" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>MARGARET</t>
         </is>
       </c>
       <c r="BC10"/>
       <c r="BD10" s="4" t="n">
-        <v>15827.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF10"/>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>123 RAINBOW ROAD</t>
+        </is>
+      </c>
       <c r="BG10"/>
-      <c r="BH10"/>
-      <c r="BI10"/>
-      <c r="BJ10"/>
+      <c r="BH10" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="BK10"/>
       <c r="BL10"/>
       <c r="BM10"/>
@@ -5146,13 +5242,13 @@
       </c>
       <c r="BO10" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP10"/>
       <c r="BQ10" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCECOMPANY</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR10"/>
@@ -5160,71 +5256,29 @@
       <c r="BT10"/>
       <c r="BU10"/>
       <c r="BV10"/>
-      <c r="BW10" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX10" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW10"/>
+      <c r="BX10"/>
       <c r="BY10"/>
       <c r="BZ10"/>
-      <c r="CA10" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB10" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC10" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA10"/>
+      <c r="CB10"/>
+      <c r="CC10"/>
       <c r="CD10"/>
-      <c r="CE10" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF10" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG10" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE10"/>
+      <c r="CF10"/>
+      <c r="CG10"/>
       <c r="CH10"/>
-      <c r="CI10" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ10" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK10" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI10"/>
+      <c r="CJ10"/>
+      <c r="CK10"/>
       <c r="CL10"/>
       <c r="CM10"/>
       <c r="CN10"/>
       <c r="CO10" s="4" t="n">
-        <v>38993.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP10" s="4" t="n">
-        <v>39000.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ10"/>
       <c r="CR10"/>
@@ -5243,11 +5297,7 @@
       <c r="DE10"/>
       <c r="DF10"/>
       <c r="DG10"/>
-      <c r="DH10" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DH10"/>
       <c r="DI10"/>
       <c r="DJ10"/>
       <c r="DK10"/>
@@ -5255,14 +5305,10 @@
       <c r="DM10"/>
       <c r="DN10" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
-        </is>
-      </c>
-      <c r="DO10" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="DO10"/>
       <c r="DP10"/>
       <c r="DQ10"/>
       <c r="DR10"/>
@@ -5287,22 +5333,74 @@
       <c r="EK10"/>
       <c r="EL10"/>
       <c r="EM10"/>
-      <c r="EN10"/>
-      <c r="EO10"/>
-      <c r="EP10"/>
-      <c r="EQ10"/>
-      <c r="ER10"/>
-      <c r="ES10"/>
-      <c r="ET10"/>
+      <c r="EN10" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO10" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP10" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ10" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER10" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES10" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET10" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU10"/>
       <c r="EV10"/>
-      <c r="EW10"/>
-      <c r="EX10"/>
-      <c r="EY10"/>
+      <c r="EW10" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX10" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY10" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ10"/>
-      <c r="FA10"/>
-      <c r="FB10"/>
-      <c r="FC10"/>
+      <c r="FA10" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB10" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC10" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD10"/>
       <c r="FE10"/>
       <c r="FF10"/>
@@ -5380,7 +5478,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69efef05ad4799caa7f5ce56</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5390,12 +5488,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>anesthesia.dat</t>
+          <t>commercial-replacement.dat</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5405,12 +5503,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2006-11-15T10:23:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5420,25 +5518,25 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>827.0</v>
+        <v>100.0</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -5458,7 +5556,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R11"/>
@@ -5469,43 +5567,47 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
+          <t>BEN KILDARE SERVICE</t>
         </is>
       </c>
       <c r="W11"/>
       <c r="X11"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z11"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
-        </is>
-      </c>
-      <c r="AD11"/>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>103GC0700X</t>
+        </is>
+      </c>
       <c r="AE11"/>
       <c r="AF11"/>
       <c r="AG11"/>
@@ -5525,16 +5627,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU11"/>
+      <c r="AT11"/>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="AV11"/>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -5544,50 +5646,34 @@
       </c>
       <c r="AY11" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ11"/>
       <c r="BA11" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
+          <t>JANE</t>
         </is>
       </c>
       <c r="BC11"/>
       <c r="BD11" s="4" t="n">
-        <v>27091.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>123 RAINBOW ROAD</t>
-        </is>
-      </c>
+      <c r="BF11"/>
       <c r="BG11"/>
-      <c r="BH11" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="BI11" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="BJ11" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
       <c r="BK11"/>
       <c r="BL11"/>
       <c r="BM11"/>
@@ -5598,13 +5684,13 @@
       </c>
       <c r="BO11" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP11"/>
       <c r="BQ11" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>KEY INSURANCECOMPANY</t>
         </is>
       </c>
       <c r="BR11"/>
@@ -5612,29 +5698,71 @@
       <c r="BT11"/>
       <c r="BU11"/>
       <c r="BV11"/>
-      <c r="BW11"/>
-      <c r="BX11"/>
+      <c r="BW11" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX11" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY11"/>
       <c r="BZ11"/>
-      <c r="CA11"/>
-      <c r="CB11"/>
-      <c r="CC11"/>
+      <c r="CA11" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB11" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC11" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD11"/>
-      <c r="CE11"/>
-      <c r="CF11"/>
-      <c r="CG11"/>
+      <c r="CE11" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF11" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG11" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH11"/>
-      <c r="CI11"/>
-      <c r="CJ11"/>
-      <c r="CK11"/>
+      <c r="CI11" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ11" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK11" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL11"/>
       <c r="CM11"/>
       <c r="CN11"/>
       <c r="CO11" s="4" t="n">
-        <v>38364.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP11" s="4" t="n">
-        <v>38365.0</v>
+        <v>39000.0</v>
       </c>
       <c r="CQ11"/>
       <c r="CR11"/>
@@ -5653,7 +5781,11 @@
       <c r="DE11"/>
       <c r="DF11"/>
       <c r="DG11"/>
-      <c r="DH11"/>
+      <c r="DH11" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI11"/>
       <c r="DJ11"/>
       <c r="DK11"/>
@@ -5661,10 +5793,14 @@
       <c r="DM11"/>
       <c r="DN11" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="DO11"/>
+          <t>J020</t>
+        </is>
+      </c>
+      <c r="DO11" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP11"/>
       <c r="DQ11"/>
       <c r="DR11"/>
@@ -5689,74 +5825,22 @@
       <c r="EK11"/>
       <c r="EL11"/>
       <c r="EM11"/>
-      <c r="EN11" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO11" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP11" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ11" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER11" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES11" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET11" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN11"/>
+      <c r="EO11"/>
+      <c r="EP11"/>
+      <c r="EQ11"/>
+      <c r="ER11"/>
+      <c r="ES11"/>
+      <c r="ET11"/>
       <c r="EU11"/>
       <c r="EV11"/>
-      <c r="EW11" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX11" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY11" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW11"/>
+      <c r="EX11"/>
+      <c r="EY11"/>
       <c r="EZ11"/>
-      <c r="FA11" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB11" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC11" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA11"/>
+      <c r="FB11"/>
+      <c r="FC11"/>
       <c r="FD11"/>
       <c r="FE11"/>
       <c r="FF11"/>
@@ -5834,7 +5918,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42f6</t>
+          <t>69efef05ad4799caa7f5ce83</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5844,12 +5928,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>wheelchair.dat</t>
+          <t>anesthesia.dat</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5859,12 +5943,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2005-03-26T10:36:00</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5874,20 +5958,20 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>75.0</v>
+        <v>827.0</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -5923,40 +6007,40 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>7778889999</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>123567989</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>XYZ WHEELCHAIR INC</t>
+          <t>PROVIDER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="W12"/>
       <c r="X12"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>1440 NORTH STREET</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z12"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>LAFAYETTE</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="AD12"/>
@@ -5970,16 +6054,8 @@
       <c r="AL12"/>
       <c r="AM12"/>
       <c r="AN12"/>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>0426960001</t>
-        </is>
-      </c>
+      <c r="AO12"/>
+      <c r="AP12"/>
       <c r="AQ12"/>
       <c r="AR12"/>
       <c r="AS12" s="3" t="inlineStr">
@@ -6006,54 +6082,52 @@
       </c>
       <c r="AY12" s="3" t="inlineStr">
         <is>
-          <t>987654321A</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ12"/>
       <c r="BA12" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>JAMES</t>
+          <t>MARGARET</t>
         </is>
       </c>
       <c r="BC12"/>
       <c r="BD12" s="4" t="n">
-        <v>7602.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE12" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="BF12" s="3" t="inlineStr">
         <is>
-          <t>12 MAIN ST</t>
+          <t>123 RAINBOW ROAD</t>
         </is>
       </c>
       <c r="BG12"/>
       <c r="BH12" s="3" t="inlineStr">
         <is>
-          <t>FRANKFORT</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="BI12" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="BJ12" s="3" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="BK12"/>
-      <c r="BL12" t="n">
-        <v>155.0</v>
-      </c>
+      <c r="BL12"/>
       <c r="BM12"/>
       <c r="BN12" s="3" t="inlineStr">
         <is>
@@ -6062,13 +6136,13 @@
       </c>
       <c r="BO12" s="3" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP12"/>
       <c r="BQ12" s="3" t="inlineStr">
         <is>
-          <t>DMERC CARRIER</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR12"/>
@@ -6095,10 +6169,10 @@
       <c r="CM12"/>
       <c r="CN12"/>
       <c r="CO12" s="4" t="n">
-        <v>38432.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP12" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ12"/>
       <c r="CR12"/>
@@ -6125,14 +6199,10 @@
       <c r="DM12"/>
       <c r="DN12" s="3" t="inlineStr">
         <is>
-          <t>I6789</t>
-        </is>
-      </c>
-      <c r="DO12" s="3" t="inlineStr">
-        <is>
-          <t>G839</t>
-        </is>
-      </c>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="DO12"/>
       <c r="DP12"/>
       <c r="DQ12"/>
       <c r="DR12"/>
@@ -6157,22 +6227,74 @@
       <c r="EK12"/>
       <c r="EL12"/>
       <c r="EM12"/>
-      <c r="EN12"/>
-      <c r="EO12"/>
-      <c r="EP12"/>
-      <c r="EQ12"/>
-      <c r="ER12"/>
-      <c r="ES12"/>
-      <c r="ET12"/>
+      <c r="EN12" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO12" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP12" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ12" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER12" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES12" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET12" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU12"/>
       <c r="EV12"/>
-      <c r="EW12"/>
-      <c r="EX12"/>
-      <c r="EY12"/>
+      <c r="EW12" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX12" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY12" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ12"/>
-      <c r="FA12"/>
-      <c r="FB12"/>
-      <c r="FC12"/>
+      <c r="FA12" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB12" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC12" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD12"/>
       <c r="FE12"/>
       <c r="FF12"/>
@@ -6250,7 +6372,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69efef05ad4799caa7f5cebf</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6260,12 +6382,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ppo-repriced.dat</t>
+          <t>wheelchair.dat</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6275,12 +6397,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2005-06-20T09:46:00</t>
+          <t>2005-03-26T10:36:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -6290,20 +6412,20 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>28.75</v>
+        <v>75.0</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -6339,30 +6461,30 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>7778889999</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>555512345</t>
+          <t>123567989</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>HAPPY DOCTORS GROUP PRACTICE</t>
+          <t>XYZ WHEELCHAIR INC</t>
         </is>
       </c>
       <c r="W13"/>
       <c r="X13"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>P O BOX 123</t>
+          <t>1440 NORTH STREET</t>
         </is>
       </c>
       <c r="Z13"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>FORT WAYNE</t>
+          <t>LAFAYETTE</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
@@ -6372,25 +6494,13 @@
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>462540000</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="AD13"/>
-      <c r="AE13" s="3" t="inlineStr">
-        <is>
-          <t>SUE BILLINGSWORTH</t>
-        </is>
-      </c>
-      <c r="AF13" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG13" s="3" t="inlineStr">
-        <is>
-          <t>8881231234</t>
-        </is>
-      </c>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
       <c r="AH13"/>
       <c r="AI13"/>
       <c r="AJ13"/>
@@ -6398,8 +6508,16 @@
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
-      <c r="AO13"/>
-      <c r="AP13"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>0426960001</t>
+        </is>
+      </c>
       <c r="AQ13"/>
       <c r="AR13"/>
       <c r="AS13" s="3" t="inlineStr">
@@ -6412,15 +6530,11 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>123XYZ</t>
-        </is>
-      </c>
+      <c r="AU13"/>
       <c r="AV13"/>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -6430,42 +6544,38 @@
       </c>
       <c r="AY13" s="3" t="inlineStr">
         <is>
-          <t>00124A089</t>
+          <t>987654321A</t>
         </is>
       </c>
       <c r="AZ13"/>
       <c r="BA13" s="3" t="inlineStr">
         <is>
-          <t>RING</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>DIAMOND</t>
-        </is>
-      </c>
-      <c r="BC13" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>JAMES</t>
+        </is>
+      </c>
+      <c r="BC13"/>
       <c r="BD13" s="4" t="n">
-        <v>14974.0</v>
+        <v>7602.0</v>
       </c>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF13" s="3" t="inlineStr">
         <is>
-          <t>123 EXAMPLE DRIVE</t>
+          <t>12 MAIN ST</t>
         </is>
       </c>
       <c r="BG13"/>
       <c r="BH13" s="3" t="inlineStr">
         <is>
-          <t>INDIANAPOLIS</t>
+          <t>FRANKFORT</t>
         </is>
       </c>
       <c r="BI13" s="3" t="inlineStr">
@@ -6475,11 +6585,13 @@
       </c>
       <c r="BJ13" s="3" t="inlineStr">
         <is>
-          <t>462290000</t>
+          <t>46209</t>
         </is>
       </c>
       <c r="BK13"/>
-      <c r="BL13"/>
+      <c r="BL13" t="n">
+        <v>155.0</v>
+      </c>
       <c r="BM13"/>
       <c r="BN13" s="3" t="inlineStr">
         <is>
@@ -6488,20 +6600,32 @@
       </c>
       <c r="BO13" s="3" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="BP13"/>
       <c r="BQ13" s="3" t="inlineStr">
         <is>
-          <t>EXTRA HEALTHY INSURANCE</t>
+          <t>DMERC CARRIER</t>
         </is>
       </c>
       <c r="BR13"/>
       <c r="BS13"/>
-      <c r="BT13"/>
-      <c r="BU13"/>
-      <c r="BV13"/>
+      <c r="BT13" s="3" t="inlineStr">
+        <is>
+          <t>LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="BU13" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="BV13" s="3" t="inlineStr">
+        <is>
+          <t>47904</t>
+        </is>
+      </c>
       <c r="BW13"/>
       <c r="BX13"/>
       <c r="BY13"/>
@@ -6521,10 +6645,10 @@
       <c r="CM13"/>
       <c r="CN13"/>
       <c r="CO13" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CP13" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CQ13"/>
       <c r="CR13"/>
@@ -6543,28 +6667,20 @@
       <c r="DE13"/>
       <c r="DF13"/>
       <c r="DG13"/>
-      <c r="DH13" s="3" t="inlineStr">
-        <is>
-          <t>061505501749388</t>
-        </is>
-      </c>
-      <c r="DI13" s="3" t="inlineStr">
-        <is>
-          <t>0902352342</t>
-        </is>
-      </c>
+      <c r="DH13"/>
+      <c r="DI13"/>
       <c r="DJ13"/>
       <c r="DK13"/>
       <c r="DL13"/>
       <c r="DM13"/>
       <c r="DN13" s="3" t="inlineStr">
         <is>
-          <t>J449</t>
+          <t>I6789</t>
         </is>
       </c>
       <c r="DO13" s="3" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>G839</t>
         </is>
       </c>
       <c r="DP13"/>
@@ -6583,78 +6699,30 @@
       <c r="EC13"/>
       <c r="ED13"/>
       <c r="EE13"/>
-      <c r="EF13" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="EG13" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH13" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="EF13"/>
+      <c r="EG13"/>
+      <c r="EH13"/>
       <c r="EI13"/>
       <c r="EJ13"/>
       <c r="EK13"/>
       <c r="EL13"/>
       <c r="EM13"/>
-      <c r="EN13" s="3" t="inlineStr">
-        <is>
-          <t>1122334455</t>
-        </is>
-      </c>
-      <c r="EO13" s="3" t="inlineStr">
-        <is>
-          <t>ANTHONY</t>
-        </is>
-      </c>
-      <c r="EP13" s="3" t="inlineStr">
-        <is>
-          <t>SUSAN</t>
-        </is>
-      </c>
-      <c r="EQ13" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+      <c r="EN13"/>
+      <c r="EO13"/>
+      <c r="EP13"/>
+      <c r="EQ13"/>
       <c r="ER13"/>
       <c r="ES13"/>
       <c r="ET13"/>
       <c r="EU13"/>
       <c r="EV13"/>
       <c r="EW13"/>
-      <c r="EX13" s="3" t="inlineStr">
-        <is>
-          <t>HAPPY DOCTORS GROUP</t>
-        </is>
-      </c>
-      <c r="EY13" s="3" t="inlineStr">
-        <is>
-          <t>123 FEEL GOOD ROAD</t>
-        </is>
-      </c>
+      <c r="EX13"/>
+      <c r="EY13"/>
       <c r="EZ13"/>
-      <c r="FA13" s="3" t="inlineStr">
-        <is>
-          <t>WASHINGTON</t>
-        </is>
-      </c>
-      <c r="FB13" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="FC13" s="3" t="inlineStr">
-        <is>
-          <t>475010000</t>
-        </is>
-      </c>
+      <c r="FA13"/>
+      <c r="FB13"/>
+      <c r="FC13"/>
       <c r="FD13"/>
       <c r="FE13"/>
       <c r="FF13"/>
@@ -6732,7 +6800,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69efef05ad4799caa7f5ceef</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6742,12 +6810,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>cob-prov-payera.dat</t>
+          <t>ppo-repriced.dat</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -6757,12 +6825,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2005-10-15T10:23:00</t>
+          <t>2005-06-20T09:46:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6772,11 +6840,11 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>79.04</v>
+        <v>28.75</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -6810,7 +6878,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R14"/>
@@ -6821,50 +6889,46 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1999996666</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>555512345</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
+          <t>HAPPY DOCTORS GROUP PRACTICE</t>
+        </is>
+      </c>
+      <c r="W14"/>
       <c r="X14"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>1234 SEAWAY ST</t>
+          <t>P O BOX 123</t>
         </is>
       </c>
       <c r="Z14"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>FORT WAYNE</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>462540000</t>
         </is>
       </c>
       <c r="AD14"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>CONNIE</t>
+          <t>SUE BILLINGSWORTH</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -6874,7 +6938,7 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>3055551234</t>
+          <t>8881231234</t>
         </is>
       </c>
       <c r="AH14"/>
@@ -6893,10 +6957,22 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT14"/>
-      <c r="AU14"/>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>123XYZ</t>
+        </is>
+      </c>
       <c r="AV14"/>
-      <c r="AW14"/>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
       <c r="AX14" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6904,34 +6980,54 @@
       </c>
       <c r="AY14" s="3" t="inlineStr">
         <is>
-          <t>111223333</t>
+          <t>00124A089</t>
         </is>
       </c>
       <c r="AZ14"/>
       <c r="BA14" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>RING</t>
         </is>
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="BC14"/>
+          <t>DIAMOND</t>
+        </is>
+      </c>
+      <c r="BC14" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="BD14" s="4" t="n">
-        <v>15827.0</v>
+        <v>14974.0</v>
       </c>
       <c r="BE14" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF14"/>
+      <c r="BF14" s="3" t="inlineStr">
+        <is>
+          <t>123 EXAMPLE DRIVE</t>
+        </is>
+      </c>
       <c r="BG14"/>
-      <c r="BH14"/>
-      <c r="BI14"/>
-      <c r="BJ14"/>
+      <c r="BH14" s="3" t="inlineStr">
+        <is>
+          <t>INDIANAPOLIS</t>
+        </is>
+      </c>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="inlineStr">
+        <is>
+          <t>462290000</t>
+        </is>
+      </c>
       <c r="BK14"/>
       <c r="BL14"/>
       <c r="BM14"/>
@@ -6942,101 +7038,43 @@
       </c>
       <c r="BO14" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="BP14"/>
       <c r="BQ14" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
-      <c r="BR14" s="3" t="inlineStr">
-        <is>
-          <t>3333OCEAN ST</t>
-        </is>
-      </c>
+          <t>EXTRA HEALTHY INSURANCE</t>
+        </is>
+      </c>
+      <c r="BR14"/>
       <c r="BS14"/>
-      <c r="BT14" s="3" t="inlineStr">
-        <is>
-          <t>SOUTH MIAMI</t>
-        </is>
-      </c>
-      <c r="BU14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BV14" s="3" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="BW14" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX14" s="3" t="inlineStr">
-        <is>
-          <t>PBS3334</t>
-        </is>
-      </c>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
       <c r="BY14"/>
       <c r="BZ14"/>
-      <c r="CA14" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB14" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC14" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA14"/>
+      <c r="CB14"/>
+      <c r="CC14"/>
       <c r="CD14"/>
-      <c r="CE14" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF14" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG14" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE14"/>
+      <c r="CF14"/>
+      <c r="CG14"/>
       <c r="CH14"/>
-      <c r="CI14" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK14" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI14"/>
+      <c r="CJ14"/>
+      <c r="CK14"/>
       <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14"/>
       <c r="CO14" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CP14" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -7055,27 +7093,31 @@
       <c r="DE14"/>
       <c r="DF14"/>
       <c r="DG14"/>
-      <c r="DH14"/>
-      <c r="DI14"/>
+      <c r="DH14" s="3" t="inlineStr">
+        <is>
+          <t>061505501749388</t>
+        </is>
+      </c>
+      <c r="DI14" s="3" t="inlineStr">
+        <is>
+          <t>0902352342</t>
+        </is>
+      </c>
       <c r="DJ14"/>
       <c r="DK14"/>
       <c r="DL14"/>
       <c r="DM14"/>
       <c r="DN14" s="3" t="inlineStr">
         <is>
-          <t>J309</t>
+          <t>J449</t>
         </is>
       </c>
       <c r="DO14" s="3" t="inlineStr">
         <is>
-          <t>E785</t>
-        </is>
-      </c>
-      <c r="DP14" s="3" t="inlineStr">
-        <is>
-          <t>E663</t>
-        </is>
-      </c>
+          <t>E119</t>
+        </is>
+      </c>
+      <c r="DP14"/>
       <c r="DQ14"/>
       <c r="DR14"/>
       <c r="DS14"/>
@@ -7091,9 +7133,21 @@
       <c r="EC14"/>
       <c r="ED14"/>
       <c r="EE14"/>
-      <c r="EF14"/>
-      <c r="EG14"/>
-      <c r="EH14"/>
+      <c r="EF14" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="EG14" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH14" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="EI14"/>
       <c r="EJ14"/>
       <c r="EK14"/>
@@ -7101,66 +7155,54 @@
       <c r="EM14"/>
       <c r="EN14" s="3" t="inlineStr">
         <is>
-          <t>1999996666</t>
+          <t>1122334455</t>
         </is>
       </c>
       <c r="EO14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE</t>
+          <t>ANTHONY</t>
         </is>
       </c>
       <c r="EP14" s="3" t="inlineStr">
         <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="EQ14"/>
-      <c r="ER14" s="3" t="inlineStr">
-        <is>
-          <t>204C00000X</t>
-        </is>
-      </c>
-      <c r="ES14" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET14" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+          <t>SUSAN</t>
+        </is>
+      </c>
+      <c r="EQ14" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ER14"/>
+      <c r="ES14"/>
+      <c r="ET14"/>
       <c r="EU14"/>
       <c r="EV14"/>
-      <c r="EW14" s="3" t="inlineStr">
-        <is>
-          <t>1581234567</t>
-        </is>
-      </c>
+      <c r="EW14"/>
       <c r="EX14" s="3" t="inlineStr">
         <is>
-          <t>KILDARE ASSOCIATES</t>
+          <t>HAPPY DOCTORS GROUP</t>
         </is>
       </c>
       <c r="EY14" s="3" t="inlineStr">
         <is>
-          <t>2345 OCEAN BLVD</t>
+          <t>123 FEEL GOOD ROAD</t>
         </is>
       </c>
       <c r="EZ14"/>
       <c r="FA14" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>WASHINGTON</t>
         </is>
       </c>
       <c r="FB14" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="FC14" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>475010000</t>
         </is>
       </c>
       <c r="FD14"/>
@@ -7191,66 +7233,22 @@
       <c r="GC14"/>
       <c r="GD14"/>
       <c r="GE14"/>
-      <c r="GF14" s="3" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="GG14" s="3" t="inlineStr">
-        <is>
-          <t>SPOUSE</t>
-        </is>
-      </c>
+      <c r="GF14"/>
+      <c r="GG14"/>
       <c r="GH14"/>
       <c r="GI14"/>
-      <c r="GJ14" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="GK14" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL14" s="3" t="inlineStr">
-        <is>
-          <t>T55TY666</t>
-        </is>
-      </c>
+      <c r="GJ14"/>
+      <c r="GK14"/>
+      <c r="GL14"/>
       <c r="GM14"/>
-      <c r="GN14" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO14" s="3" t="inlineStr">
-        <is>
-          <t>JACK</t>
-        </is>
-      </c>
+      <c r="GN14"/>
+      <c r="GO14"/>
       <c r="GP14"/>
-      <c r="GQ14" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ14"/>
       <c r="GR14"/>
-      <c r="GS14" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT14" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU14" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="GS14"/>
+      <c r="GT14"/>
+      <c r="GU14"/>
       <c r="GV14"/>
       <c r="GW14"/>
       <c r="GX14"/>
@@ -7267,22 +7265,10 @@
       <c r="HI14"/>
       <c r="HJ14"/>
       <c r="HK14"/>
-      <c r="HL14" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM14" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
+      <c r="HL14"/>
+      <c r="HM14"/>
       <c r="HN14"/>
-      <c r="HO14" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
+      <c r="HO14"/>
       <c r="HP14"/>
       <c r="HQ14"/>
       <c r="HR14"/>
@@ -7296,7 +7282,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf2a</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7306,12 +7292,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>home-infusion-ndc.dat</t>
+          <t>cob-prov-payera.dat</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0711</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -7321,12 +7307,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2004-03-01T12:00:00</t>
+          <t>2005-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -7336,20 +7322,20 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>2232.93</v>
+        <v>79.04</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -7374,7 +7360,7 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R15"/>
@@ -7385,46 +7371,50 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>1234567893</t>
+          <t>1999996666</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>10-1234567</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>Professional Home IV, LLC</t>
-        </is>
-      </c>
-      <c r="W15"/>
+          <t>KILDARE</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
       <c r="X15"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>1500 Industrial Drive</t>
+          <t>1234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z15"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>Libertyville</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="AD15"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>Brenda Holly</t>
+          <t>CONNIE</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -7434,7 +7424,7 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>8019999999</t>
+          <t>3055551234</t>
         </is>
       </c>
       <c r="AH15"/>
@@ -7453,22 +7443,10 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>GRP01020102</t>
-        </is>
-      </c>
+      <c r="AT15"/>
+      <c r="AU15"/>
       <c r="AV15"/>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
+      <c r="AW15"/>
       <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -7476,101 +7454,139 @@
       </c>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>MBRID01234</t>
+          <t>111223333</t>
         </is>
       </c>
       <c r="AZ15"/>
       <c r="BA15" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC15"/>
       <c r="BD15" s="4" t="n">
         <v>15827.0</v>
       </c>
       <c r="BE15" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr">
-        <is>
-          <t>15210 Juliet Lane</t>
-        </is>
-      </c>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF15"/>
       <c r="BG15"/>
-      <c r="BH15" s="3" t="inlineStr">
-        <is>
-          <t>Libertyville</t>
-        </is>
-      </c>
-      <c r="BI15" s="3" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="BJ15" s="3" t="inlineStr">
-        <is>
-          <t>60048</t>
-        </is>
-      </c>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
       <c r="BK15"/>
       <c r="BL15"/>
       <c r="BM15"/>
       <c r="BN15" s="3" t="inlineStr">
         <is>
-          <t>CMS_PLAN_ID</t>
+          <t>PAYOR_ID</t>
         </is>
       </c>
       <c r="BO15" s="3" t="inlineStr">
         <is>
-          <t>PLANID12345</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP15"/>
       <c r="BQ15" s="3" t="inlineStr">
         <is>
-          <t>R&amp;R Health Plan</t>
-        </is>
-      </c>
-      <c r="BR15"/>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
+      <c r="BR15" s="3" t="inlineStr">
+        <is>
+          <t>3333OCEAN ST</t>
+        </is>
+      </c>
       <c r="BS15"/>
-      <c r="BT15"/>
-      <c r="BU15"/>
-      <c r="BV15"/>
-      <c r="BW15"/>
-      <c r="BX15"/>
+      <c r="BT15" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH MIAMI</t>
+        </is>
+      </c>
+      <c r="BU15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV15" s="3" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="BW15" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX15" s="3" t="inlineStr">
+        <is>
+          <t>PBS3334</t>
+        </is>
+      </c>
       <c r="BY15"/>
       <c r="BZ15"/>
-      <c r="CA15"/>
-      <c r="CB15"/>
-      <c r="CC15"/>
+      <c r="CA15" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB15" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC15" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD15"/>
-      <c r="CE15"/>
-      <c r="CF15"/>
-      <c r="CG15"/>
+      <c r="CE15" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF15" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG15" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH15"/>
-      <c r="CI15"/>
-      <c r="CJ15"/>
-      <c r="CK15"/>
+      <c r="CI15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK15" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15"/>
       <c r="CO15" s="4" t="n">
-        <v>38018.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CP15" s="4" t="n">
-        <v>38024.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CQ15"/>
       <c r="CR15"/>
@@ -7597,11 +7613,19 @@
       <c r="DM15"/>
       <c r="DN15" s="3" t="inlineStr">
         <is>
-          <t>J069</t>
-        </is>
-      </c>
-      <c r="DO15"/>
-      <c r="DP15"/>
+          <t>J309</t>
+        </is>
+      </c>
+      <c r="DO15" s="3" t="inlineStr">
+        <is>
+          <t>E785</t>
+        </is>
+      </c>
+      <c r="DP15" s="3" t="inlineStr">
+        <is>
+          <t>E663</t>
+        </is>
+      </c>
       <c r="DQ15"/>
       <c r="DR15"/>
       <c r="DS15"/>
@@ -7625,22 +7649,70 @@
       <c r="EK15"/>
       <c r="EL15"/>
       <c r="EM15"/>
-      <c r="EN15"/>
-      <c r="EO15"/>
-      <c r="EP15"/>
+      <c r="EN15" s="3" t="inlineStr">
+        <is>
+          <t>1999996666</t>
+        </is>
+      </c>
+      <c r="EO15" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE</t>
+        </is>
+      </c>
+      <c r="EP15" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
       <c r="EQ15"/>
-      <c r="ER15"/>
-      <c r="ES15"/>
-      <c r="ET15"/>
+      <c r="ER15" s="3" t="inlineStr">
+        <is>
+          <t>204C00000X</t>
+        </is>
+      </c>
+      <c r="ES15" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET15" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="EU15"/>
       <c r="EV15"/>
-      <c r="EW15"/>
-      <c r="EX15"/>
-      <c r="EY15"/>
+      <c r="EW15" s="3" t="inlineStr">
+        <is>
+          <t>1581234567</t>
+        </is>
+      </c>
+      <c r="EX15" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="EY15" s="3" t="inlineStr">
+        <is>
+          <t>2345 OCEAN BLVD</t>
+        </is>
+      </c>
       <c r="EZ15"/>
-      <c r="FA15"/>
-      <c r="FB15"/>
-      <c r="FC15"/>
+      <c r="FA15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC15" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD15"/>
       <c r="FE15"/>
       <c r="FF15"/>
@@ -7669,22 +7741,66 @@
       <c r="GC15"/>
       <c r="GD15"/>
       <c r="GE15"/>
-      <c r="GF15"/>
-      <c r="GG15"/>
+      <c r="GF15" s="3" t="inlineStr">
+        <is>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="GG15" s="3" t="inlineStr">
+        <is>
+          <t>SPOUSE</t>
+        </is>
+      </c>
       <c r="GH15"/>
       <c r="GI15"/>
-      <c r="GJ15"/>
-      <c r="GK15"/>
-      <c r="GL15"/>
+      <c r="GJ15" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="GK15" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL15" s="3" t="inlineStr">
+        <is>
+          <t>T55TY666</t>
+        </is>
+      </c>
       <c r="GM15"/>
-      <c r="GN15"/>
-      <c r="GO15"/>
+      <c r="GN15" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO15" s="3" t="inlineStr">
+        <is>
+          <t>JACK</t>
+        </is>
+      </c>
       <c r="GP15"/>
-      <c r="GQ15"/>
+      <c r="GQ15" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR15"/>
-      <c r="GS15"/>
-      <c r="GT15"/>
-      <c r="GU15"/>
+      <c r="GS15" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU15" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="GV15"/>
       <c r="GW15"/>
       <c r="GX15"/>
@@ -7701,10 +7817,22 @@
       <c r="HI15"/>
       <c r="HJ15"/>
       <c r="HK15"/>
-      <c r="HL15"/>
-      <c r="HM15"/>
+      <c r="HL15" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM15" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
       <c r="HN15"/>
-      <c r="HO15"/>
+      <c r="HO15" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
       <c r="HP15"/>
       <c r="HQ15"/>
       <c r="HR15"/>
@@ -7718,7 +7846,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7728,12 +7856,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>837P-all-fields.dat</t>
+          <t>home-infusion-ndc.dat</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0031</t>
+          <t>0711</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -7743,12 +7871,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>0031</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2006-10-15T10:23:00</t>
+          <t>2004-03-01T12:00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -7758,20 +7886,20 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>36463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>100.0</v>
+        <v>2232.93</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -7799,11 +7927,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="R16"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
           <t>NPI</t>
@@ -7811,50 +7935,46 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>1234567893</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>10-1234567</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>Professional Home IV, LLC</t>
         </is>
       </c>
       <c r="W16"/>
       <c r="X16"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1500 Industrial Drive</t>
         </is>
       </c>
       <c r="Z16"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>Libertyville</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>203BF0100Y</t>
-        </is>
-      </c>
+          <t>60048</t>
+        </is>
+      </c>
+      <c r="AD16"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>JOHN SMITH</t>
+          <t>Brenda Holly</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -7864,34 +7984,18 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>5555551234</t>
-        </is>
-      </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="AI16" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
+          <t>8019999999</t>
+        </is>
+      </c>
+      <c r="AH16"/>
+      <c r="AI16"/>
       <c r="AJ16"/>
       <c r="AK16"/>
       <c r="AL16"/>
       <c r="AM16"/>
       <c r="AN16"/>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>STATE_LICENSE_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>654321</t>
-        </is>
-      </c>
+      <c r="AO16"/>
+      <c r="AP16"/>
       <c r="AQ16"/>
       <c r="AR16"/>
       <c r="AS16" s="3" t="inlineStr">
@@ -7899,10 +8003,14 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT16"/>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2222-SJ</t>
+          <t>GRP01020102</t>
         </is>
       </c>
       <c r="AV16"/>
@@ -7918,464 +8026,186 @@
       </c>
       <c r="AY16" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
-        </is>
-      </c>
-      <c r="AZ16" s="3" t="inlineStr">
-        <is>
-          <t>123450000</t>
-        </is>
-      </c>
+          <t>MBRID01234</t>
+        </is>
+      </c>
+      <c r="AZ16"/>
       <c r="BA16" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="BC16"/>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="BD16" s="4" t="n">
         <v>15827.0</v>
       </c>
       <c r="BE16" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF16" s="3" t="inlineStr">
         <is>
-          <t>236 N MAIN ST</t>
+          <t>15210 Juliet Lane</t>
         </is>
       </c>
       <c r="BG16"/>
       <c r="BH16" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>Libertyville</t>
         </is>
       </c>
       <c r="BI16" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="BJ16" s="3" t="inlineStr">
         <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="BK16" s="4" t="n">
-        <v>32905.0</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>176.0</v>
-      </c>
-      <c r="BM16" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>60048</t>
+        </is>
+      </c>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
       <c r="BN16" s="3" t="inlineStr">
         <is>
-          <t>PAYOR_ID</t>
+          <t>CMS_PLAN_ID</t>
         </is>
       </c>
       <c r="BO16" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
-        </is>
-      </c>
-      <c r="BP16" s="3" t="inlineStr">
-        <is>
-          <t>435261708</t>
-        </is>
-      </c>
+          <t>PLANID12345</t>
+        </is>
+      </c>
+      <c r="BP16"/>
       <c r="BQ16" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCECOMPANY</t>
-        </is>
-      </c>
-      <c r="BR16" s="3" t="inlineStr">
-        <is>
-          <t>P.O. BOX 569008</t>
-        </is>
-      </c>
+          <t>R&amp;R Health Plan</t>
+        </is>
+      </c>
+      <c r="BR16"/>
       <c r="BS16"/>
-      <c r="BT16" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="BU16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BV16" s="3" t="inlineStr">
-        <is>
-          <t>332560000</t>
-        </is>
-      </c>
-      <c r="BW16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
+      <c r="BX16"/>
       <c r="BY16"/>
       <c r="BZ16"/>
-      <c r="CA16" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB16" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC16" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA16"/>
+      <c r="CB16"/>
+      <c r="CC16"/>
       <c r="CD16"/>
-      <c r="CE16" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF16" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG16" s="3" t="inlineStr">
-        <is>
-          <t>237 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE16"/>
+      <c r="CF16"/>
+      <c r="CG16"/>
       <c r="CH16"/>
-      <c r="CI16" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK16" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="CL16" s="4" t="n">
-        <v>35503.0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>156.0</v>
-      </c>
-      <c r="CN16" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="CI16"/>
+      <c r="CJ16"/>
+      <c r="CK16"/>
+      <c r="CL16"/>
+      <c r="CM16"/>
+      <c r="CN16"/>
       <c r="CO16" s="4" t="n">
-        <v>38425.0</v>
+        <v>38018.0</v>
       </c>
       <c r="CP16" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="CQ16" s="4" t="n">
-        <v>43171.0</v>
-      </c>
-      <c r="CR16" s="4" t="n">
-        <v>43160.0</v>
-      </c>
-      <c r="CS16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CT16" s="4" t="n">
-        <v>43161.0</v>
-      </c>
-      <c r="CU16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CV16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CW16" s="4" t="n">
-        <v>38360.0</v>
-      </c>
+        <v>38024.0</v>
+      </c>
+      <c r="CQ16"/>
+      <c r="CR16"/>
+      <c r="CS16"/>
+      <c r="CT16"/>
+      <c r="CU16"/>
+      <c r="CV16"/>
+      <c r="CW16"/>
       <c r="CX16"/>
-      <c r="CY16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="CZ16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DA16" s="4" t="n">
-        <v>38480.0</v>
-      </c>
-      <c r="DB16" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DC16" s="1" t="n">
-        <v>152.45</v>
-      </c>
-      <c r="DD16" s="3" t="inlineStr">
-        <is>
-          <t>ServiceAuthorizationExceptionCode</t>
-        </is>
-      </c>
-      <c r="DE16" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNum</t>
-        </is>
-      </c>
-      <c r="DF16" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuth</t>
-        </is>
-      </c>
-      <c r="DG16" s="3" t="inlineStr">
-        <is>
-          <t>PayerClaimControlNum</t>
-        </is>
-      </c>
-      <c r="DH16" s="3" t="inlineStr">
-        <is>
-          <t>ClaimIdForTransm</t>
-        </is>
-      </c>
-      <c r="DI16" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="DJ16" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="DK16" s="3" t="inlineStr">
-        <is>
-          <t>MedicalRecordNum</t>
-        </is>
-      </c>
-      <c r="DL16" s="3" t="inlineStr">
-        <is>
-          <t>DemonstrProjectId</t>
-        </is>
-      </c>
-      <c r="DM16" s="3" t="inlineStr">
-        <is>
-          <t>SURGERY WAS UNUSUALLY LONG</t>
-        </is>
-      </c>
+      <c r="CY16"/>
+      <c r="CZ16"/>
+      <c r="DA16"/>
+      <c r="DB16"/>
+      <c r="DC16"/>
+      <c r="DD16"/>
+      <c r="DE16"/>
+      <c r="DF16"/>
+      <c r="DG16"/>
+      <c r="DH16"/>
+      <c r="DI16"/>
+      <c r="DJ16"/>
+      <c r="DK16"/>
+      <c r="DL16"/>
+      <c r="DM16"/>
       <c r="DN16" s="3" t="inlineStr">
         <is>
-          <t>J0300</t>
-        </is>
-      </c>
-      <c r="DO16" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>J069</t>
+        </is>
+      </c>
+      <c r="DO16"/>
       <c r="DP16"/>
       <c r="DQ16"/>
       <c r="DR16"/>
-      <c r="DS16" s="3" t="inlineStr">
-        <is>
-          <t>33414</t>
-        </is>
-      </c>
-      <c r="DT16" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="DU16" s="3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+      <c r="DS16"/>
+      <c r="DT16"/>
+      <c r="DU16"/>
       <c r="DV16"/>
-      <c r="DW16" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="DX16" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="DY16" s="3" t="inlineStr">
-        <is>
-          <t>DMN0012</t>
-        </is>
-      </c>
+      <c r="DW16"/>
+      <c r="DX16"/>
+      <c r="DY16"/>
       <c r="DZ16"/>
       <c r="EA16"/>
       <c r="EB16"/>
       <c r="EC16"/>
       <c r="ED16"/>
       <c r="EE16"/>
-      <c r="EF16" s="3" t="inlineStr">
-        <is>
-          <t>5234567805</t>
-        </is>
-      </c>
-      <c r="EG16" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH16" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="EI16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EJ16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="EK16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="EF16"/>
+      <c r="EG16"/>
+      <c r="EH16"/>
+      <c r="EI16"/>
+      <c r="EJ16"/>
+      <c r="EK16"/>
       <c r="EL16"/>
       <c r="EM16"/>
-      <c r="EN16" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="EO16" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EP16" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="EQ16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="ER16" s="3" t="inlineStr">
-        <is>
-          <t>000000000X</t>
-        </is>
-      </c>
-      <c r="ES16" s="3" t="inlineStr">
-        <is>
-          <t>LOCATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="EN16"/>
+      <c r="EO16"/>
+      <c r="EP16"/>
+      <c r="EQ16"/>
+      <c r="ER16"/>
+      <c r="ES16"/>
+      <c r="ET16"/>
       <c r="EU16"/>
       <c r="EV16"/>
-      <c r="EW16" s="3" t="inlineStr">
-        <is>
-          <t>000000004</t>
-        </is>
-      </c>
-      <c r="EX16" s="3" t="inlineStr">
-        <is>
-          <t>Service Facility</t>
-        </is>
-      </c>
-      <c r="EY16" s="3" t="inlineStr">
-        <is>
-          <t>123 FAKE STREET</t>
-        </is>
-      </c>
+      <c r="EW16"/>
+      <c r="EX16"/>
+      <c r="EY16"/>
       <c r="EZ16"/>
-      <c r="FA16" s="3" t="inlineStr">
-        <is>
-          <t>CITY</t>
-        </is>
-      </c>
-      <c r="FB16" s="3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="FC16" s="3" t="inlineStr">
-        <is>
-          <t>123459999</t>
-        </is>
-      </c>
+      <c r="FA16"/>
+      <c r="FB16"/>
+      <c r="FC16"/>
       <c r="FD16"/>
       <c r="FE16"/>
       <c r="FF16"/>
       <c r="FG16"/>
       <c r="FH16"/>
-      <c r="FI16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FJ16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="FI16"/>
+      <c r="FJ16"/>
       <c r="FK16"/>
       <c r="FL16"/>
-      <c r="FM16" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="FN16" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="FO16" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="FP16" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="FQ16" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FR16" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="FM16"/>
+      <c r="FN16"/>
+      <c r="FO16"/>
+      <c r="FP16"/>
+      <c r="FQ16"/>
+      <c r="FR16"/>
       <c r="FS16"/>
       <c r="FT16"/>
       <c r="FU16"/>
@@ -8389,189 +8219,911 @@
       <c r="GC16"/>
       <c r="GD16"/>
       <c r="GE16"/>
-      <c r="GF16" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="GG16" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="GH16" s="3" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="GI16" s="3" t="inlineStr">
-        <is>
-          <t>PLAN NAME</t>
-        </is>
-      </c>
-      <c r="GJ16" s="3" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="GK16" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL16" s="3" t="inlineStr">
-        <is>
-          <t>JS00111223999</t>
-        </is>
-      </c>
+      <c r="GF16"/>
+      <c r="GG16"/>
+      <c r="GH16"/>
+      <c r="GI16"/>
+      <c r="GJ16"/>
+      <c r="GK16"/>
+      <c r="GL16"/>
       <c r="GM16"/>
-      <c r="GN16" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO16" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="GN16"/>
+      <c r="GO16"/>
       <c r="GP16"/>
-      <c r="GQ16" s="3" t="inlineStr">
-        <is>
-          <t>239 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ16"/>
       <c r="GR16"/>
-      <c r="GS16" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU16" s="3" t="inlineStr">
-        <is>
-          <t>33415</t>
-        </is>
-      </c>
-      <c r="GV16" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="GW16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="GX16" s="1" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="GS16"/>
+      <c r="GT16"/>
+      <c r="GU16"/>
+      <c r="GV16"/>
+      <c r="GW16"/>
+      <c r="GX16"/>
       <c r="GY16"/>
-      <c r="GZ16" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="HA16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="HB16" s="1" t="n">
-        <v>15.0</v>
-      </c>
+      <c r="GZ16"/>
+      <c r="HA16"/>
+      <c r="HB16"/>
       <c r="HC16"/>
-      <c r="HD16" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="HE16" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="HF16" s="1" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="HG16" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="HH16" s="1" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="HI16" s="1" t="n">
-        <v>273.0</v>
-      </c>
-      <c r="HJ16" s="1" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="HK16" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM99</t>
-        </is>
-      </c>
-      <c r="HL16" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM16" s="3" t="inlineStr">
-        <is>
-          <t>OTP</t>
-        </is>
-      </c>
-      <c r="HN16" s="3" t="inlineStr">
-        <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="HO16" s="3" t="inlineStr">
-        <is>
-          <t>OTHER PAYER</t>
-        </is>
-      </c>
-      <c r="HP16" s="3" t="inlineStr">
-        <is>
-          <t>PO BOX 7901</t>
-        </is>
-      </c>
-      <c r="HQ16" s="3" t="inlineStr">
-        <is>
-          <t>DEP 2</t>
-        </is>
-      </c>
-      <c r="HR16" s="3" t="inlineStr">
-        <is>
-          <t>MADISON</t>
-        </is>
-      </c>
-      <c r="HS16" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="HT16" s="3" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="HU16" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM_OFFICE_NUMBER</t>
-        </is>
-      </c>
-      <c r="HV16" s="3" t="inlineStr">
-        <is>
-          <t>98765</t>
-        </is>
-      </c>
+      <c r="HD16"/>
+      <c r="HE16"/>
+      <c r="HF16"/>
+      <c r="HG16"/>
+      <c r="HH16"/>
+      <c r="HI16"/>
+      <c r="HJ16"/>
+      <c r="HK16"/>
+      <c r="HL16"/>
+      <c r="HM16"/>
+      <c r="HN16"/>
+      <c r="HO16"/>
+      <c r="HP16"/>
+      <c r="HQ16"/>
+      <c r="HR16"/>
+      <c r="HS16"/>
+      <c r="HT16"/>
+      <c r="HU16"/>
+      <c r="HV16"/>
       <c r="HW16"/>
       <c r="HX16"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>69efef05ad4799caa7f5d033</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>837P</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>837P-all-fields.dat</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>2006-10-15T10:23:00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>CHARGEABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>36463774</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>NPI</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>587654321</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>BEN KILDARE SERVICE</t>
+        </is>
+      </c>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>234 SEAWAY ST</t>
+        </is>
+      </c>
+      <c r="Z17"/>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>203BF0100Y</t>
+        </is>
+      </c>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>JOHN SMITH</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>5555551234</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AJ17"/>
+      <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>STATE_LICENSE_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>654321</t>
+        </is>
+      </c>
+      <c r="AQ17"/>
+      <c r="AR17"/>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="AT17"/>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
+      <c r="AV17"/>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="AY17" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223333</t>
+        </is>
+      </c>
+      <c r="AZ17" s="3" t="inlineStr">
+        <is>
+          <t>123450000</t>
+        </is>
+      </c>
+      <c r="BA17" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="BB17" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC17"/>
+      <c r="BD17" s="4" t="n">
+        <v>15827.0</v>
+      </c>
+      <c r="BE17" s="3" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="BF17" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="BG17"/>
+      <c r="BH17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BI17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ17" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="BK17" s="4" t="n">
+        <v>32905.0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>176.0</v>
+      </c>
+      <c r="BM17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BN17" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="BO17" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
+      <c r="BP17" s="3" t="inlineStr">
+        <is>
+          <t>435261708</t>
+        </is>
+      </c>
+      <c r="BQ17" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCECOMPANY</t>
+        </is>
+      </c>
+      <c r="BR17" s="3" t="inlineStr">
+        <is>
+          <t>P.O. BOX 569008</t>
+        </is>
+      </c>
+      <c r="BS17"/>
+      <c r="BT17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BU17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV17" s="3" t="inlineStr">
+        <is>
+          <t>332560000</t>
+        </is>
+      </c>
+      <c r="BW17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="BY17"/>
+      <c r="BZ17"/>
+      <c r="CA17" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB17" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC17" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
+      <c r="CD17"/>
+      <c r="CE17" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF17" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG17" s="3" t="inlineStr">
+        <is>
+          <t>237 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="CH17"/>
+      <c r="CI17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK17" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="CL17" s="4" t="n">
+        <v>35503.0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="CN17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="CO17" s="4" t="n">
+        <v>38425.0</v>
+      </c>
+      <c r="CP17" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="CQ17" s="4" t="n">
+        <v>43171.0</v>
+      </c>
+      <c r="CR17" s="4" t="n">
+        <v>43160.0</v>
+      </c>
+      <c r="CS17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CT17" s="4" t="n">
+        <v>43161.0</v>
+      </c>
+      <c r="CU17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CV17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CW17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CX17" s="4" t="n">
+        <v>38473.0</v>
+      </c>
+      <c r="CY17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="CZ17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DA17" s="4" t="n">
+        <v>38480.0</v>
+      </c>
+      <c r="DB17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DC17" s="1" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="DD17" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="DE17" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNum</t>
+        </is>
+      </c>
+      <c r="DF17" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuth</t>
+        </is>
+      </c>
+      <c r="DG17" s="3" t="inlineStr">
+        <is>
+          <t>PayerClaimControlNum</t>
+        </is>
+      </c>
+      <c r="DH17" s="3" t="inlineStr">
+        <is>
+          <t>ClaimIdForTransm</t>
+        </is>
+      </c>
+      <c r="DI17" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="DJ17" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="DK17" s="3" t="inlineStr">
+        <is>
+          <t>MedicalRecordNum</t>
+        </is>
+      </c>
+      <c r="DL17" s="3" t="inlineStr">
+        <is>
+          <t>DemonstrProjectId</t>
+        </is>
+      </c>
+      <c r="DM17" s="3" t="inlineStr">
+        <is>
+          <t>SURGERY WAS UNUSUALLY LONG</t>
+        </is>
+      </c>
+      <c r="DN17" s="3" t="inlineStr">
+        <is>
+          <t>J0300</t>
+        </is>
+      </c>
+      <c r="DO17" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
+      <c r="DP17"/>
+      <c r="DQ17"/>
+      <c r="DR17"/>
+      <c r="DS17" s="3" t="inlineStr">
+        <is>
+          <t>33414</t>
+        </is>
+      </c>
+      <c r="DT17" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="DU17" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="DV17"/>
+      <c r="DW17" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="DX17" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="DY17" s="3" t="inlineStr">
+        <is>
+          <t>DMN0012</t>
+        </is>
+      </c>
+      <c r="DZ17"/>
+      <c r="EA17"/>
+      <c r="EB17"/>
+      <c r="EC17"/>
+      <c r="ED17"/>
+      <c r="EE17"/>
+      <c r="EF17" s="3" t="inlineStr">
+        <is>
+          <t>5234567805</t>
+        </is>
+      </c>
+      <c r="EG17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH17" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="EI17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EJ17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="EK17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="EL17"/>
+      <c r="EM17"/>
+      <c r="EN17" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="EO17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EP17" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="EQ17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER17" s="3" t="inlineStr">
+        <is>
+          <t>000000000X</t>
+        </is>
+      </c>
+      <c r="ES17" s="3" t="inlineStr">
+        <is>
+          <t>LOCATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="EU17"/>
+      <c r="EV17"/>
+      <c r="EW17" s="3" t="inlineStr">
+        <is>
+          <t>000000004</t>
+        </is>
+      </c>
+      <c r="EX17" s="3" t="inlineStr">
+        <is>
+          <t>Service Facility</t>
+        </is>
+      </c>
+      <c r="EY17" s="3" t="inlineStr">
+        <is>
+          <t>123 FAKE STREET</t>
+        </is>
+      </c>
+      <c r="EZ17"/>
+      <c r="FA17" s="3" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="FB17" s="3" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="FC17" s="3" t="inlineStr">
+        <is>
+          <t>123459999</t>
+        </is>
+      </c>
+      <c r="FD17"/>
+      <c r="FE17"/>
+      <c r="FF17"/>
+      <c r="FG17"/>
+      <c r="FH17"/>
+      <c r="FI17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FJ17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="FK17"/>
+      <c r="FL17"/>
+      <c r="FM17" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="FN17" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="FO17" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="FP17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FR17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
+      <c r="FS17"/>
+      <c r="FT17"/>
+      <c r="FU17"/>
+      <c r="FV17"/>
+      <c r="FW17"/>
+      <c r="FX17"/>
+      <c r="FY17"/>
+      <c r="FZ17"/>
+      <c r="GA17"/>
+      <c r="GB17"/>
+      <c r="GC17"/>
+      <c r="GD17"/>
+      <c r="GE17"/>
+      <c r="GF17" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="GG17" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="GH17" s="3" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="GI17" s="3" t="inlineStr">
+        <is>
+          <t>PLAN NAME</t>
+        </is>
+      </c>
+      <c r="GJ17" s="3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="GK17" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL17" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223999</t>
+        </is>
+      </c>
+      <c r="GM17"/>
+      <c r="GN17" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO17" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="GP17"/>
+      <c r="GQ17" s="3" t="inlineStr">
+        <is>
+          <t>239 N MAIN ST</t>
+        </is>
+      </c>
+      <c r="GR17"/>
+      <c r="GS17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU17" s="3" t="inlineStr">
+        <is>
+          <t>33415</t>
+        </is>
+      </c>
+      <c r="GV17" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="GW17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="GX17" s="1" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="GY17"/>
+      <c r="GZ17" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="HA17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="HB17" s="1" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="HC17"/>
+      <c r="HD17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="HE17" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="HF17" s="1" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="HG17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HH17" s="1" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="HI17" s="1" t="n">
+        <v>273.0</v>
+      </c>
+      <c r="HJ17" s="1" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="HK17" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM99</t>
+        </is>
+      </c>
+      <c r="HL17" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM17" s="3" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="HN17" s="3" t="inlineStr">
+        <is>
+          <t>987654321</t>
+        </is>
+      </c>
+      <c r="HO17" s="3" t="inlineStr">
+        <is>
+          <t>OTHER PAYER</t>
+        </is>
+      </c>
+      <c r="HP17" s="3" t="inlineStr">
+        <is>
+          <t>PO BOX 7901</t>
+        </is>
+      </c>
+      <c r="HQ17" s="3" t="inlineStr">
+        <is>
+          <t>DEP 2</t>
+        </is>
+      </c>
+      <c r="HR17" s="3" t="inlineStr">
+        <is>
+          <t>MADISON</t>
+        </is>
+      </c>
+      <c r="HS17" s="3" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="HT17" s="3" t="inlineStr">
+        <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="HU17" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM_OFFICE_NUMBER</t>
+        </is>
+      </c>
+      <c r="HV17" s="3" t="inlineStr">
+        <is>
+          <t>98765</t>
+        </is>
+      </c>
+      <c r="HW17"/>
+      <c r="HX17"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -8580,7 +9132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:DS45"/>
+  <dimension ref="A1:DS46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -9203,7 +9755,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69efef05ad4799caa7f5cc98</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -9406,7 +9958,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69efef05ad4799caa7f5cc98</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9573,7 +10125,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69efef05ad4799caa7f5cc98</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -9740,7 +10292,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4122</t>
+          <t>69efef05ad4799caa7f5cc98</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -9907,7 +10459,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69efef05ad4799caa7f5ccc9</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10062,7 +10614,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69efef05ad4799caa7f5ccc9</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -10217,7 +10769,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69efef05ad4799caa7f5ccc9</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -10372,7 +10924,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4153</t>
+          <t>69efef05ad4799caa7f5ccc9</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -10527,7 +11079,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4177</t>
+          <t>69efef05ad4799caa7f5ccf3</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -10682,7 +11234,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69efef05ad4799caa7f5cd3c</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -10841,7 +11393,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69efef05ad4799caa7f5cd3c</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -10998,7 +11550,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41c0</t>
+          <t>69efef05ad4799caa7f5cd3c</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -11155,7 +11707,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69efef05ad4799caa7f5cd74</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11179,7 +11731,7 @@
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" s="1" t="n">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -11189,22 +11741,42 @@
       <c r="L14" t="n">
         <v>1.0</v>
       </c>
-      <c r="M14"/>
-      <c r="N14"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
-      <c r="R14"/>
-      <c r="S14"/>
-      <c r="T14"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="U14"/>
       <c r="V14" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>38993.0</v>
+        <v>40943.0</v>
       </c>
       <c r="X14"/>
       <c r="Y14"/>
@@ -11310,7 +11882,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69efef05ad4799caa7f5cdaa</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11320,12 +11892,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E15"/>
@@ -11334,7 +11906,7 @@
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -11465,7 +12037,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f41ef</t>
+          <t>69efef05ad4799caa7f5cdaa</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -11475,12 +12047,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E16"/>
@@ -11489,7 +12061,7 @@
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -11502,7 +12074,7 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
@@ -11511,10 +12083,10 @@
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X16"/>
       <c r="Y16"/>
@@ -11620,22 +12192,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69efef05ad4799caa7f5cdaa</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E17"/>
@@ -11644,7 +12216,7 @@
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" s="1" t="n">
-        <v>40.0</v>
+        <v>35.0</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -11657,7 +12229,7 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
@@ -11666,10 +12238,10 @@
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X17"/>
       <c r="Y17"/>
@@ -11775,7 +12347,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69efef05ad4799caa7f5ce21</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -11785,12 +12357,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E18"/>
@@ -11799,7 +12371,7 @@
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -11930,7 +12502,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69efef05ad4799caa7f5ce21</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -11940,12 +12512,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E19"/>
@@ -11954,7 +12526,7 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -11967,7 +12539,7 @@
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
@@ -11976,10 +12548,10 @@
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X19"/>
       <c r="Y19"/>
@@ -12085,7 +12657,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4266</t>
+          <t>69efef05ad4799caa7f5ce21</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12095,12 +12667,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E20"/>
@@ -12109,7 +12681,7 @@
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" s="1" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -12240,22 +12812,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4267</t>
+          <t>69efef05ad4799caa7f5ce21</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E21"/>
@@ -12264,7 +12836,7 @@
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" s="1" t="n">
-        <v>145.5</v>
+        <v>10.0</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -12277,7 +12849,7 @@
       <c r="M21"/>
       <c r="N21"/>
       <c r="O21" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -12286,10 +12858,10 @@
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21" s="4" t="n">
-        <v>38398.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>38398.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X21"/>
       <c r="Y21"/>
@@ -12395,51 +12967,39 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69efef05ad4799caa7f5ce22</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="E22"/>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>QK</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22"/>
       <c r="J22" s="1" t="n">
-        <v>827.0</v>
+        <v>145.5</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
@@ -12453,10 +13013,10 @@
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>38364.0</v>
+        <v>38398.0</v>
       </c>
       <c r="X22"/>
       <c r="Y22"/>
@@ -12562,7 +13122,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4268</t>
+          <t>69efef05ad4799caa7f5ce23</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -12572,7 +13132,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -12620,10 +13180,10 @@
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X23"/>
       <c r="Y23"/>
@@ -12729,39 +13289,51 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69efef05ad4799caa7f5ce23</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="I24"/>
       <c r="J24" s="1" t="n">
-        <v>40.0</v>
+        <v>827.0</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -12775,10 +13347,10 @@
       <c r="T24"/>
       <c r="U24"/>
       <c r="V24" s="4" t="n">
-        <v>38993.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>38993.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X24"/>
       <c r="Y24"/>
@@ -12884,7 +13456,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69efef05ad4799caa7f5ce56</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -12894,12 +13466,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E25"/>
@@ -12908,7 +13480,7 @@
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -13039,7 +13611,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69efef05ad4799caa7f5ce56</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -13049,12 +13621,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E26"/>
@@ -13063,7 +13635,7 @@
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -13076,7 +13648,7 @@
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
@@ -13085,10 +13657,10 @@
       <c r="T26"/>
       <c r="U26"/>
       <c r="V26" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X26"/>
       <c r="Y26"/>
@@ -13194,7 +13766,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f429b</t>
+          <t>69efef05ad4799caa7f5ce56</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -13204,12 +13776,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E27"/>
@@ -13218,7 +13790,7 @@
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" s="1" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -13349,56 +13921,44 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69efef05ad4799caa7f5ce56</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E28"/>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>QK</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
       <c r="I28"/>
       <c r="J28" s="1" t="n">
-        <v>827.0</v>
+        <v>10.0</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
@@ -13407,10 +13967,10 @@
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28" s="4" t="n">
-        <v>38364.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>38364.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X28"/>
       <c r="Y28"/>
@@ -13516,7 +14076,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42c4</t>
+          <t>69efef05ad4799caa7f5ce83</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -13526,7 +14086,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -13574,10 +14134,10 @@
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>38365.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X29"/>
       <c r="Y29"/>
@@ -13683,75 +14243,71 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f42f6</t>
+          <t>69efef05ad4799caa7f5ce83</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>K0001</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E30"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>QK</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>KH</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="I30"/>
       <c r="J30" s="1" t="n">
-        <v>75.0</v>
+        <v>827.0</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M30"/>
       <c r="N30"/>
       <c r="O30" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P30" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P30"/>
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>38432.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X30"/>
-      <c r="Y30" s="4" t="n">
-        <v>38067.0</v>
-      </c>
+      <c r="Y30"/>
       <c r="Z30"/>
       <c r="AA30"/>
       <c r="AB30"/>
@@ -13766,16 +14322,8 @@
       <c r="AK30"/>
       <c r="AL30"/>
       <c r="AM30"/>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AO30" s="3" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
+      <c r="AN30"/>
+      <c r="AO30"/>
       <c r="AP30"/>
       <c r="AQ30"/>
       <c r="AR30"/>
@@ -13829,70 +14377,22 @@
       <c r="CN30"/>
       <c r="CO30"/>
       <c r="CP30"/>
-      <c r="CQ30" s="3" t="inlineStr">
-        <is>
-          <t>1111155555</t>
-        </is>
-      </c>
-      <c r="CR30" s="3" t="inlineStr">
-        <is>
-          <t>WILSON</t>
-        </is>
-      </c>
-      <c r="CS30" s="3" t="inlineStr">
-        <is>
-          <t>RANDALL</t>
-        </is>
-      </c>
+      <c r="CQ30"/>
+      <c r="CR30"/>
+      <c r="CS30"/>
       <c r="CT30"/>
-      <c r="CU30" s="3" t="inlineStr">
-        <is>
-          <t>1226 WEST RAILROAD STREET</t>
-        </is>
-      </c>
+      <c r="CU30"/>
       <c r="CV30"/>
-      <c r="CW30" s="3" t="inlineStr">
-        <is>
-          <t>LAFAYETTE</t>
-        </is>
-      </c>
-      <c r="CX30" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="CY30" s="3" t="inlineStr">
-        <is>
-          <t>47905</t>
-        </is>
-      </c>
-      <c r="CZ30" s="3" t="inlineStr">
-        <is>
-          <t>LEE</t>
-        </is>
-      </c>
-      <c r="DA30" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="DB30" s="3" t="inlineStr">
-        <is>
-          <t>7659259999</t>
-        </is>
-      </c>
+      <c r="CW30"/>
+      <c r="CX30"/>
+      <c r="CY30"/>
+      <c r="CZ30"/>
+      <c r="DA30"/>
+      <c r="DB30"/>
       <c r="DC30"/>
       <c r="DD30"/>
-      <c r="DE30" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DF30" s="3" t="inlineStr">
-        <is>
-          <t>M12345</t>
-        </is>
-      </c>
+      <c r="DE30"/>
+      <c r="DF30"/>
       <c r="DG30"/>
       <c r="DH30"/>
       <c r="DI30"/>
@@ -13910,12 +14410,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69efef05ad4799caa7f5cebf</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -13925,7 +14425,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>E0570</t>
+          <t>K0001</t>
         </is>
       </c>
       <c r="E31"/>
@@ -13934,11 +14434,19 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="G31"/>
-      <c r="H31"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>KH</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
       <c r="I31"/>
       <c r="J31" s="1" t="n">
-        <v>25.0</v>
+        <v>75.0</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -13962,23 +14470,21 @@
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>38486.0</v>
+        <v>38432.0</v>
       </c>
       <c r="X31"/>
-      <c r="Y31"/>
+      <c r="Y31" s="4" t="n">
+        <v>38067.0</v>
+      </c>
       <c r="Z31"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31"/>
-      <c r="AE31" s="3" t="inlineStr">
-        <is>
-          <t>V123456</t>
-        </is>
-      </c>
+      <c r="AE31"/>
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
@@ -13987,8 +14493,16 @@
       <c r="AK31"/>
       <c r="AL31"/>
       <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
       <c r="AP31"/>
       <c r="AQ31"/>
       <c r="AR31"/>
@@ -14034,42 +14548,78 @@
       <c r="CF31"/>
       <c r="CG31"/>
       <c r="CH31"/>
-      <c r="CI31" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="CJ31" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CK31" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="CI31"/>
+      <c r="CJ31"/>
+      <c r="CK31"/>
       <c r="CL31"/>
       <c r="CM31"/>
       <c r="CN31"/>
       <c r="CO31"/>
       <c r="CP31"/>
-      <c r="CQ31"/>
-      <c r="CR31"/>
-      <c r="CS31"/>
+      <c r="CQ31" s="3" t="inlineStr">
+        <is>
+          <t>1111155555</t>
+        </is>
+      </c>
+      <c r="CR31" s="3" t="inlineStr">
+        <is>
+          <t>WILSON</t>
+        </is>
+      </c>
+      <c r="CS31" s="3" t="inlineStr">
+        <is>
+          <t>RANDALL</t>
+        </is>
+      </c>
       <c r="CT31"/>
-      <c r="CU31"/>
+      <c r="CU31" s="3" t="inlineStr">
+        <is>
+          <t>1226 WEST RAILROAD STREET</t>
+        </is>
+      </c>
       <c r="CV31"/>
-      <c r="CW31"/>
-      <c r="CX31"/>
-      <c r="CY31"/>
-      <c r="CZ31"/>
-      <c r="DA31"/>
-      <c r="DB31"/>
+      <c r="CW31" s="3" t="inlineStr">
+        <is>
+          <t>LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="CX31" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="CY31" s="3" t="inlineStr">
+        <is>
+          <t>47905</t>
+        </is>
+      </c>
+      <c r="CZ31" s="3" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="DA31" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="DB31" s="3" t="inlineStr">
+        <is>
+          <t>7659259999</t>
+        </is>
+      </c>
       <c r="DC31"/>
       <c r="DD31"/>
-      <c r="DE31"/>
-      <c r="DF31"/>
+      <c r="DE31" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="DF31" s="3" t="inlineStr">
+        <is>
+          <t>M12345</t>
+        </is>
+      </c>
       <c r="DG31"/>
       <c r="DH31"/>
       <c r="DI31"/>
@@ -14087,7 +14637,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4326</t>
+          <t>69efef05ad4799caa7f5ceef</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -14097,25 +14647,25 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>A7003</t>
+          <t>E0570</t>
         </is>
       </c>
       <c r="E32"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" s="1" t="n">
-        <v>3.75</v>
+        <v>25.0</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -14130,7 +14680,9 @@
       <c r="O32" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P32"/>
+      <c r="P32" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
@@ -14149,7 +14701,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32"/>
-      <c r="AE32"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>V123456</t>
+        </is>
+      </c>
       <c r="AF32"/>
       <c r="AG32"/>
       <c r="AH32"/>
@@ -14205,9 +14761,21 @@
       <c r="CF32"/>
       <c r="CG32"/>
       <c r="CH32"/>
-      <c r="CI32"/>
-      <c r="CJ32"/>
-      <c r="CK32"/>
+      <c r="CI32" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="CJ32" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK32" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="CL32"/>
       <c r="CM32"/>
       <c r="CN32"/>
@@ -14246,31 +14814,35 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69efef05ad4799caa7f5ceef</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>A7003</t>
         </is>
       </c>
       <c r="E33"/>
-      <c r="F33"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>NU</t>
+        </is>
+      </c>
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" s="1" t="n">
-        <v>43.0</v>
+        <v>3.75</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -14285,21 +14857,17 @@
       <c r="O33" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P33" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Q33" s="2" t="n">
-        <v>3.0</v>
-      </c>
+      <c r="P33"/>
+      <c r="Q33"/>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33"/>
       <c r="U33"/>
       <c r="V33" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>38628.0</v>
+        <v>38486.0</v>
       </c>
       <c r="X33"/>
       <c r="Y33"/>
@@ -14405,7 +14973,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69efef05ad4799caa7f5cf2a</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14415,12 +14983,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E34"/>
@@ -14429,7 +14997,7 @@
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" s="1" t="n">
-        <v>15.0</v>
+        <v>43.0</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -14447,7 +15015,9 @@
       <c r="P34" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Q34"/>
+      <c r="Q34" s="2" t="n">
+        <v>3.0</v>
+      </c>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34"/>
@@ -14562,7 +15132,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f4361</t>
+          <t>69efef05ad4799caa7f5cf2a</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -14572,12 +15142,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>J3301</t>
+          <t>96372</t>
         </is>
       </c>
       <c r="E35"/>
@@ -14586,7 +15156,7 @@
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" s="1" t="n">
-        <v>21.04</v>
+        <v>15.0</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -14719,22 +15289,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf2a</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>S9500</t>
+          <t>J3301</t>
         </is>
       </c>
       <c r="E36"/>
@@ -14743,7 +15313,7 @@
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" s="1" t="n">
-        <v>1400.0</v>
+        <v>21.04</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -14751,32 +15321,26 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="M36"/>
+      <c r="N36"/>
       <c r="O36" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P36"/>
+      <c r="P36" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
       <c r="V36" s="4" t="n">
-        <v>38018.0</v>
+        <v>38628.0</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>38024.0</v>
+        <v>38628.0</v>
       </c>
       <c r="X36"/>
       <c r="Y36"/>
@@ -14849,21 +15413,9 @@
       <c r="CN36"/>
       <c r="CO36"/>
       <c r="CP36"/>
-      <c r="CQ36" s="3" t="inlineStr">
-        <is>
-          <t>1112223338</t>
-        </is>
-      </c>
-      <c r="CR36" s="3" t="inlineStr">
-        <is>
-          <t>Welby</t>
-        </is>
-      </c>
-      <c r="CS36" s="3" t="inlineStr">
-        <is>
-          <t>Marcus</t>
-        </is>
-      </c>
+      <c r="CQ36"/>
+      <c r="CR36"/>
+      <c r="CS36"/>
       <c r="CT36"/>
       <c r="CU36"/>
       <c r="CV36"/>
@@ -14894,7 +15446,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -14904,12 +15456,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>S5001</t>
+          <t>S9500</t>
         </is>
       </c>
       <c r="E37"/>
@@ -14918,7 +15470,7 @@
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" s="1" t="n">
-        <v>682.5</v>
+        <v>1400.0</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -14953,9 +15505,7 @@
       <c r="W37" s="4" t="n">
         <v>38024.0</v>
       </c>
-      <c r="X37" s="4" t="n">
-        <v>38016.0</v>
-      </c>
+      <c r="X37"/>
       <c r="Y37"/>
       <c r="Z37"/>
       <c r="AA37"/>
@@ -14967,24 +15517,10 @@
       <c r="AG37"/>
       <c r="AH37"/>
       <c r="AI37"/>
-      <c r="AJ37" s="3" t="inlineStr">
-        <is>
-          <t>00003161201</t>
-        </is>
-      </c>
-      <c r="AK37" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="AL37" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2530001</t>
-        </is>
-      </c>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
       <c r="AN37"/>
       <c r="AO37"/>
       <c r="AP37"/>
@@ -15085,7 +15621,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -15095,12 +15631,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>S5000</t>
+          <t>S5001</t>
         </is>
       </c>
       <c r="E38"/>
@@ -15109,7 +15645,7 @@
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" s="1" t="n">
-        <v>15.12</v>
+        <v>682.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -15117,7 +15653,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -15160,11 +15696,11 @@
       <c r="AI38"/>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>63323025510</t>
+          <t>00003161201</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
@@ -15276,7 +15812,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -15286,7 +15822,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -15300,7 +15836,7 @@
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" s="1" t="n">
-        <v>67.69</v>
+        <v>15.12</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -15308,7 +15844,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -15351,11 +15887,11 @@
       <c r="AI39"/>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>00338004938</t>
+          <t>63323025510</t>
         </is>
       </c>
       <c r="AK39" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
@@ -15467,7 +16003,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -15477,7 +16013,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -15491,7 +16027,7 @@
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" s="1" t="n">
-        <v>57.12</v>
+        <v>67.69</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -15499,7 +16035,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -15542,11 +16078,11 @@
       <c r="AI40"/>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>08290326810</t>
+          <t>00338004938</t>
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
@@ -15555,7 +16091,7 @@
       </c>
       <c r="AM40" s="3" t="inlineStr">
         <is>
-          <t>2530002</t>
+          <t>2530001</t>
         </is>
       </c>
       <c r="AN40"/>
@@ -15658,7 +16194,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>695c20296c0eb413b46f43a9</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -15668,7 +16204,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -15682,7 +16218,7 @@
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" s="1" t="n">
-        <v>10.5</v>
+        <v>57.12</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -15690,7 +16226,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -15733,11 +16269,11 @@
       <c r="AI41"/>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>829080357005</t>
+          <t>08290326810</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
@@ -15746,7 +16282,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2530003</t>
+          <t>2530002</t>
         </is>
       </c>
       <c r="AN41"/>
@@ -15849,47 +16385,31 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69efef05ad4799caa7f5cf72</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>36463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>99299</t>
+          <t>S5000</t>
         </is>
       </c>
       <c r="E42"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
       <c r="J42" s="1" t="n">
-        <v>40.0</v>
+        <v>10.5</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -15897,104 +16417,54 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O42" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P42" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P42"/>
       <c r="Q42"/>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42"/>
       <c r="V42" s="4" t="n">
-        <v>38425.0</v>
+        <v>38018.0</v>
       </c>
       <c r="W42" s="4" t="n">
-        <v>38436.0</v>
+        <v>38024.0</v>
       </c>
       <c r="X42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="Y42" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="AA42" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="AB42" s="4" t="n">
-        <v>38360.0</v>
-      </c>
+        <v>38016.0</v>
+      </c>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
+      <c r="AB42"/>
       <c r="AC42"/>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuthorization</t>
-        </is>
-      </c>
-      <c r="AE42" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNumber</t>
-        </is>
-      </c>
-      <c r="AF42" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="AG42" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
-        </is>
-      </c>
-      <c r="AI42" s="3" t="inlineStr">
-        <is>
-          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
-        </is>
-      </c>
+      <c r="AD42"/>
+      <c r="AE42"/>
+      <c r="AF42"/>
+      <c r="AG42"/>
+      <c r="AH42"/>
+      <c r="AI42"/>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>00002143481</t>
+          <t>829080357005</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>1.01</v>
+        <v>7.0</v>
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
@@ -16003,78 +16473,30 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="AO42" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>Line123</t>
-        </is>
-      </c>
-      <c r="AQ42" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AR42" s="3" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
+          <t>2530003</t>
+        </is>
+      </c>
+      <c r="AN42"/>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+      <c r="AR42"/>
       <c r="AS42"/>
       <c r="AT42"/>
       <c r="AU42"/>
       <c r="AV42"/>
-      <c r="AW42" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>DOE LINE</t>
-        </is>
-      </c>
-      <c r="AY42" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="AZ42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="AW42"/>
+      <c r="AX42"/>
+      <c r="AY42"/>
+      <c r="AZ42"/>
       <c r="BA42"/>
       <c r="BB42"/>
       <c r="BC42"/>
       <c r="BD42"/>
       <c r="BE42"/>
-      <c r="BF42" s="3" t="inlineStr">
-        <is>
-          <t>1234567809</t>
-        </is>
-      </c>
-      <c r="BG42" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BH42" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="BF42"/>
+      <c r="BG42"/>
+      <c r="BH42"/>
       <c r="BI42"/>
       <c r="BJ42"/>
       <c r="BK42"/>
@@ -16093,36 +16515,12 @@
       <c r="BX42"/>
       <c r="BY42"/>
       <c r="BZ42"/>
-      <c r="CA42" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="CB42" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="CC42" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="CD42" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CE42" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="CF42" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="CA42"/>
+      <c r="CB42"/>
+      <c r="CC42"/>
+      <c r="CD42"/>
+      <c r="CE42"/>
+      <c r="CF42"/>
       <c r="CG42"/>
       <c r="CH42"/>
       <c r="CI42"/>
@@ -16133,9 +16531,21 @@
       <c r="CN42"/>
       <c r="CO42"/>
       <c r="CP42"/>
-      <c r="CQ42"/>
-      <c r="CR42"/>
-      <c r="CS42"/>
+      <c r="CQ42" s="3" t="inlineStr">
+        <is>
+          <t>1112223338</t>
+        </is>
+      </c>
+      <c r="CR42" s="3" t="inlineStr">
+        <is>
+          <t>Welby</t>
+        </is>
+      </c>
+      <c r="CS42" s="3" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
       <c r="CT42"/>
       <c r="CU42"/>
       <c r="CV42"/>
@@ -16166,7 +16576,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69efef05ad4799caa7f5d033</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -16176,21 +16586,37 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>99299</t>
         </is>
       </c>
       <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="J43" s="1" t="n">
-        <v>15.0</v>
+        <v>40.0</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -16200,60 +16626,182 @@
       <c r="L43" t="n">
         <v>1.0</v>
       </c>
-      <c r="M43"/>
-      <c r="N43"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P43"/>
+      <c r="P43" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q43"/>
-      <c r="R43"/>
-      <c r="S43"/>
-      <c r="T43"/>
-      <c r="U43"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V43" s="4" t="n">
-        <v>38993.0</v>
+        <v>38425.0</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>38993.0</v>
-      </c>
-      <c r="X43"/>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43"/>
-      <c r="AB43"/>
+        <v>38436.0</v>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="Z43" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="AB43" s="4" t="n">
+        <v>38360.0</v>
+      </c>
       <c r="AC43"/>
-      <c r="AD43"/>
-      <c r="AE43"/>
-      <c r="AF43"/>
-      <c r="AG43"/>
-      <c r="AH43"/>
-      <c r="AI43"/>
-      <c r="AJ43"/>
-      <c r="AK43"/>
-      <c r="AL43"/>
-      <c r="AM43"/>
-      <c r="AN43"/>
-      <c r="AO43"/>
-      <c r="AP43"/>
-      <c r="AQ43"/>
-      <c r="AR43"/>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuthorization</t>
+        </is>
+      </c>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNumber</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
+        </is>
+      </c>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr">
+        <is>
+          <t>00002143481</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>Line123</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="AS43"/>
       <c r="AT43"/>
       <c r="AU43"/>
       <c r="AV43"/>
-      <c r="AW43"/>
-      <c r="AX43"/>
-      <c r="AY43"/>
-      <c r="AZ43"/>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>DOE LINE</t>
+        </is>
+      </c>
+      <c r="AY43" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="AZ43" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="BA43"/>
       <c r="BB43"/>
       <c r="BC43"/>
       <c r="BD43"/>
       <c r="BE43"/>
-      <c r="BF43"/>
-      <c r="BG43"/>
-      <c r="BH43"/>
+      <c r="BF43" s="3" t="inlineStr">
+        <is>
+          <t>1234567809</t>
+        </is>
+      </c>
+      <c r="BG43" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BH43" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="BI43"/>
       <c r="BJ43"/>
       <c r="BK43"/>
@@ -16272,12 +16820,36 @@
       <c r="BX43"/>
       <c r="BY43"/>
       <c r="BZ43"/>
-      <c r="CA43"/>
-      <c r="CB43"/>
-      <c r="CC43"/>
-      <c r="CD43"/>
-      <c r="CE43"/>
-      <c r="CF43"/>
+      <c r="CA43" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="CB43" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="CC43" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="CD43" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CE43" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="CF43" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="CG43"/>
       <c r="CH43"/>
       <c r="CI43"/>
@@ -16321,7 +16893,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69efef05ad4799caa7f5d033</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -16331,12 +16903,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="E44"/>
@@ -16345,7 +16917,7 @@
       <c r="H44"/>
       <c r="I44"/>
       <c r="J44" s="1" t="n">
-        <v>35.0</v>
+        <v>15.0</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -16358,7 +16930,7 @@
       <c r="M44"/>
       <c r="N44"/>
       <c r="O44" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P44"/>
       <c r="Q44"/>
@@ -16367,10 +16939,10 @@
       <c r="T44"/>
       <c r="U44"/>
       <c r="V44" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X44"/>
       <c r="Y44"/>
@@ -16476,7 +17048,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>695c202a6c0eb413b46f4460</t>
+          <t>69efef05ad4799caa7f5d033</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -16486,12 +17058,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E45"/>
@@ -16500,7 +17072,7 @@
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" s="1" t="n">
-        <v>10.0</v>
+        <v>35.0</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -16522,10 +17094,10 @@
       <c r="T45"/>
       <c r="U45"/>
       <c r="V45" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X45"/>
       <c r="Y45"/>
@@ -16539,11 +17111,7 @@
       <c r="AG45"/>
       <c r="AH45"/>
       <c r="AI45"/>
-      <c r="AJ45" s="3" t="inlineStr">
-        <is>
-          <t>01234567891</t>
-        </is>
-      </c>
+      <c r="AJ45"/>
       <c r="AK45"/>
       <c r="AL45"/>
       <c r="AM45"/>
@@ -16632,6 +17200,171 @@
       <c r="DR45"/>
       <c r="DS45"/>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>69efef05ad4799caa7f5d033</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>36463774</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>86663</t>
+        </is>
+      </c>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46"/>
+      <c r="J46" s="1" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="W46" s="4" t="n">
+        <v>39000.0</v>
+      </c>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
+      <c r="AJ46" s="3" t="inlineStr">
+        <is>
+          <t>01234567891</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+      <c r="AR46"/>
+      <c r="AS46"/>
+      <c r="AT46"/>
+      <c r="AU46"/>
+      <c r="AV46"/>
+      <c r="AW46"/>
+      <c r="AX46"/>
+      <c r="AY46"/>
+      <c r="AZ46"/>
+      <c r="BA46"/>
+      <c r="BB46"/>
+      <c r="BC46"/>
+      <c r="BD46"/>
+      <c r="BE46"/>
+      <c r="BF46"/>
+      <c r="BG46"/>
+      <c r="BH46"/>
+      <c r="BI46"/>
+      <c r="BJ46"/>
+      <c r="BK46"/>
+      <c r="BL46"/>
+      <c r="BM46"/>
+      <c r="BN46"/>
+      <c r="BO46"/>
+      <c r="BP46"/>
+      <c r="BQ46"/>
+      <c r="BR46"/>
+      <c r="BS46"/>
+      <c r="BT46"/>
+      <c r="BU46"/>
+      <c r="BV46"/>
+      <c r="BW46"/>
+      <c r="BX46"/>
+      <c r="BY46"/>
+      <c r="BZ46"/>
+      <c r="CA46"/>
+      <c r="CB46"/>
+      <c r="CC46"/>
+      <c r="CD46"/>
+      <c r="CE46"/>
+      <c r="CF46"/>
+      <c r="CG46"/>
+      <c r="CH46"/>
+      <c r="CI46"/>
+      <c r="CJ46"/>
+      <c r="CK46"/>
+      <c r="CL46"/>
+      <c r="CM46"/>
+      <c r="CN46"/>
+      <c r="CO46"/>
+      <c r="CP46"/>
+      <c r="CQ46"/>
+      <c r="CR46"/>
+      <c r="CS46"/>
+      <c r="CT46"/>
+      <c r="CU46"/>
+      <c r="CV46"/>
+      <c r="CW46"/>
+      <c r="CX46"/>
+      <c r="CY46"/>
+      <c r="CZ46"/>
+      <c r="DA46"/>
+      <c r="DB46"/>
+      <c r="DC46"/>
+      <c r="DD46"/>
+      <c r="DE46"/>
+      <c r="DF46"/>
+      <c r="DG46"/>
+      <c r="DH46"/>
+      <c r="DI46"/>
+      <c r="DJ46"/>
+      <c r="DK46"/>
+      <c r="DL46"/>
+      <c r="DM46"/>
+      <c r="DN46"/>
+      <c r="DO46"/>
+      <c r="DP46"/>
+      <c r="DQ46"/>
+      <c r="DR46"/>
+      <c r="DS46"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f19</t>
+          <t>6a04cb3a618f76c4f7b17dca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f4a</t>
+          <t>6a04cb3a618f76c4f7b17dfb</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f74</t>
+          <t>6a04cb3a618f76c4f7b17e25</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03fbd</t>
+          <t>6a04cb3a618f76c4f7b17e6e</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03ff5</t>
+          <t>6a04cb3a618f76c4f7b17ea6</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04024</t>
+          <t>6a04cb3a618f76c4f7b17ed5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4124,7 +4124,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409b</t>
+          <t>6a04cb3a618f76c4f7b17f4c</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4568,7 +4568,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409c</t>
+          <t>6a04cb3a618f76c4f7b17f4d</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -5000,7 +5000,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409d</t>
+          <t>6a04cb3a618f76c4f7b17f4e</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040d0</t>
+          <t>6a04cb3a618f76c4f7b17f81</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5894,7 +5894,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040fd</t>
+          <t>6a04cb3a618f76c4f7b17fae</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04138</t>
+          <t>6a04cb3a618f76c4f7b17fe9</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6764,7 +6764,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04168</t>
+          <t>6a04cb3a618f76c4f7b18019</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041a3</t>
+          <t>6a04cb3a618f76c4f7b18054</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041c7</t>
+          <t>6a04cb3a618f76c4f7b18078</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -8226,7 +8226,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a042cd</t>
+          <t>6a04cb3a618f76c4f7b1817e</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -10135,7 +10135,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f19</t>
+          <t>6a04cb3a618f76c4f7b17dca</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -10338,7 +10338,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f19</t>
+          <t>6a04cb3a618f76c4f7b17dca</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -10505,7 +10505,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f19</t>
+          <t>6a04cb3a618f76c4f7b17dca</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -10672,7 +10672,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f19</t>
+          <t>6a04cb3a618f76c4f7b17dca</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -10839,7 +10839,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f4a</t>
+          <t>6a04cb3a618f76c4f7b17dfb</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f4a</t>
+          <t>6a04cb3a618f76c4f7b17dfb</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -11149,7 +11149,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f4a</t>
+          <t>6a04cb3a618f76c4f7b17dfb</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -11304,7 +11304,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f4a</t>
+          <t>6a04cb3a618f76c4f7b17dfb</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -11459,7 +11459,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03f74</t>
+          <t>6a04cb3a618f76c4f7b17e25</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11614,7 +11614,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03fbd</t>
+          <t>6a04cb3a618f76c4f7b17e6e</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03fbd</t>
+          <t>6a04cb3a618f76c4f7b17e6e</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -11930,7 +11930,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03fbd</t>
+          <t>6a04cb3a618f76c4f7b17e6e</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -12087,7 +12087,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a03ff5</t>
+          <t>6a04cb3a618f76c4f7b17ea6</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -12262,7 +12262,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04024</t>
+          <t>6a04cb3a618f76c4f7b17ed5</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -12417,7 +12417,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04024</t>
+          <t>6a04cb3a618f76c4f7b17ed5</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12572,7 +12572,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04024</t>
+          <t>6a04cb3a618f76c4f7b17ed5</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12727,7 +12727,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409b</t>
+          <t>6a04cb3a618f76c4f7b17f4c</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12882,7 +12882,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409b</t>
+          <t>6a04cb3a618f76c4f7b17f4c</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409b</t>
+          <t>6a04cb3a618f76c4f7b17f4c</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -13192,7 +13192,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409b</t>
+          <t>6a04cb3a618f76c4f7b17f4c</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -13347,7 +13347,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409c</t>
+          <t>6a04cb3a618f76c4f7b17f4d</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -13502,7 +13502,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409d</t>
+          <t>6a04cb3a618f76c4f7b17f4e</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -13669,7 +13669,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0409d</t>
+          <t>6a04cb3a618f76c4f7b17f4e</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13836,7 +13836,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040d0</t>
+          <t>6a04cb3a618f76c4f7b17f81</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -13991,7 +13991,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040d0</t>
+          <t>6a04cb3a618f76c4f7b17f81</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -14146,7 +14146,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040d0</t>
+          <t>6a04cb3a618f76c4f7b17f81</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14301,7 +14301,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040d0</t>
+          <t>6a04cb3a618f76c4f7b17f81</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -14456,7 +14456,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040fd</t>
+          <t>6a04cb3a618f76c4f7b17fae</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -14623,7 +14623,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a040fd</t>
+          <t>6a04cb3a618f76c4f7b17fae</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -14790,7 +14790,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04138</t>
+          <t>6a04cb3a618f76c4f7b17fe9</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -15017,7 +15017,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04168</t>
+          <t>6a04cb3a618f76c4f7b18019</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a04168</t>
+          <t>6a04cb3a618f76c4f7b18019</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -15353,7 +15353,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041a3</t>
+          <t>6a04cb3a618f76c4f7b18054</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -15512,7 +15512,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041a3</t>
+          <t>6a04cb3a618f76c4f7b18054</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -15669,7 +15669,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041a3</t>
+          <t>6a04cb3a618f76c4f7b18054</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -15826,7 +15826,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a041c7</t>
+          <t>6a04cb3a618f76c4f7b18078</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -15981,7 +15981,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -16156,7 +16156,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -16347,7 +16347,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -16729,7 +16729,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a0420f</t>
+          <t>6a04cb3a618f76c4f7b180c0</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -17111,7 +17111,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a042cd</t>
+          <t>6a04cb3a618f76c4f7b1817e</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -17428,7 +17428,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a042cd</t>
+          <t>6a04cb3a618f76c4f7b1817e</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -17583,7 +17583,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a042cd</t>
+          <t>6a04cb3a618f76c4f7b1817e</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -17738,7 +17738,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>69e82c68836d7d05c9a042cd</t>
+          <t>6a04cb3a618f76c4f7b1817e</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">

--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -60,7 +60,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:HX18"/>
+  <dimension ref="A1:HX17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dca</t>
+          <t>6a04cc5a1ef26d534baf29f1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dfb</t>
+          <t>6a04cc5a1ef26d534baf2a22</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e25</t>
+          <t>6a04cc5a1ef26d534baf2a4c</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e6e</t>
+          <t>6a04cc5a1ef26d534baf2a95</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ea6</t>
+          <t>6a04cc5a1ef26d534baf2ac4</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>837P-X298-all-fields.dat</t>
+          <t>commercial.dat</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2012-03-15T10:23:00</t>
+          <t>2006-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>REPORTING</t>
+          <t>CHARGEABLE</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -3231,10 +3231,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="R6"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -3253,7 +3269,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>PHYSICIAN CLINIC</t>
+          <t>Ben Kildare Service</t>
         </is>
       </c>
       <c r="W6"/>
@@ -3281,7 +3297,7 @@
       </c>
       <c r="AD6" s="3" t="inlineStr">
         <is>
-          <t>207Q00000X</t>
+          <t>103G00000X</t>
         </is>
       </c>
       <c r="AE6"/>
@@ -3300,13 +3316,21 @@
       <c r="AR6"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>UNCONFIRMED</t>
+          <t>PRIMARY</t>
         </is>
       </c>
       <c r="AT6"/>
-      <c r="AU6"/>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="AV6"/>
-      <c r="AW6"/>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
       <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -3320,12 +3344,12 @@
       <c r="AZ6"/>
       <c r="BA6" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB6" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="BC6"/>
@@ -3337,41 +3361,45 @@
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="BF6"/>
       <c r="BG6"/>
-      <c r="BH6" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="BI6" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BJ6" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="BH6"/>
+      <c r="BI6"/>
+      <c r="BJ6"/>
       <c r="BK6"/>
       <c r="BL6"/>
       <c r="BM6"/>
-      <c r="BN6"/>
-      <c r="BO6"/>
+      <c r="BN6" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="BO6" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
       <c r="BP6"/>
-      <c r="BQ6"/>
+      <c r="BQ6" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
       <c r="BR6"/>
       <c r="BS6"/>
       <c r="BT6"/>
       <c r="BU6"/>
       <c r="BV6"/>
-      <c r="BW6"/>
-      <c r="BX6"/>
+      <c r="BW6" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX6" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY6"/>
       <c r="BZ6"/>
       <c r="CA6" s="3" t="inlineStr">
@@ -3381,12 +3409,12 @@
       </c>
       <c r="CB6" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>TED</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="CD6"/>
@@ -3423,10 +3451,10 @@
       <c r="CM6"/>
       <c r="CN6"/>
       <c r="CO6" s="4" t="n">
-        <v>40943.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP6" s="4" t="n">
-        <v>40943.0</v>
+        <v>39000.0</v>
       </c>
       <c r="CQ6"/>
       <c r="CR6"/>
@@ -3444,12 +3472,12 @@
       <c r="DD6"/>
       <c r="DE6"/>
       <c r="DF6"/>
-      <c r="DG6" s="3" t="inlineStr">
-        <is>
-          <t>20121092600001</t>
-        </is>
-      </c>
-      <c r="DH6"/>
+      <c r="DG6"/>
+      <c r="DH6" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI6"/>
       <c r="DJ6"/>
       <c r="DK6"/>
@@ -3457,12 +3485,12 @@
       <c r="DM6"/>
       <c r="DN6" s="3" t="inlineStr">
         <is>
-          <t>M25375</t>
+          <t>J020</t>
         </is>
       </c>
       <c r="DO6" s="3" t="inlineStr">
         <is>
-          <t>M19072</t>
+          <t>Z1159</t>
         </is>
       </c>
       <c r="DP6"/>
@@ -3489,58 +3517,22 @@
       <c r="EK6"/>
       <c r="EL6"/>
       <c r="EM6"/>
-      <c r="EN6" s="3" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="EO6" s="3" t="inlineStr">
-        <is>
-          <t>JONES</t>
-        </is>
-      </c>
-      <c r="EP6" s="3" t="inlineStr">
-        <is>
-          <t>BARNABY</t>
-        </is>
-      </c>
+      <c r="EN6"/>
+      <c r="EO6"/>
+      <c r="EP6"/>
       <c r="EQ6"/>
       <c r="ER6"/>
       <c r="ES6"/>
       <c r="ET6"/>
       <c r="EU6"/>
       <c r="EV6"/>
-      <c r="EW6" s="3" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="EX6" s="3" t="inlineStr">
-        <is>
-          <t>PHYSICIAN CLINIC</t>
-        </is>
-      </c>
-      <c r="EY6" s="3" t="inlineStr">
-        <is>
-          <t>234 SEAWAY ST</t>
-        </is>
-      </c>
+      <c r="EW6"/>
+      <c r="EX6"/>
+      <c r="EY6"/>
       <c r="EZ6"/>
-      <c r="FA6" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="FB6" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="FC6" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="FA6"/>
+      <c r="FB6"/>
+      <c r="FC6"/>
       <c r="FD6"/>
       <c r="FE6"/>
       <c r="FF6"/>
@@ -3569,70 +3561,22 @@
       <c r="GC6"/>
       <c r="GD6"/>
       <c r="GE6"/>
-      <c r="GF6" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="GG6" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="GH6" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="GF6"/>
+      <c r="GG6"/>
+      <c r="GH6"/>
       <c r="GI6"/>
-      <c r="GJ6" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="GK6" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL6" s="3" t="inlineStr">
-        <is>
-          <t>JS00111223333</t>
-        </is>
-      </c>
+      <c r="GJ6"/>
+      <c r="GK6"/>
+      <c r="GL6"/>
       <c r="GM6"/>
-      <c r="GN6" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO6" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
+      <c r="GN6"/>
+      <c r="GO6"/>
       <c r="GP6"/>
-      <c r="GQ6" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ6"/>
       <c r="GR6"/>
-      <c r="GS6" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT6" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU6" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="GS6"/>
+      <c r="GT6"/>
+      <c r="GU6"/>
       <c r="GV6"/>
       <c r="GW6"/>
       <c r="GX6"/>
@@ -3645,32 +3589,14 @@
       <c r="HE6"/>
       <c r="HF6"/>
       <c r="HG6"/>
-      <c r="HH6" s="1" t="n">
-        <v>75.0</v>
-      </c>
+      <c r="HH6"/>
       <c r="HI6"/>
       <c r="HJ6"/>
-      <c r="HK6" s="3" t="inlineStr">
-        <is>
-          <t>20121092600001</t>
-        </is>
-      </c>
-      <c r="HL6" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM6" s="3" t="inlineStr">
-        <is>
-          <t>59999</t>
-        </is>
-      </c>
+      <c r="HK6"/>
+      <c r="HL6"/>
+      <c r="HM6"/>
       <c r="HN6"/>
-      <c r="HO6" s="3" t="inlineStr">
-        <is>
-          <t>ABC PLAN</t>
-        </is>
-      </c>
+      <c r="HO6"/>
       <c r="HP6"/>
       <c r="HQ6"/>
       <c r="HR6"/>
@@ -3684,7 +3610,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ed5</t>
+          <t>6a04cc5a1ef26d534baf2b3b</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3694,7 +3620,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>commercial.dat</t>
+          <t>multi-tran.dat</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -3709,7 +3635,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -3719,12 +3645,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>CHARGEABLE</t>
+          <t>REPORTING</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="J7" s="1" t="n">
@@ -3783,7 +3709,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Ben Kildare Service</t>
+          <t>BEN KILDARE SERVICE</t>
         </is>
       </c>
       <c r="W7"/>
@@ -3811,7 +3737,7 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>103G00000X</t>
+          <t>103GC0700X</t>
         </is>
       </c>
       <c r="AE7"/>
@@ -3833,16 +3759,20 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT7"/>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2222-SJ</t>
+          <t>12312-A</t>
         </is>
       </c>
       <c r="AV7"/>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>HM</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -3852,18 +3782,18 @@
       </c>
       <c r="AY7" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
+          <t>00221111</t>
         </is>
       </c>
       <c r="AZ7"/>
       <c r="BA7" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>TED</t>
         </is>
       </c>
       <c r="BC7"/>
@@ -3872,14 +3802,30 @@
       </c>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
-        </is>
-      </c>
-      <c r="BF7"/>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="BF7" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="BG7"/>
-      <c r="BH7"/>
-      <c r="BI7"/>
-      <c r="BJ7"/>
+      <c r="BH7" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="BK7"/>
       <c r="BL7"/>
       <c r="BM7"/>
@@ -3890,13 +3836,13 @@
       </c>
       <c r="BO7" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>741234</t>
         </is>
       </c>
       <c r="BP7"/>
       <c r="BQ7" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCE COMPANY</t>
+          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
         </is>
       </c>
       <c r="BR7"/>
@@ -3904,63 +3850,21 @@
       <c r="BT7"/>
       <c r="BU7"/>
       <c r="BV7"/>
-      <c r="BW7" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX7" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW7"/>
+      <c r="BX7"/>
       <c r="BY7"/>
       <c r="BZ7"/>
-      <c r="CA7" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB7" s="3" t="inlineStr">
-        <is>
-          <t>Smith</t>
-        </is>
-      </c>
-      <c r="CC7" s="3" t="inlineStr">
-        <is>
-          <t>Ted</t>
-        </is>
-      </c>
+      <c r="CA7"/>
+      <c r="CB7"/>
+      <c r="CC7"/>
       <c r="CD7"/>
-      <c r="CE7" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF7" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG7" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE7"/>
+      <c r="CF7"/>
+      <c r="CG7"/>
       <c r="CH7"/>
-      <c r="CI7" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ7" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK7" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI7"/>
+      <c r="CJ7"/>
+      <c r="CK7"/>
       <c r="CL7"/>
       <c r="CM7"/>
       <c r="CN7"/>
@@ -3970,7 +3874,9 @@
       <c r="CP7" s="4" t="n">
         <v>39000.0</v>
       </c>
-      <c r="CQ7"/>
+      <c r="CQ7" s="4" t="n">
+        <v>36071.0</v>
+      </c>
       <c r="CR7"/>
       <c r="CS7"/>
       <c r="CT7"/>
@@ -3999,7 +3905,7 @@
       <c r="DM7"/>
       <c r="DN7" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
+          <t>G35</t>
         </is>
       </c>
       <c r="DO7" s="3" t="inlineStr">
@@ -4040,13 +3946,37 @@
       <c r="ET7"/>
       <c r="EU7"/>
       <c r="EV7"/>
-      <c r="EW7"/>
-      <c r="EX7"/>
-      <c r="EY7"/>
+      <c r="EW7" s="3" t="inlineStr">
+        <is>
+          <t>5812345679</t>
+        </is>
+      </c>
+      <c r="EX7" s="3" t="inlineStr">
+        <is>
+          <t>KILDARE ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="EY7" s="3" t="inlineStr">
+        <is>
+          <t>2345 OCEAN BLVD</t>
+        </is>
+      </c>
       <c r="EZ7"/>
-      <c r="FA7"/>
-      <c r="FB7"/>
-      <c r="FC7"/>
+      <c r="FA7" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="FB7" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="FC7" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="FD7"/>
       <c r="FE7"/>
       <c r="FF7"/>
@@ -4124,7 +4054,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4c</t>
+          <t>6a04cc5a1ef26d534baf2b3c</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4139,7 +4069,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -4149,26 +4079,26 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>007227</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2006-10-15T10:23:00</t>
+          <t>2005-02-15T07:54:20</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>REPORTING</t>
+          <t>CHARGEABLE</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="J8" s="1" t="n">
-        <v>100.0</v>
+        <v>145.5</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -4202,7 +4132,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R8"/>
@@ -4213,50 +4143,66 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>987654321</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
-        </is>
-      </c>
-      <c r="W8"/>
-      <c r="X8"/>
+          <t>GREENE</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1264 OAKWOOD AVE</t>
         </is>
       </c>
       <c r="Z8"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>103GC0700X</t>
-        </is>
-      </c>
-      <c r="AE8"/>
-      <c r="AF8"/>
-      <c r="AG8"/>
+          <t>21236</t>
+        </is>
+      </c>
+      <c r="AD8"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>4105551212</t>
+        </is>
+      </c>
       <c r="AH8"/>
       <c r="AI8"/>
       <c r="AJ8"/>
@@ -4278,15 +4224,11 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>12312-A</t>
-        </is>
-      </c>
+      <c r="AU8"/>
       <c r="AV8"/>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>HM</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -4296,23 +4238,27 @@
       </c>
       <c r="AY8" s="3" t="inlineStr">
         <is>
-          <t>00221111</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ8"/>
       <c r="BA8" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>WILLIAMSON</t>
         </is>
       </c>
       <c r="BB8" s="3" t="inlineStr">
         <is>
-          <t>TED</t>
-        </is>
-      </c>
-      <c r="BC8"/>
+          <t>MATTHEW</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
       <c r="BD8" s="4" t="n">
-        <v>15827.0</v>
+        <v>9142.0</v>
       </c>
       <c r="BE8" s="3" t="inlineStr">
         <is>
@@ -4321,23 +4267,23 @@
       </c>
       <c r="BF8" s="3" t="inlineStr">
         <is>
-          <t>236 N MAIN ST</t>
+          <t>128 BROADCREEK</t>
         </is>
       </c>
       <c r="BG8"/>
       <c r="BH8" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>BALTIMORE</t>
         </is>
       </c>
       <c r="BI8" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="BJ8" s="3" t="inlineStr">
         <is>
-          <t>33413</t>
+          <t>21234</t>
         </is>
       </c>
       <c r="BK8"/>
@@ -4350,13 +4296,13 @@
       </c>
       <c r="BO8" s="3" t="inlineStr">
         <is>
-          <t>741234</t>
+          <t>C12345</t>
         </is>
       </c>
       <c r="BP8"/>
       <c r="BQ8" s="3" t="inlineStr">
         <is>
-          <t>ALLIANCE HEALTH AND LIFE INSURANCE</t>
+          <t>MEDICARE PART B MARYLAND</t>
         </is>
       </c>
       <c r="BR8"/>
@@ -4383,20 +4329,24 @@
       <c r="CM8"/>
       <c r="CN8"/>
       <c r="CO8" s="4" t="n">
-        <v>38993.0</v>
+        <v>38398.0</v>
       </c>
       <c r="CP8" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="CQ8" s="4" t="n">
-        <v>36071.0</v>
-      </c>
-      <c r="CR8"/>
+        <v>38398.0</v>
+      </c>
+      <c r="CQ8"/>
+      <c r="CR8" s="4" t="n">
+        <v>38367.0</v>
+      </c>
       <c r="CS8"/>
-      <c r="CT8"/>
+      <c r="CT8" s="4" t="n">
+        <v>38362.0</v>
+      </c>
       <c r="CU8"/>
       <c r="CV8"/>
-      <c r="CW8"/>
+      <c r="CW8" s="4" t="n">
+        <v>38365.0</v>
+      </c>
       <c r="CX8"/>
       <c r="CY8"/>
       <c r="CZ8"/>
@@ -4407,11 +4357,7 @@
       <c r="DE8"/>
       <c r="DF8"/>
       <c r="DG8"/>
-      <c r="DH8" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DH8"/>
       <c r="DI8"/>
       <c r="DJ8"/>
       <c r="DK8"/>
@@ -4419,14 +4365,10 @@
       <c r="DM8"/>
       <c r="DN8" s="3" t="inlineStr">
         <is>
-          <t>G35</t>
-        </is>
-      </c>
-      <c r="DO8" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>M4820</t>
+        </is>
+      </c>
+      <c r="DO8"/>
       <c r="DP8"/>
       <c r="DQ8"/>
       <c r="DR8"/>
@@ -4460,37 +4402,13 @@
       <c r="ET8"/>
       <c r="EU8"/>
       <c r="EV8"/>
-      <c r="EW8" s="3" t="inlineStr">
-        <is>
-          <t>5812345679</t>
-        </is>
-      </c>
-      <c r="EX8" s="3" t="inlineStr">
-        <is>
-          <t>KILDARE ASSOCIATES</t>
-        </is>
-      </c>
-      <c r="EY8" s="3" t="inlineStr">
-        <is>
-          <t>2345 OCEAN BLVD</t>
-        </is>
-      </c>
+      <c r="EW8"/>
+      <c r="EX8"/>
+      <c r="EY8"/>
       <c r="EZ8"/>
-      <c r="FA8" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="FB8" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="FC8" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="FA8"/>
+      <c r="FB8"/>
+      <c r="FC8"/>
       <c r="FD8"/>
       <c r="FE8"/>
       <c r="FF8"/>
@@ -4568,7 +4486,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4d</t>
+          <t>6a04cc5a1ef26d534baf2b3d</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4583,7 +4501,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3701</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -4593,12 +4511,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>007227</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2005-02-15T07:54:20</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -4608,20 +4526,20 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J9" s="1" t="n">
-        <v>145.5</v>
+        <v>827.0</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -4657,66 +4575,46 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>987654321</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>GREENE</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
+          <t>PROVIDER MEDICAL GROUP</t>
+        </is>
+      </c>
+      <c r="W9"/>
+      <c r="X9"/>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>1264 OAKWOOD AVE</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z9"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="AD9"/>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t>4105551212</t>
-        </is>
-      </c>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
       <c r="AH9"/>
       <c r="AI9"/>
       <c r="AJ9"/>
@@ -4758,46 +4656,42 @@
       <c r="AZ9"/>
       <c r="BA9" s="3" t="inlineStr">
         <is>
-          <t>WILLIAMSON</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>MATTHEW</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
+          <t>MARGARET</t>
+        </is>
+      </c>
+      <c r="BC9"/>
       <c r="BD9" s="4" t="n">
-        <v>9142.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="BF9" s="3" t="inlineStr">
         <is>
-          <t>128 BROADCREEK</t>
+          <t>123 RAINBOW ROAD</t>
         </is>
       </c>
       <c r="BG9"/>
       <c r="BH9" s="3" t="inlineStr">
         <is>
-          <t>BALTIMORE</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="BI9" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="BJ9" s="3" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="BK9"/>
@@ -4810,13 +4704,13 @@
       </c>
       <c r="BO9" s="3" t="inlineStr">
         <is>
-          <t>C12345</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP9"/>
       <c r="BQ9" s="3" t="inlineStr">
         <is>
-          <t>MEDICARE PART B MARYLAND</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR9"/>
@@ -4843,24 +4737,18 @@
       <c r="CM9"/>
       <c r="CN9"/>
       <c r="CO9" s="4" t="n">
-        <v>38398.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP9" s="4" t="n">
-        <v>38398.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ9"/>
-      <c r="CR9" s="4" t="n">
-        <v>38367.0</v>
-      </c>
+      <c r="CR9"/>
       <c r="CS9"/>
-      <c r="CT9" s="4" t="n">
-        <v>38362.0</v>
-      </c>
+      <c r="CT9"/>
       <c r="CU9"/>
       <c r="CV9"/>
-      <c r="CW9" s="4" t="n">
-        <v>38365.0</v>
-      </c>
+      <c r="CW9"/>
       <c r="CX9"/>
       <c r="CY9"/>
       <c r="CZ9"/>
@@ -4879,7 +4767,7 @@
       <c r="DM9"/>
       <c r="DN9" s="3" t="inlineStr">
         <is>
-          <t>M4820</t>
+          <t>E15</t>
         </is>
       </c>
       <c r="DO9"/>
@@ -4907,22 +4795,74 @@
       <c r="EK9"/>
       <c r="EL9"/>
       <c r="EM9"/>
-      <c r="EN9"/>
-      <c r="EO9"/>
-      <c r="EP9"/>
-      <c r="EQ9"/>
-      <c r="ER9"/>
-      <c r="ES9"/>
-      <c r="ET9"/>
+      <c r="EN9" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO9" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP9" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ9" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER9" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES9" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET9" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU9"/>
       <c r="EV9"/>
-      <c r="EW9"/>
-      <c r="EX9"/>
-      <c r="EY9"/>
+      <c r="EW9" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX9" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY9" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ9"/>
-      <c r="FA9"/>
-      <c r="FB9"/>
-      <c r="FC9"/>
+      <c r="FA9" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB9" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC9" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD9"/>
       <c r="FE9"/>
       <c r="FF9"/>
@@ -5000,7 +4940,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4e</t>
+          <t>6a04cc5a1ef26d534baf2b70</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5010,12 +4950,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>multi-tran.dat</t>
+          <t>commercial-replacement.dat</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -5025,12 +4965,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2006-11-15T10:23:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -5040,25 +4980,25 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J10" s="1" t="n">
-        <v>827.0</v>
+        <v>100.0</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -5078,7 +5018,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R10"/>
@@ -5089,43 +5029,47 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
+          <t>BEN KILDARE SERVICE</t>
         </is>
       </c>
       <c r="W10"/>
       <c r="X10"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z10"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
-        </is>
-      </c>
-      <c r="AD10"/>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>103GC0700X</t>
+        </is>
+      </c>
       <c r="AE10"/>
       <c r="AF10"/>
       <c r="AG10"/>
@@ -5145,16 +5089,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU10"/>
+      <c r="AT10"/>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>2222-SJ</t>
+        </is>
+      </c>
       <c r="AV10"/>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -5164,50 +5108,34 @@
       </c>
       <c r="AY10" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ10"/>
       <c r="BA10" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
+          <t>JANE</t>
         </is>
       </c>
       <c r="BC10"/>
       <c r="BD10" s="4" t="n">
-        <v>27091.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
-        <is>
-          <t>123 RAINBOW ROAD</t>
-        </is>
-      </c>
+      <c r="BF10"/>
       <c r="BG10"/>
-      <c r="BH10" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="BI10" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="BJ10" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
       <c r="BK10"/>
       <c r="BL10"/>
       <c r="BM10"/>
@@ -5218,13 +5146,13 @@
       </c>
       <c r="BO10" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP10"/>
       <c r="BQ10" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>KEY INSURANCECOMPANY</t>
         </is>
       </c>
       <c r="BR10"/>
@@ -5232,29 +5160,71 @@
       <c r="BT10"/>
       <c r="BU10"/>
       <c r="BV10"/>
-      <c r="BW10"/>
-      <c r="BX10"/>
+      <c r="BW10" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX10" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="BY10"/>
       <c r="BZ10"/>
-      <c r="CA10"/>
-      <c r="CB10"/>
-      <c r="CC10"/>
+      <c r="CA10" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB10" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC10" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD10"/>
-      <c r="CE10"/>
-      <c r="CF10"/>
-      <c r="CG10"/>
+      <c r="CE10" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF10" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG10" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH10"/>
-      <c r="CI10"/>
-      <c r="CJ10"/>
-      <c r="CK10"/>
+      <c r="CI10" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ10" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK10" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL10"/>
       <c r="CM10"/>
       <c r="CN10"/>
       <c r="CO10" s="4" t="n">
-        <v>38364.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP10" s="4" t="n">
-        <v>38365.0</v>
+        <v>39000.0</v>
       </c>
       <c r="CQ10"/>
       <c r="CR10"/>
@@ -5273,7 +5243,11 @@
       <c r="DE10"/>
       <c r="DF10"/>
       <c r="DG10"/>
-      <c r="DH10"/>
+      <c r="DH10" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI10"/>
       <c r="DJ10"/>
       <c r="DK10"/>
@@ -5281,10 +5255,14 @@
       <c r="DM10"/>
       <c r="DN10" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="DO10"/>
+          <t>J020</t>
+        </is>
+      </c>
+      <c r="DO10" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP10"/>
       <c r="DQ10"/>
       <c r="DR10"/>
@@ -5309,74 +5287,22 @@
       <c r="EK10"/>
       <c r="EL10"/>
       <c r="EM10"/>
-      <c r="EN10" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO10" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP10" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ10" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER10" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES10" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET10" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN10"/>
+      <c r="EO10"/>
+      <c r="EP10"/>
+      <c r="EQ10"/>
+      <c r="ER10"/>
+      <c r="ES10"/>
+      <c r="ET10"/>
       <c r="EU10"/>
       <c r="EV10"/>
-      <c r="EW10" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX10" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY10" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW10"/>
+      <c r="EX10"/>
+      <c r="EY10"/>
       <c r="EZ10"/>
-      <c r="FA10" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB10" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC10" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA10"/>
+      <c r="FB10"/>
+      <c r="FC10"/>
       <c r="FD10"/>
       <c r="FE10"/>
       <c r="FF10"/>
@@ -5454,7 +5380,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f81</t>
+          <t>6a04cc5a1ef26d534baf2b9d</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5464,12 +5390,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>commercial-replacement.dat</t>
+          <t>anesthesia.dat</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>0001</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5479,12 +5405,12 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2006-11-15T10:23:00</t>
+          <t>2005-01-17T10:23:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -5494,25 +5420,25 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>100.0</v>
+        <v>827.0</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>OUTPATIENT</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -5532,7 +5458,7 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R11"/>
@@ -5543,47 +5469,43 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>2366554859</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>756473826</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>BEN KILDARE SERVICE</t>
+          <t>PROVIDER MEDICAL GROUP</t>
         </is>
       </c>
       <c r="W11"/>
       <c r="X11"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1234 WESTEND AVE</t>
         </is>
       </c>
       <c r="Z11"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>NASHVILLE</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>103GC0700X</t>
-        </is>
-      </c>
+          <t>37232</t>
+        </is>
+      </c>
+      <c r="AD11"/>
       <c r="AE11"/>
       <c r="AF11"/>
       <c r="AG11"/>
@@ -5603,16 +5525,16 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT11"/>
-      <c r="AU11" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU11"/>
       <c r="AV11"/>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MB</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -5622,34 +5544,50 @@
       </c>
       <c r="AY11" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
+          <t>123456789A</t>
         </is>
       </c>
       <c r="AZ11"/>
       <c r="BA11" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>JONES</t>
         </is>
       </c>
       <c r="BB11" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>MARGARET</t>
         </is>
       </c>
       <c r="BC11"/>
       <c r="BD11" s="4" t="n">
-        <v>15827.0</v>
+        <v>27091.0</v>
       </c>
       <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF11"/>
+      <c r="BF11" s="3" t="inlineStr">
+        <is>
+          <t>123 RAINBOW ROAD</t>
+        </is>
+      </c>
       <c r="BG11"/>
-      <c r="BH11"/>
-      <c r="BI11"/>
-      <c r="BJ11"/>
+      <c r="BH11" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="BK11"/>
       <c r="BL11"/>
       <c r="BM11"/>
@@ -5660,13 +5598,13 @@
       </c>
       <c r="BO11" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>05440</t>
         </is>
       </c>
       <c r="BP11"/>
       <c r="BQ11" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCECOMPANY</t>
+          <t>ABC PAYER</t>
         </is>
       </c>
       <c r="BR11"/>
@@ -5674,71 +5612,29 @@
       <c r="BT11"/>
       <c r="BU11"/>
       <c r="BV11"/>
-      <c r="BW11" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX11" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="BW11"/>
+      <c r="BX11"/>
       <c r="BY11"/>
       <c r="BZ11"/>
-      <c r="CA11" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB11" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC11" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA11"/>
+      <c r="CB11"/>
+      <c r="CC11"/>
       <c r="CD11"/>
-      <c r="CE11" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF11" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG11" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE11"/>
+      <c r="CF11"/>
+      <c r="CG11"/>
       <c r="CH11"/>
-      <c r="CI11" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ11" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK11" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI11"/>
+      <c r="CJ11"/>
+      <c r="CK11"/>
       <c r="CL11"/>
       <c r="CM11"/>
       <c r="CN11"/>
       <c r="CO11" s="4" t="n">
-        <v>38993.0</v>
+        <v>38364.0</v>
       </c>
       <c r="CP11" s="4" t="n">
-        <v>39000.0</v>
+        <v>38365.0</v>
       </c>
       <c r="CQ11"/>
       <c r="CR11"/>
@@ -5757,11 +5653,7 @@
       <c r="DE11"/>
       <c r="DF11"/>
       <c r="DG11"/>
-      <c r="DH11" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DH11"/>
       <c r="DI11"/>
       <c r="DJ11"/>
       <c r="DK11"/>
@@ -5769,14 +5661,10 @@
       <c r="DM11"/>
       <c r="DN11" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
-        </is>
-      </c>
-      <c r="DO11" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="DO11"/>
       <c r="DP11"/>
       <c r="DQ11"/>
       <c r="DR11"/>
@@ -5801,22 +5689,74 @@
       <c r="EK11"/>
       <c r="EL11"/>
       <c r="EM11"/>
-      <c r="EN11"/>
-      <c r="EO11"/>
-      <c r="EP11"/>
-      <c r="EQ11"/>
-      <c r="ER11"/>
-      <c r="ES11"/>
-      <c r="ET11"/>
+      <c r="EN11" s="3" t="inlineStr">
+        <is>
+          <t>5678912345</t>
+        </is>
+      </c>
+      <c r="EO11" s="3" t="inlineStr">
+        <is>
+          <t>TOWNSEND</t>
+        </is>
+      </c>
+      <c r="EP11" s="3" t="inlineStr">
+        <is>
+          <t>JACOB</t>
+        </is>
+      </c>
+      <c r="EQ11" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="ER11" s="3" t="inlineStr">
+        <is>
+          <t>207L00000X</t>
+        </is>
+      </c>
+      <c r="ES11" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET11" s="3" t="inlineStr">
+        <is>
+          <t>A41234</t>
+        </is>
+      </c>
       <c r="EU11"/>
       <c r="EV11"/>
-      <c r="EW11"/>
-      <c r="EX11"/>
-      <c r="EY11"/>
+      <c r="EW11" s="3" t="inlineStr">
+        <is>
+          <t>432198765</t>
+        </is>
+      </c>
+      <c r="EX11" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER OP HOSP</t>
+        </is>
+      </c>
+      <c r="EY11" s="3" t="inlineStr">
+        <is>
+          <t>345 MAIN DRIVE</t>
+        </is>
+      </c>
       <c r="EZ11"/>
-      <c r="FA11"/>
-      <c r="FB11"/>
-      <c r="FC11"/>
+      <c r="FA11" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="FB11" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="FC11" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="FD11"/>
       <c r="FE11"/>
       <c r="FF11"/>
@@ -5894,7 +5834,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17fae</t>
+          <t>6a04cc5a1ef26d534baf2bd8</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -5904,12 +5844,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>anesthesia.dat</t>
+          <t>wheelchair.dat</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0001</t>
+          <t>112233</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5919,12 +5859,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2005-01-17T10:23:00</t>
+          <t>2005-03-26T10:36:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -5934,20 +5874,20 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="J12" s="1" t="n">
-        <v>827.0</v>
+        <v>75.0</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>OUTPATIENT</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -5983,40 +5923,40 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2366554859</t>
+          <t>7778889999</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>756473826</t>
+          <t>123567989</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>PROVIDER MEDICAL GROUP</t>
+          <t>XYZ WHEELCHAIR INC</t>
         </is>
       </c>
       <c r="W12"/>
       <c r="X12"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>1234 WESTEND AVE</t>
+          <t>1440 NORTH STREET</t>
         </is>
       </c>
       <c r="Z12"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>LAFAYETTE</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="AD12"/>
@@ -6030,8 +5970,16 @@
       <c r="AL12"/>
       <c r="AM12"/>
       <c r="AN12"/>
-      <c r="AO12"/>
-      <c r="AP12"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>0426960001</t>
+        </is>
+      </c>
       <c r="AQ12"/>
       <c r="AR12"/>
       <c r="AS12" s="3" t="inlineStr">
@@ -6058,52 +6006,54 @@
       </c>
       <c r="AY12" s="3" t="inlineStr">
         <is>
-          <t>123456789A</t>
+          <t>987654321A</t>
         </is>
       </c>
       <c r="AZ12"/>
       <c r="BA12" s="3" t="inlineStr">
         <is>
-          <t>JONES</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB12" s="3" t="inlineStr">
         <is>
-          <t>MARGARET</t>
+          <t>JAMES</t>
         </is>
       </c>
       <c r="BC12"/>
       <c r="BD12" s="4" t="n">
-        <v>27091.0</v>
+        <v>7602.0</v>
       </c>
       <c r="BE12" s="3" t="inlineStr">
         <is>
-          <t>FEMALE</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="BF12" s="3" t="inlineStr">
         <is>
-          <t>123 RAINBOW ROAD</t>
+          <t>12 MAIN ST</t>
         </is>
       </c>
       <c r="BG12"/>
       <c r="BH12" s="3" t="inlineStr">
         <is>
-          <t>NASHVILLE</t>
+          <t>FRANKFORT</t>
         </is>
       </c>
       <c r="BI12" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="BJ12" s="3" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>46209</t>
         </is>
       </c>
       <c r="BK12"/>
-      <c r="BL12"/>
+      <c r="BL12" t="n">
+        <v>155.0</v>
+      </c>
       <c r="BM12"/>
       <c r="BN12" s="3" t="inlineStr">
         <is>
@@ -6112,13 +6062,13 @@
       </c>
       <c r="BO12" s="3" t="inlineStr">
         <is>
-          <t>05440</t>
+          <t>99999</t>
         </is>
       </c>
       <c r="BP12"/>
       <c r="BQ12" s="3" t="inlineStr">
         <is>
-          <t>ABC PAYER</t>
+          <t>DMERC CARRIER</t>
         </is>
       </c>
       <c r="BR12"/>
@@ -6145,10 +6095,10 @@
       <c r="CM12"/>
       <c r="CN12"/>
       <c r="CO12" s="4" t="n">
-        <v>38364.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CP12" s="4" t="n">
-        <v>38365.0</v>
+        <v>38432.0</v>
       </c>
       <c r="CQ12"/>
       <c r="CR12"/>
@@ -6175,10 +6125,14 @@
       <c r="DM12"/>
       <c r="DN12" s="3" t="inlineStr">
         <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="DO12"/>
+          <t>I6789</t>
+        </is>
+      </c>
+      <c r="DO12" s="3" t="inlineStr">
+        <is>
+          <t>G839</t>
+        </is>
+      </c>
       <c r="DP12"/>
       <c r="DQ12"/>
       <c r="DR12"/>
@@ -6203,74 +6157,22 @@
       <c r="EK12"/>
       <c r="EL12"/>
       <c r="EM12"/>
-      <c r="EN12" s="3" t="inlineStr">
-        <is>
-          <t>5678912345</t>
-        </is>
-      </c>
-      <c r="EO12" s="3" t="inlineStr">
-        <is>
-          <t>TOWNSEND</t>
-        </is>
-      </c>
-      <c r="EP12" s="3" t="inlineStr">
-        <is>
-          <t>JACOB</t>
-        </is>
-      </c>
-      <c r="EQ12" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="ER12" s="3" t="inlineStr">
-        <is>
-          <t>207L00000X</t>
-        </is>
-      </c>
-      <c r="ES12" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET12" s="3" t="inlineStr">
-        <is>
-          <t>A41234</t>
-        </is>
-      </c>
+      <c r="EN12"/>
+      <c r="EO12"/>
+      <c r="EP12"/>
+      <c r="EQ12"/>
+      <c r="ER12"/>
+      <c r="ES12"/>
+      <c r="ET12"/>
       <c r="EU12"/>
       <c r="EV12"/>
-      <c r="EW12" s="3" t="inlineStr">
-        <is>
-          <t>432198765</t>
-        </is>
-      </c>
-      <c r="EX12" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER OP HOSP</t>
-        </is>
-      </c>
-      <c r="EY12" s="3" t="inlineStr">
-        <is>
-          <t>345 MAIN DRIVE</t>
-        </is>
-      </c>
+      <c r="EW12"/>
+      <c r="EX12"/>
+      <c r="EY12"/>
       <c r="EZ12"/>
-      <c r="FA12" s="3" t="inlineStr">
-        <is>
-          <t>NASHVILLE</t>
-        </is>
-      </c>
-      <c r="FB12" s="3" t="inlineStr">
-        <is>
-          <t>TN</t>
-        </is>
-      </c>
-      <c r="FC12" s="3" t="inlineStr">
-        <is>
-          <t>37232</t>
-        </is>
-      </c>
+      <c r="FA12"/>
+      <c r="FB12"/>
+      <c r="FC12"/>
       <c r="FD12"/>
       <c r="FE12"/>
       <c r="FF12"/>
@@ -6348,7 +6250,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17fe9</t>
+          <t>6a04cc5a1ef26d534baf2c08</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6358,12 +6260,12 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>wheelchair.dat</t>
+          <t>ppo-repriced.dat</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -6373,12 +6275,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2005-03-26T10:36:00</t>
+          <t>2005-06-20T09:46:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -6388,20 +6290,20 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="J13" s="1" t="n">
-        <v>75.0</v>
+        <v>28.75</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -6437,30 +6339,30 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>7778889999</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>123567989</t>
+          <t>555512345</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>XYZ WHEELCHAIR INC</t>
+          <t>HAPPY DOCTORS GROUP PRACTICE</t>
         </is>
       </c>
       <c r="W13"/>
       <c r="X13"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>1440 NORTH STREET</t>
+          <t>P O BOX 123</t>
         </is>
       </c>
       <c r="Z13"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>LAFAYETTE</t>
+          <t>FORT WAYNE</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
@@ -6470,13 +6372,25 @@
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>462540000</t>
         </is>
       </c>
       <c r="AD13"/>
-      <c r="AE13"/>
-      <c r="AF13"/>
-      <c r="AG13"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>SUE BILLINGSWORTH</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>8881231234</t>
+        </is>
+      </c>
       <c r="AH13"/>
       <c r="AI13"/>
       <c r="AJ13"/>
@@ -6484,16 +6398,8 @@
       <c r="AL13"/>
       <c r="AM13"/>
       <c r="AN13"/>
-      <c r="AO13" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>0426960001</t>
-        </is>
-      </c>
+      <c r="AO13"/>
+      <c r="AP13"/>
       <c r="AQ13"/>
       <c r="AR13"/>
       <c r="AS13" s="3" t="inlineStr">
@@ -6506,11 +6412,15 @@
           <t>SELF</t>
         </is>
       </c>
-      <c r="AU13"/>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>123XYZ</t>
+        </is>
+      </c>
       <c r="AV13"/>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>MB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -6520,38 +6430,42 @@
       </c>
       <c r="AY13" s="3" t="inlineStr">
         <is>
-          <t>987654321A</t>
+          <t>00124A089</t>
         </is>
       </c>
       <c r="AZ13"/>
       <c r="BA13" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>RING</t>
         </is>
       </c>
       <c r="BB13" s="3" t="inlineStr">
         <is>
-          <t>JAMES</t>
-        </is>
-      </c>
-      <c r="BC13"/>
+          <t>DIAMOND</t>
+        </is>
+      </c>
+      <c r="BC13" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="BD13" s="4" t="n">
-        <v>7602.0</v>
+        <v>14974.0</v>
       </c>
       <c r="BE13" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="BF13" s="3" t="inlineStr">
         <is>
-          <t>12 MAIN ST</t>
+          <t>123 EXAMPLE DRIVE</t>
         </is>
       </c>
       <c r="BG13"/>
       <c r="BH13" s="3" t="inlineStr">
         <is>
-          <t>FRANKFORT</t>
+          <t>INDIANAPOLIS</t>
         </is>
       </c>
       <c r="BI13" s="3" t="inlineStr">
@@ -6561,13 +6475,11 @@
       </c>
       <c r="BJ13" s="3" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>462290000</t>
         </is>
       </c>
       <c r="BK13"/>
-      <c r="BL13" t="n">
-        <v>155.0</v>
-      </c>
+      <c r="BL13"/>
       <c r="BM13"/>
       <c r="BN13" s="3" t="inlineStr">
         <is>
@@ -6576,13 +6488,13 @@
       </c>
       <c r="BO13" s="3" t="inlineStr">
         <is>
-          <t>99999</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="BP13"/>
       <c r="BQ13" s="3" t="inlineStr">
         <is>
-          <t>DMERC CARRIER</t>
+          <t>EXTRA HEALTHY INSURANCE</t>
         </is>
       </c>
       <c r="BR13"/>
@@ -6609,10 +6521,10 @@
       <c r="CM13"/>
       <c r="CN13"/>
       <c r="CO13" s="4" t="n">
-        <v>38432.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CP13" s="4" t="n">
-        <v>38432.0</v>
+        <v>38486.0</v>
       </c>
       <c r="CQ13"/>
       <c r="CR13"/>
@@ -6631,20 +6543,28 @@
       <c r="DE13"/>
       <c r="DF13"/>
       <c r="DG13"/>
-      <c r="DH13"/>
-      <c r="DI13"/>
+      <c r="DH13" s="3" t="inlineStr">
+        <is>
+          <t>061505501749388</t>
+        </is>
+      </c>
+      <c r="DI13" s="3" t="inlineStr">
+        <is>
+          <t>0902352342</t>
+        </is>
+      </c>
       <c r="DJ13"/>
       <c r="DK13"/>
       <c r="DL13"/>
       <c r="DM13"/>
       <c r="DN13" s="3" t="inlineStr">
         <is>
-          <t>I6789</t>
+          <t>J449</t>
         </is>
       </c>
       <c r="DO13" s="3" t="inlineStr">
         <is>
-          <t>G839</t>
+          <t>E119</t>
         </is>
       </c>
       <c r="DP13"/>
@@ -6663,30 +6583,78 @@
       <c r="EC13"/>
       <c r="ED13"/>
       <c r="EE13"/>
-      <c r="EF13"/>
-      <c r="EG13"/>
-      <c r="EH13"/>
+      <c r="EF13" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="EG13" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH13" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="EI13"/>
       <c r="EJ13"/>
       <c r="EK13"/>
       <c r="EL13"/>
       <c r="EM13"/>
-      <c r="EN13"/>
-      <c r="EO13"/>
-      <c r="EP13"/>
-      <c r="EQ13"/>
+      <c r="EN13" s="3" t="inlineStr">
+        <is>
+          <t>1122334455</t>
+        </is>
+      </c>
+      <c r="EO13" s="3" t="inlineStr">
+        <is>
+          <t>ANTHONY</t>
+        </is>
+      </c>
+      <c r="EP13" s="3" t="inlineStr">
+        <is>
+          <t>SUSAN</t>
+        </is>
+      </c>
+      <c r="EQ13" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="ER13"/>
       <c r="ES13"/>
       <c r="ET13"/>
       <c r="EU13"/>
       <c r="EV13"/>
       <c r="EW13"/>
-      <c r="EX13"/>
-      <c r="EY13"/>
+      <c r="EX13" s="3" t="inlineStr">
+        <is>
+          <t>HAPPY DOCTORS GROUP</t>
+        </is>
+      </c>
+      <c r="EY13" s="3" t="inlineStr">
+        <is>
+          <t>123 FEEL GOOD ROAD</t>
+        </is>
+      </c>
       <c r="EZ13"/>
-      <c r="FA13"/>
-      <c r="FB13"/>
-      <c r="FC13"/>
+      <c r="FA13" s="3" t="inlineStr">
+        <is>
+          <t>WASHINGTON</t>
+        </is>
+      </c>
+      <c r="FB13" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="FC13" s="3" t="inlineStr">
+        <is>
+          <t>475010000</t>
+        </is>
+      </c>
       <c r="FD13"/>
       <c r="FE13"/>
       <c r="FF13"/>
@@ -6764,7 +6732,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18019</t>
+          <t>6a04cc5a1ef26d534baf2c43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6774,12 +6742,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ppo-repriced.dat</t>
+          <t>cob-prov-payera.dat</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>0021</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -6789,12 +6757,12 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>0123</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2005-06-20T09:46:00</t>
+          <t>2005-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -6804,11 +6772,11 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="J14" s="1" t="n">
-        <v>28.75</v>
+        <v>79.04</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -6842,7 +6810,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>I</t>
         </is>
       </c>
       <c r="R14"/>
@@ -6853,46 +6821,50 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>1234567890</t>
+          <t>1999996666</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>555512345</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>HAPPY DOCTORS GROUP PRACTICE</t>
-        </is>
-      </c>
-      <c r="W14"/>
+          <t>KILDARE</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>BEN</t>
+        </is>
+      </c>
       <c r="X14"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>P O BOX 123</t>
+          <t>1234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z14"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>FORT WAYNE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>462540000</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="AD14"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>SUE BILLINGSWORTH</t>
+          <t>CONNIE</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -6902,7 +6874,7 @@
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>8881231234</t>
+          <t>3055551234</t>
         </is>
       </c>
       <c r="AH14"/>
@@ -6921,22 +6893,10 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="AU14" s="3" t="inlineStr">
-        <is>
-          <t>123XYZ</t>
-        </is>
-      </c>
+      <c r="AT14"/>
+      <c r="AU14"/>
       <c r="AV14"/>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
+      <c r="AW14"/>
       <c r="AX14" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -6944,54 +6904,34 @@
       </c>
       <c r="AY14" s="3" t="inlineStr">
         <is>
-          <t>00124A089</t>
+          <t>111223333</t>
         </is>
       </c>
       <c r="AZ14"/>
       <c r="BA14" s="3" t="inlineStr">
         <is>
-          <t>RING</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB14" s="3" t="inlineStr">
         <is>
-          <t>DIAMOND</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC14"/>
       <c r="BD14" s="4" t="n">
-        <v>14974.0</v>
+        <v>15827.0</v>
       </c>
       <c r="BE14" s="3" t="inlineStr">
         <is>
           <t>FEMALE</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr">
-        <is>
-          <t>123 EXAMPLE DRIVE</t>
-        </is>
-      </c>
+      <c r="BF14"/>
       <c r="BG14"/>
-      <c r="BH14" s="3" t="inlineStr">
-        <is>
-          <t>INDIANAPOLIS</t>
-        </is>
-      </c>
-      <c r="BI14" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="BJ14" s="3" t="inlineStr">
-        <is>
-          <t>462290000</t>
-        </is>
-      </c>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
       <c r="BK14"/>
       <c r="BL14"/>
       <c r="BM14"/>
@@ -7002,43 +6942,101 @@
       </c>
       <c r="BO14" s="3" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>999996666</t>
         </is>
       </c>
       <c r="BP14"/>
       <c r="BQ14" s="3" t="inlineStr">
         <is>
-          <t>EXTRA HEALTHY INSURANCE</t>
-        </is>
-      </c>
-      <c r="BR14"/>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
+      <c r="BR14" s="3" t="inlineStr">
+        <is>
+          <t>3333OCEAN ST</t>
+        </is>
+      </c>
       <c r="BS14"/>
-      <c r="BT14"/>
-      <c r="BU14"/>
-      <c r="BV14"/>
-      <c r="BW14"/>
-      <c r="BX14"/>
+      <c r="BT14" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH MIAMI</t>
+        </is>
+      </c>
+      <c r="BU14" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV14" s="3" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="BW14" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX14" s="3" t="inlineStr">
+        <is>
+          <t>PBS3334</t>
+        </is>
+      </c>
       <c r="BY14"/>
       <c r="BZ14"/>
-      <c r="CA14"/>
-      <c r="CB14"/>
-      <c r="CC14"/>
+      <c r="CA14" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB14" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC14" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD14"/>
-      <c r="CE14"/>
-      <c r="CF14"/>
-      <c r="CG14"/>
+      <c r="CE14" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF14" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG14" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH14"/>
-      <c r="CI14"/>
-      <c r="CJ14"/>
-      <c r="CK14"/>
+      <c r="CI14" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ14" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK14" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
       <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14"/>
       <c r="CO14" s="4" t="n">
-        <v>38486.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CP14" s="4" t="n">
-        <v>38486.0</v>
+        <v>38628.0</v>
       </c>
       <c r="CQ14"/>
       <c r="CR14"/>
@@ -7057,31 +7055,27 @@
       <c r="DE14"/>
       <c r="DF14"/>
       <c r="DG14"/>
-      <c r="DH14" s="3" t="inlineStr">
-        <is>
-          <t>061505501749388</t>
-        </is>
-      </c>
-      <c r="DI14" s="3" t="inlineStr">
-        <is>
-          <t>0902352342</t>
-        </is>
-      </c>
+      <c r="DH14"/>
+      <c r="DI14"/>
       <c r="DJ14"/>
       <c r="DK14"/>
       <c r="DL14"/>
       <c r="DM14"/>
       <c r="DN14" s="3" t="inlineStr">
         <is>
-          <t>J449</t>
+          <t>J309</t>
         </is>
       </c>
       <c r="DO14" s="3" t="inlineStr">
         <is>
-          <t>E119</t>
-        </is>
-      </c>
-      <c r="DP14"/>
+          <t>E785</t>
+        </is>
+      </c>
+      <c r="DP14" s="3" t="inlineStr">
+        <is>
+          <t>E663</t>
+        </is>
+      </c>
       <c r="DQ14"/>
       <c r="DR14"/>
       <c r="DS14"/>
@@ -7097,21 +7091,9 @@
       <c r="EC14"/>
       <c r="ED14"/>
       <c r="EE14"/>
-      <c r="EF14" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="EG14" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH14" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="EF14"/>
+      <c r="EG14"/>
+      <c r="EH14"/>
       <c r="EI14"/>
       <c r="EJ14"/>
       <c r="EK14"/>
@@ -7119,54 +7101,66 @@
       <c r="EM14"/>
       <c r="EN14" s="3" t="inlineStr">
         <is>
-          <t>1122334455</t>
+          <t>1999996666</t>
         </is>
       </c>
       <c r="EO14" s="3" t="inlineStr">
         <is>
-          <t>ANTHONY</t>
+          <t>KILDARE</t>
         </is>
       </c>
       <c r="EP14" s="3" t="inlineStr">
         <is>
-          <t>SUSAN</t>
-        </is>
-      </c>
-      <c r="EQ14" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="ER14"/>
-      <c r="ES14"/>
-      <c r="ET14"/>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="EQ14"/>
+      <c r="ER14" s="3" t="inlineStr">
+        <is>
+          <t>204C00000X</t>
+        </is>
+      </c>
+      <c r="ES14" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET14" s="3" t="inlineStr">
+        <is>
+          <t>KA6663</t>
+        </is>
+      </c>
       <c r="EU14"/>
       <c r="EV14"/>
-      <c r="EW14"/>
+      <c r="EW14" s="3" t="inlineStr">
+        <is>
+          <t>1581234567</t>
+        </is>
+      </c>
       <c r="EX14" s="3" t="inlineStr">
         <is>
-          <t>HAPPY DOCTORS GROUP</t>
+          <t>KILDARE ASSOCIATES</t>
         </is>
       </c>
       <c r="EY14" s="3" t="inlineStr">
         <is>
-          <t>123 FEEL GOOD ROAD</t>
+          <t>2345 OCEAN BLVD</t>
         </is>
       </c>
       <c r="EZ14"/>
       <c r="FA14" s="3" t="inlineStr">
         <is>
-          <t>WASHINGTON</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="FB14" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="FC14" s="3" t="inlineStr">
         <is>
-          <t>475010000</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="FD14"/>
@@ -7197,22 +7191,66 @@
       <c r="GC14"/>
       <c r="GD14"/>
       <c r="GE14"/>
-      <c r="GF14"/>
-      <c r="GG14"/>
+      <c r="GF14" s="3" t="inlineStr">
+        <is>
+          <t>SECONDARY</t>
+        </is>
+      </c>
+      <c r="GG14" s="3" t="inlineStr">
+        <is>
+          <t>SPOUSE</t>
+        </is>
+      </c>
       <c r="GH14"/>
       <c r="GI14"/>
-      <c r="GJ14"/>
-      <c r="GK14"/>
-      <c r="GL14"/>
+      <c r="GJ14" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="GK14" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL14" s="3" t="inlineStr">
+        <is>
+          <t>T55TY666</t>
+        </is>
+      </c>
       <c r="GM14"/>
-      <c r="GN14"/>
-      <c r="GO14"/>
+      <c r="GN14" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO14" s="3" t="inlineStr">
+        <is>
+          <t>JACK</t>
+        </is>
+      </c>
       <c r="GP14"/>
-      <c r="GQ14"/>
+      <c r="GQ14" s="3" t="inlineStr">
+        <is>
+          <t>236 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR14"/>
-      <c r="GS14"/>
-      <c r="GT14"/>
-      <c r="GU14"/>
+      <c r="GS14" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT14" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU14" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="GV14"/>
       <c r="GW14"/>
       <c r="GX14"/>
@@ -7229,10 +7267,22 @@
       <c r="HI14"/>
       <c r="HJ14"/>
       <c r="HK14"/>
-      <c r="HL14"/>
-      <c r="HM14"/>
+      <c r="HL14" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM14" s="3" t="inlineStr">
+        <is>
+          <t>999996666</t>
+        </is>
+      </c>
       <c r="HN14"/>
-      <c r="HO14"/>
+      <c r="HO14" s="3" t="inlineStr">
+        <is>
+          <t>KEY INSURANCE COMPANY</t>
+        </is>
+      </c>
       <c r="HP14"/>
       <c r="HQ14"/>
       <c r="HR14"/>
@@ -7246,7 +7296,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18054</t>
+          <t>6a04cc5a1ef26d534baf2c67</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7256,7 +7306,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>cob-prov-payera.dat</t>
+          <t>837P-minimal.dat</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -7271,12 +7321,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2005-10-15T10:23:00</t>
+          <t>2006-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -7286,11 +7336,11 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="J15" s="1" t="n">
-        <v>79.04</v>
+        <v>100.0</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -7335,28 +7385,24 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>1999996666</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>123456789</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t>KILDARE</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
+          <t>Ben Kildare Service</t>
+        </is>
+      </c>
+      <c r="W15"/>
       <c r="X15"/>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>1234 SEAWAY ST</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z15"/>
@@ -7376,21 +7422,9 @@
         </is>
       </c>
       <c r="AD15"/>
-      <c r="AE15" s="3" t="inlineStr">
-        <is>
-          <t>CONNIE</t>
-        </is>
-      </c>
-      <c r="AF15" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG15" s="3" t="inlineStr">
-        <is>
-          <t>3055551234</t>
-        </is>
-      </c>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
       <c r="AH15"/>
       <c r="AI15"/>
       <c r="AJ15"/>
@@ -7407,10 +7441,22 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT15"/>
-      <c r="AU15"/>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
       <c r="AV15"/>
-      <c r="AW15"/>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
       <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
@@ -7418,34 +7464,40 @@
       </c>
       <c r="AY15" s="3" t="inlineStr">
         <is>
-          <t>111223333</t>
+          <t>JS00111223333</t>
         </is>
       </c>
       <c r="AZ15"/>
       <c r="BA15" s="3" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="BB15" s="3" t="inlineStr">
         <is>
-          <t>JANE</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="BC15"/>
-      <c r="BD15" s="4" t="n">
-        <v>15827.0</v>
-      </c>
-      <c r="BE15" s="3" t="inlineStr">
-        <is>
-          <t>FEMALE</t>
-        </is>
-      </c>
+      <c r="BD15"/>
+      <c r="BE15"/>
       <c r="BF15"/>
       <c r="BG15"/>
-      <c r="BH15"/>
-      <c r="BI15"/>
-      <c r="BJ15"/>
+      <c r="BH15" s="3" t="inlineStr">
+        <is>
+          <t>MAIMI</t>
+        </is>
+      </c>
+      <c r="BI15" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BJ15" s="3" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
       <c r="BK15"/>
       <c r="BL15"/>
       <c r="BM15"/>
@@ -7465,15 +7517,11 @@
           <t>KEY INSURANCE COMPANY</t>
         </is>
       </c>
-      <c r="BR15" s="3" t="inlineStr">
-        <is>
-          <t>3333OCEAN ST</t>
-        </is>
-      </c>
+      <c r="BR15"/>
       <c r="BS15"/>
       <c r="BT15" s="3" t="inlineStr">
         <is>
-          <t>SOUTH MIAMI</t>
+          <t>MAIMI</t>
         </is>
       </c>
       <c r="BU15" s="3" t="inlineStr">
@@ -7483,74 +7531,32 @@
       </c>
       <c r="BV15" s="3" t="inlineStr">
         <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="BW15" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX15" s="3" t="inlineStr">
-        <is>
-          <t>PBS3334</t>
-        </is>
-      </c>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="BW15"/>
+      <c r="BX15"/>
       <c r="BY15"/>
       <c r="BZ15"/>
-      <c r="CA15" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB15" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC15" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
+      <c r="CA15"/>
+      <c r="CB15"/>
+      <c r="CC15"/>
       <c r="CD15"/>
-      <c r="CE15" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF15" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG15" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="CE15"/>
+      <c r="CF15"/>
+      <c r="CG15"/>
       <c r="CH15"/>
-      <c r="CI15" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ15" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK15" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
+      <c r="CI15"/>
+      <c r="CJ15"/>
+      <c r="CK15"/>
       <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15"/>
       <c r="CO15" s="4" t="n">
-        <v>38628.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CP15" s="4" t="n">
-        <v>38628.0</v>
+        <v>38993.0</v>
       </c>
       <c r="CQ15"/>
       <c r="CR15"/>
@@ -7569,7 +7575,11 @@
       <c r="DE15"/>
       <c r="DF15"/>
       <c r="DG15"/>
-      <c r="DH15"/>
+      <c r="DH15" s="3" t="inlineStr">
+        <is>
+          <t>17312345600006351</t>
+        </is>
+      </c>
       <c r="DI15"/>
       <c r="DJ15"/>
       <c r="DK15"/>
@@ -7577,19 +7587,15 @@
       <c r="DM15"/>
       <c r="DN15" s="3" t="inlineStr">
         <is>
-          <t>J309</t>
+          <t>J020</t>
         </is>
       </c>
       <c r="DO15" s="3" t="inlineStr">
         <is>
-          <t>E785</t>
-        </is>
-      </c>
-      <c r="DP15" s="3" t="inlineStr">
-        <is>
-          <t>E663</t>
-        </is>
-      </c>
+          <t>Z1159</t>
+        </is>
+      </c>
+      <c r="DP15"/>
       <c r="DQ15"/>
       <c r="DR15"/>
       <c r="DS15"/>
@@ -7613,70 +7619,22 @@
       <c r="EK15"/>
       <c r="EL15"/>
       <c r="EM15"/>
-      <c r="EN15" s="3" t="inlineStr">
-        <is>
-          <t>1999996666</t>
-        </is>
-      </c>
-      <c r="EO15" s="3" t="inlineStr">
-        <is>
-          <t>KILDARE</t>
-        </is>
-      </c>
-      <c r="EP15" s="3" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
+      <c r="EN15"/>
+      <c r="EO15"/>
+      <c r="EP15"/>
       <c r="EQ15"/>
-      <c r="ER15" s="3" t="inlineStr">
-        <is>
-          <t>204C00000X</t>
-        </is>
-      </c>
-      <c r="ES15" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET15" s="3" t="inlineStr">
-        <is>
-          <t>KA6663</t>
-        </is>
-      </c>
+      <c r="ER15"/>
+      <c r="ES15"/>
+      <c r="ET15"/>
       <c r="EU15"/>
       <c r="EV15"/>
-      <c r="EW15" s="3" t="inlineStr">
-        <is>
-          <t>1581234567</t>
-        </is>
-      </c>
-      <c r="EX15" s="3" t="inlineStr">
-        <is>
-          <t>KILDARE ASSOCIATES</t>
-        </is>
-      </c>
-      <c r="EY15" s="3" t="inlineStr">
-        <is>
-          <t>2345 OCEAN BLVD</t>
-        </is>
-      </c>
+      <c r="EW15"/>
+      <c r="EX15"/>
+      <c r="EY15"/>
       <c r="EZ15"/>
-      <c r="FA15" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="FB15" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="FC15" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="FA15"/>
+      <c r="FB15"/>
+      <c r="FC15"/>
       <c r="FD15"/>
       <c r="FE15"/>
       <c r="FF15"/>
@@ -7705,66 +7663,22 @@
       <c r="GC15"/>
       <c r="GD15"/>
       <c r="GE15"/>
-      <c r="GF15" s="3" t="inlineStr">
-        <is>
-          <t>SECONDARY</t>
-        </is>
-      </c>
-      <c r="GG15" s="3" t="inlineStr">
-        <is>
-          <t>SPOUSE</t>
-        </is>
-      </c>
+      <c r="GF15"/>
+      <c r="GG15"/>
       <c r="GH15"/>
       <c r="GI15"/>
-      <c r="GJ15" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="GK15" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL15" s="3" t="inlineStr">
-        <is>
-          <t>T55TY666</t>
-        </is>
-      </c>
+      <c r="GJ15"/>
+      <c r="GK15"/>
+      <c r="GL15"/>
       <c r="GM15"/>
-      <c r="GN15" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO15" s="3" t="inlineStr">
-        <is>
-          <t>JACK</t>
-        </is>
-      </c>
+      <c r="GN15"/>
+      <c r="GO15"/>
       <c r="GP15"/>
-      <c r="GQ15" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
+      <c r="GQ15"/>
       <c r="GR15"/>
-      <c r="GS15" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT15" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU15" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="GS15"/>
+      <c r="GT15"/>
+      <c r="GU15"/>
       <c r="GV15"/>
       <c r="GW15"/>
       <c r="GX15"/>
@@ -7781,22 +7695,10 @@
       <c r="HI15"/>
       <c r="HJ15"/>
       <c r="HK15"/>
-      <c r="HL15" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM15" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
+      <c r="HL15"/>
+      <c r="HM15"/>
       <c r="HN15"/>
-      <c r="HO15" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCE COMPANY</t>
-        </is>
-      </c>
+      <c r="HO15"/>
       <c r="HP15"/>
       <c r="HQ15"/>
       <c r="HR15"/>
@@ -7810,7 +7712,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18078</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7820,12 +7722,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>837P-minimal.dat</t>
+          <t>home-infusion-ndc.dat</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0021</t>
+          <t>0711</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -7835,12 +7737,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>0013</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2006-10-15T10:23:00</t>
+          <t>2004-03-01T12:00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -7850,20 +7752,20 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="J16" s="1" t="n">
-        <v>100.0</v>
+        <v>2232.93</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>OFFICE</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -7888,7 +7790,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="R16"/>
@@ -7899,46 +7801,58 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>1234567893</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>587654321</t>
+          <t>10-1234567</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>Ben Kildare Service</t>
+          <t>Professional Home IV, LLC</t>
         </is>
       </c>
       <c r="W16"/>
       <c r="X16"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>234 SEAWAY ST</t>
+          <t>1500 Industrial Drive</t>
         </is>
       </c>
       <c r="Z16"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>Libertyville</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>60048</t>
         </is>
       </c>
       <c r="AD16"/>
-      <c r="AE16"/>
-      <c r="AF16"/>
-      <c r="AG16"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Brenda Holly</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>8019999999</t>
+        </is>
+      </c>
       <c r="AH16"/>
       <c r="AI16"/>
       <c r="AJ16"/>
@@ -7962,7 +7876,7 @@
       </c>
       <c r="AU16" s="3" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>GRP01020102</t>
         </is>
       </c>
       <c r="AV16"/>
@@ -7978,7 +7892,7 @@
       </c>
       <c r="AY16" s="3" t="inlineStr">
         <is>
-          <t>JS00111223333</t>
+          <t>MBRID01234</t>
         </is>
       </c>
       <c r="AZ16"/>
@@ -7989,27 +7903,41 @@
       </c>
       <c r="BB16" s="3" t="inlineStr">
         <is>
-          <t>Jane</t>
-        </is>
-      </c>
-      <c r="BC16"/>
-      <c r="BD16"/>
-      <c r="BE16"/>
-      <c r="BF16"/>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD16" s="4" t="n">
+        <v>15827.0</v>
+      </c>
+      <c r="BE16" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr">
+        <is>
+          <t>15210 Juliet Lane</t>
+        </is>
+      </c>
       <c r="BG16"/>
       <c r="BH16" s="3" t="inlineStr">
         <is>
-          <t>MAIMI</t>
+          <t>Libertyville</t>
         </is>
       </c>
       <c r="BI16" s="3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="BJ16" s="3" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>60048</t>
         </is>
       </c>
       <c r="BK16"/>
@@ -8017,37 +7945,25 @@
       <c r="BM16"/>
       <c r="BN16" s="3" t="inlineStr">
         <is>
-          <t>PAYOR_ID</t>
+          <t>CMS_PLAN_ID</t>
         </is>
       </c>
       <c r="BO16" s="3" t="inlineStr">
         <is>
-          <t>999996666</t>
+          <t>PLANID12345</t>
         </is>
       </c>
       <c r="BP16"/>
       <c r="BQ16" s="3" t="inlineStr">
         <is>
-          <t>KEY INSURANCE COMPANY</t>
+          <t>R&amp;R Health Plan</t>
         </is>
       </c>
       <c r="BR16"/>
       <c r="BS16"/>
-      <c r="BT16" s="3" t="inlineStr">
-        <is>
-          <t>MAIMI</t>
-        </is>
-      </c>
-      <c r="BU16" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BV16" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
       <c r="BW16"/>
       <c r="BX16"/>
       <c r="BY16"/>
@@ -8067,10 +7983,10 @@
       <c r="CM16"/>
       <c r="CN16"/>
       <c r="CO16" s="4" t="n">
-        <v>38993.0</v>
+        <v>38018.0</v>
       </c>
       <c r="CP16" s="4" t="n">
-        <v>38993.0</v>
+        <v>38024.0</v>
       </c>
       <c r="CQ16"/>
       <c r="CR16"/>
@@ -8089,11 +8005,7 @@
       <c r="DE16"/>
       <c r="DF16"/>
       <c r="DG16"/>
-      <c r="DH16" s="3" t="inlineStr">
-        <is>
-          <t>17312345600006351</t>
-        </is>
-      </c>
+      <c r="DH16"/>
       <c r="DI16"/>
       <c r="DJ16"/>
       <c r="DK16"/>
@@ -8101,14 +8013,10 @@
       <c r="DM16"/>
       <c r="DN16" s="3" t="inlineStr">
         <is>
-          <t>J020</t>
-        </is>
-      </c>
-      <c r="DO16" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
+          <t>J069</t>
+        </is>
+      </c>
+      <c r="DO16"/>
       <c r="DP16"/>
       <c r="DQ16"/>
       <c r="DR16"/>
@@ -8226,7 +8134,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2d6d</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -8236,12 +8144,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>home-infusion-ndc.dat</t>
+          <t>837P-all-fields.dat</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0711</t>
+          <t>0031</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -8251,12 +8159,12 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>0013</t>
+          <t>0031</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2004-03-01T12:00:00</t>
+          <t>2006-10-15T10:23:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -8266,20 +8174,20 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>36463774</t>
         </is>
       </c>
       <c r="J17" s="1" t="n">
-        <v>2232.93</v>
+        <v>100.0</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -8307,7 +8215,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="R17"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
           <t>NPI</t>
@@ -8315,46 +8227,50 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>1234567893</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>10-1234567</t>
+          <t>587654321</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>Professional Home IV, LLC</t>
+          <t>BEN KILDARE SERVICE</t>
         </is>
       </c>
       <c r="W17"/>
       <c r="X17"/>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>1500 Industrial Drive</t>
+          <t>234 SEAWAY ST</t>
         </is>
       </c>
       <c r="Z17"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>Libertyville</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>60048</t>
-        </is>
-      </c>
-      <c r="AD17"/>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>203BF0100Y</t>
+        </is>
+      </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>Brenda Holly</t>
+          <t>JOHN SMITH</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -8364,18 +8280,34 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>8019999999</t>
-        </is>
-      </c>
-      <c r="AH17"/>
-      <c r="AI17"/>
+          <t>5555551234</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
       <c r="AJ17"/>
       <c r="AK17"/>
       <c r="AL17"/>
       <c r="AM17"/>
       <c r="AN17"/>
-      <c r="AO17"/>
-      <c r="AP17"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>STATE_LICENSE_NUMBER</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>654321</t>
+        </is>
+      </c>
       <c r="AQ17"/>
       <c r="AR17"/>
       <c r="AS17" s="3" t="inlineStr">
@@ -8383,14 +8315,10 @@
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
+      <c r="AT17"/>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>GRP01020102</t>
+          <t>2222-SJ</t>
         </is>
       </c>
       <c r="AV17"/>
@@ -8406,186 +8334,466 @@
       </c>
       <c r="AY17" s="3" t="inlineStr">
         <is>
-          <t>MBRID01234</t>
-        </is>
-      </c>
-      <c r="AZ17"/>
+          <t>JS00111223333</t>
+        </is>
+      </c>
+      <c r="AZ17" s="3" t="inlineStr">
+        <is>
+          <t>123450000</t>
+        </is>
+      </c>
       <c r="BA17" s="3" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="BB17" s="3" t="inlineStr">
         <is>
-          <t>Steve</t>
-        </is>
-      </c>
-      <c r="BC17" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="BC17"/>
       <c r="BD17" s="4" t="n">
         <v>15827.0</v>
       </c>
       <c r="BE17" s="3" t="inlineStr">
         <is>
-          <t>MALE</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="BF17" s="3" t="inlineStr">
         <is>
-          <t>15210 Juliet Lane</t>
+          <t>236 N MAIN ST</t>
         </is>
       </c>
       <c r="BG17"/>
       <c r="BH17" s="3" t="inlineStr">
         <is>
-          <t>Libertyville</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="BI17" s="3" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="BJ17" s="3" t="inlineStr">
         <is>
-          <t>60048</t>
-        </is>
-      </c>
-      <c r="BK17"/>
-      <c r="BL17"/>
-      <c r="BM17"/>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="BK17" s="4" t="n">
+        <v>32905.0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>176.0</v>
+      </c>
+      <c r="BM17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BN17" s="3" t="inlineStr">
         <is>
-          <t>CMS_PLAN_ID</t>
+          <t>PAYOR_ID</t>
         </is>
       </c>
       <c r="BO17" s="3" t="inlineStr">
         <is>
-          <t>PLANID12345</t>
-        </is>
-      </c>
-      <c r="BP17"/>
+          <t>999996666</t>
+        </is>
+      </c>
+      <c r="BP17" s="3" t="inlineStr">
+        <is>
+          <t>435261708</t>
+        </is>
+      </c>
       <c r="BQ17" s="3" t="inlineStr">
         <is>
-          <t>R&amp;R Health Plan</t>
-        </is>
-      </c>
-      <c r="BR17"/>
+          <t>KEY INSURANCECOMPANY</t>
+        </is>
+      </c>
+      <c r="BR17" s="3" t="inlineStr">
+        <is>
+          <t>P.O. BOX 569008</t>
+        </is>
+      </c>
       <c r="BS17"/>
-      <c r="BT17"/>
-      <c r="BU17"/>
-      <c r="BV17"/>
-      <c r="BW17"/>
-      <c r="BX17"/>
+      <c r="BT17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="BU17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="BV17" s="3" t="inlineStr">
+        <is>
+          <t>332560000</t>
+        </is>
+      </c>
+      <c r="BW17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BX17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="BY17"/>
       <c r="BZ17"/>
-      <c r="CA17"/>
-      <c r="CB17"/>
-      <c r="CC17"/>
+      <c r="CA17" s="3" t="inlineStr">
+        <is>
+          <t>CHILD</t>
+        </is>
+      </c>
+      <c r="CB17" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="CC17" s="3" t="inlineStr">
+        <is>
+          <t>TED</t>
+        </is>
+      </c>
       <c r="CD17"/>
-      <c r="CE17"/>
-      <c r="CF17"/>
-      <c r="CG17"/>
+      <c r="CE17" s="4" t="n">
+        <v>26785.0</v>
+      </c>
+      <c r="CF17" s="3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="CG17" s="3" t="inlineStr">
+        <is>
+          <t>237 N MAIN ST</t>
+        </is>
+      </c>
       <c r="CH17"/>
-      <c r="CI17"/>
-      <c r="CJ17"/>
-      <c r="CK17"/>
-      <c r="CL17"/>
-      <c r="CM17"/>
-      <c r="CN17"/>
+      <c r="CI17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="CJ17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="CK17" s="3" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="CL17" s="4" t="n">
+        <v>35503.0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>156.0</v>
+      </c>
+      <c r="CN17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="CO17" s="4" t="n">
-        <v>38018.0</v>
+        <v>38425.0</v>
       </c>
       <c r="CP17" s="4" t="n">
-        <v>38024.0</v>
-      </c>
-      <c r="CQ17"/>
-      <c r="CR17"/>
-      <c r="CS17"/>
-      <c r="CT17"/>
-      <c r="CU17"/>
-      <c r="CV17"/>
-      <c r="CW17"/>
-      <c r="CX17"/>
-      <c r="CY17"/>
-      <c r="CZ17"/>
-      <c r="DA17"/>
-      <c r="DB17"/>
-      <c r="DC17"/>
-      <c r="DD17"/>
-      <c r="DE17"/>
-      <c r="DF17"/>
-      <c r="DG17"/>
-      <c r="DH17"/>
-      <c r="DI17"/>
-      <c r="DJ17"/>
-      <c r="DK17"/>
-      <c r="DL17"/>
-      <c r="DM17"/>
+        <v>39000.0</v>
+      </c>
+      <c r="CQ17" s="4" t="n">
+        <v>43171.0</v>
+      </c>
+      <c r="CR17" s="4" t="n">
+        <v>43160.0</v>
+      </c>
+      <c r="CS17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CT17" s="4" t="n">
+        <v>43161.0</v>
+      </c>
+      <c r="CU17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CV17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CW17" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="CX17" s="4" t="n">
+        <v>38473.0</v>
+      </c>
+      <c r="CY17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="CZ17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DA17" s="4" t="n">
+        <v>38480.0</v>
+      </c>
+      <c r="DB17" s="4" t="n">
+        <v>38511.0</v>
+      </c>
+      <c r="DC17" s="1" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="DD17" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="DE17" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNum</t>
+        </is>
+      </c>
+      <c r="DF17" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuth</t>
+        </is>
+      </c>
+      <c r="DG17" s="3" t="inlineStr">
+        <is>
+          <t>PayerClaimControlNum</t>
+        </is>
+      </c>
+      <c r="DH17" s="3" t="inlineStr">
+        <is>
+          <t>ClaimIdForTransm</t>
+        </is>
+      </c>
+      <c r="DI17" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="DJ17" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="DK17" s="3" t="inlineStr">
+        <is>
+          <t>MedicalRecordNum</t>
+        </is>
+      </c>
+      <c r="DL17" s="3" t="inlineStr">
+        <is>
+          <t>DemonstrProjectId</t>
+        </is>
+      </c>
+      <c r="DM17" s="3" t="inlineStr">
+        <is>
+          <t>SURGERY WAS UNUSUALLY LONG</t>
+        </is>
+      </c>
       <c r="DN17" s="3" t="inlineStr">
         <is>
-          <t>J069</t>
-        </is>
-      </c>
-      <c r="DO17"/>
+          <t>J0300</t>
+        </is>
+      </c>
+      <c r="DO17" s="3" t="inlineStr">
+        <is>
+          <t>Z1159</t>
+        </is>
+      </c>
       <c r="DP17"/>
       <c r="DQ17"/>
       <c r="DR17"/>
-      <c r="DS17"/>
-      <c r="DT17"/>
-      <c r="DU17"/>
+      <c r="DS17" s="3" t="inlineStr">
+        <is>
+          <t>33414</t>
+        </is>
+      </c>
+      <c r="DT17" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="DU17" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="DV17"/>
-      <c r="DW17"/>
-      <c r="DX17"/>
-      <c r="DY17"/>
+      <c r="DW17" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="DX17" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="DY17" s="3" t="inlineStr">
+        <is>
+          <t>DMN0012</t>
+        </is>
+      </c>
       <c r="DZ17"/>
       <c r="EA17"/>
       <c r="EB17"/>
       <c r="EC17"/>
       <c r="ED17"/>
       <c r="EE17"/>
-      <c r="EF17"/>
-      <c r="EG17"/>
-      <c r="EH17"/>
-      <c r="EI17"/>
-      <c r="EJ17"/>
-      <c r="EK17"/>
+      <c r="EF17" s="3" t="inlineStr">
+        <is>
+          <t>5234567805</t>
+        </is>
+      </c>
+      <c r="EG17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EH17" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="EI17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EJ17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="EK17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="EL17"/>
       <c r="EM17"/>
-      <c r="EN17"/>
-      <c r="EO17"/>
-      <c r="EP17"/>
-      <c r="EQ17"/>
-      <c r="ER17"/>
-      <c r="ES17"/>
-      <c r="ET17"/>
+      <c r="EN17" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="EO17" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="EP17" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="EQ17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER17" s="3" t="inlineStr">
+        <is>
+          <t>000000000X</t>
+        </is>
+      </c>
+      <c r="ES17" s="3" t="inlineStr">
+        <is>
+          <t>LOCATION_NUMBER</t>
+        </is>
+      </c>
+      <c r="ET17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="EU17"/>
       <c r="EV17"/>
-      <c r="EW17"/>
-      <c r="EX17"/>
-      <c r="EY17"/>
+      <c r="EW17" s="3" t="inlineStr">
+        <is>
+          <t>000000004</t>
+        </is>
+      </c>
+      <c r="EX17" s="3" t="inlineStr">
+        <is>
+          <t>Service Facility</t>
+        </is>
+      </c>
+      <c r="EY17" s="3" t="inlineStr">
+        <is>
+          <t>123 FAKE STREET</t>
+        </is>
+      </c>
       <c r="EZ17"/>
-      <c r="FA17"/>
-      <c r="FB17"/>
-      <c r="FC17"/>
+      <c r="FA17" s="3" t="inlineStr">
+        <is>
+          <t>CITY</t>
+        </is>
+      </c>
+      <c r="FB17" s="3" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="FC17" s="3" t="inlineStr">
+        <is>
+          <t>123459999</t>
+        </is>
+      </c>
       <c r="FD17"/>
       <c r="FE17"/>
       <c r="FF17"/>
       <c r="FG17"/>
       <c r="FH17"/>
-      <c r="FI17"/>
-      <c r="FJ17"/>
+      <c r="FI17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FJ17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="FK17"/>
       <c r="FL17"/>
-      <c r="FM17"/>
-      <c r="FN17"/>
-      <c r="FO17"/>
-      <c r="FP17"/>
-      <c r="FQ17"/>
-      <c r="FR17"/>
+      <c r="FM17" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="FN17" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="FO17" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="FP17" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ17" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="FR17" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="FS17"/>
       <c r="FT17"/>
       <c r="FU17"/>
@@ -8599,911 +8807,189 @@
       <c r="GC17"/>
       <c r="GD17"/>
       <c r="GE17"/>
-      <c r="GF17"/>
-      <c r="GG17"/>
-      <c r="GH17"/>
-      <c r="GI17"/>
-      <c r="GJ17"/>
-      <c r="GK17"/>
-      <c r="GL17"/>
+      <c r="GF17" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="GG17" s="3" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="GH17" s="3" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="GI17" s="3" t="inlineStr">
+        <is>
+          <t>PLAN NAME</t>
+        </is>
+      </c>
+      <c r="GJ17" s="3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="GK17" s="3" t="inlineStr">
+        <is>
+          <t>MEMBER_ID</t>
+        </is>
+      </c>
+      <c r="GL17" s="3" t="inlineStr">
+        <is>
+          <t>JS00111223999</t>
+        </is>
+      </c>
       <c r="GM17"/>
-      <c r="GN17"/>
-      <c r="GO17"/>
+      <c r="GN17" s="3" t="inlineStr">
+        <is>
+          <t>SMITH</t>
+        </is>
+      </c>
+      <c r="GO17" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="GP17"/>
-      <c r="GQ17"/>
+      <c r="GQ17" s="3" t="inlineStr">
+        <is>
+          <t>239 N MAIN ST</t>
+        </is>
+      </c>
       <c r="GR17"/>
-      <c r="GS17"/>
-      <c r="GT17"/>
-      <c r="GU17"/>
-      <c r="GV17"/>
-      <c r="GW17"/>
-      <c r="GX17"/>
+      <c r="GS17" s="3" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="GT17" s="3" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="GU17" s="3" t="inlineStr">
+        <is>
+          <t>33415</t>
+        </is>
+      </c>
+      <c r="GV17" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="GW17" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="GX17" s="1" t="n">
+        <v>21.89</v>
+      </c>
       <c r="GY17"/>
-      <c r="GZ17"/>
-      <c r="HA17"/>
-      <c r="HB17"/>
+      <c r="GZ17" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT_RESPONSIBILITY</t>
+        </is>
+      </c>
+      <c r="HA17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="HB17" s="1" t="n">
+        <v>15.0</v>
+      </c>
       <c r="HC17"/>
-      <c r="HD17"/>
-      <c r="HE17"/>
-      <c r="HF17"/>
-      <c r="HG17"/>
-      <c r="HH17"/>
-      <c r="HI17"/>
-      <c r="HJ17"/>
-      <c r="HK17"/>
-      <c r="HL17"/>
-      <c r="HM17"/>
-      <c r="HN17"/>
-      <c r="HO17"/>
-      <c r="HP17"/>
-      <c r="HQ17"/>
-      <c r="HR17"/>
-      <c r="HS17"/>
-      <c r="HT17"/>
-      <c r="HU17"/>
-      <c r="HV17"/>
+      <c r="HD17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="HE17" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="HF17" s="1" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="HG17" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="HH17" s="1" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="HI17" s="1" t="n">
+        <v>273.0</v>
+      </c>
+      <c r="HJ17" s="1" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="HK17" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM99</t>
+        </is>
+      </c>
+      <c r="HL17" s="3" t="inlineStr">
+        <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="HM17" s="3" t="inlineStr">
+        <is>
+          <t>OTP</t>
+        </is>
+      </c>
+      <c r="HN17" s="3" t="inlineStr">
+        <is>
+          <t>987654321</t>
+        </is>
+      </c>
+      <c r="HO17" s="3" t="inlineStr">
+        <is>
+          <t>OTHER PAYER</t>
+        </is>
+      </c>
+      <c r="HP17" s="3" t="inlineStr">
+        <is>
+          <t>PO BOX 7901</t>
+        </is>
+      </c>
+      <c r="HQ17" s="3" t="inlineStr">
+        <is>
+          <t>DEP 2</t>
+        </is>
+      </c>
+      <c r="HR17" s="3" t="inlineStr">
+        <is>
+          <t>MADISON</t>
+        </is>
+      </c>
+      <c r="HS17" s="3" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="HT17" s="3" t="inlineStr">
+        <is>
+          <t>53707</t>
+        </is>
+      </c>
+      <c r="HU17" s="3" t="inlineStr">
+        <is>
+          <t>CLAIM_OFFICE_NUMBER</t>
+        </is>
+      </c>
+      <c r="HV17" s="3" t="inlineStr">
+        <is>
+          <t>98765</t>
+        </is>
+      </c>
       <c r="HW17"/>
       <c r="HX17"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>6a04cb3a618f76c4f7b1817e</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>837P</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>837P-all-fields.dat</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>0031</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>0031</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>2006-10-15T10:23:00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>CHARGEABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>36463774</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>OFFICE</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>NPI</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>587654321</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>BEN KILDARE SERVICE</t>
-        </is>
-      </c>
-      <c r="W18"/>
-      <c r="X18"/>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>234 SEAWAY ST</t>
-        </is>
-      </c>
-      <c r="Z18"/>
-      <c r="AA18" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
-        <is>
-          <t>203BF0100Y</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="inlineStr">
-        <is>
-          <t>JOHN SMITH</t>
-        </is>
-      </c>
-      <c r="AF18" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="AG18" s="3" t="inlineStr">
-        <is>
-          <t>5555551234</t>
-        </is>
-      </c>
-      <c r="AH18" s="3" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="AI18" s="3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AJ18"/>
-      <c r="AK18"/>
-      <c r="AL18"/>
-      <c r="AM18"/>
-      <c r="AN18"/>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>STATE_LICENSE_NUMBER</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>654321</t>
-        </is>
-      </c>
-      <c r="AQ18"/>
-      <c r="AR18"/>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="AT18"/>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>2222-SJ</t>
-        </is>
-      </c>
-      <c r="AV18"/>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="AY18" s="3" t="inlineStr">
-        <is>
-          <t>JS00111223333</t>
-        </is>
-      </c>
-      <c r="AZ18" s="3" t="inlineStr">
-        <is>
-          <t>123450000</t>
-        </is>
-      </c>
-      <c r="BA18" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="BB18" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="BC18"/>
-      <c r="BD18" s="4" t="n">
-        <v>15827.0</v>
-      </c>
-      <c r="BE18" s="3" t="inlineStr">
-        <is>
-          <t>FEMALE</t>
-        </is>
-      </c>
-      <c r="BF18" s="3" t="inlineStr">
-        <is>
-          <t>236 N MAIN ST</t>
-        </is>
-      </c>
-      <c r="BG18"/>
-      <c r="BH18" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="BI18" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BJ18" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="BK18" s="4" t="n">
-        <v>32905.0</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>176.0</v>
-      </c>
-      <c r="BM18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BN18" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="BO18" s="3" t="inlineStr">
-        <is>
-          <t>999996666</t>
-        </is>
-      </c>
-      <c r="BP18" s="3" t="inlineStr">
-        <is>
-          <t>435261708</t>
-        </is>
-      </c>
-      <c r="BQ18" s="3" t="inlineStr">
-        <is>
-          <t>KEY INSURANCECOMPANY</t>
-        </is>
-      </c>
-      <c r="BR18" s="3" t="inlineStr">
-        <is>
-          <t>P.O. BOX 569008</t>
-        </is>
-      </c>
-      <c r="BS18"/>
-      <c r="BT18" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="BU18" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="BV18" s="3" t="inlineStr">
-        <is>
-          <t>332560000</t>
-        </is>
-      </c>
-      <c r="BW18" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BX18" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="BY18"/>
-      <c r="BZ18"/>
-      <c r="CA18" s="3" t="inlineStr">
-        <is>
-          <t>CHILD</t>
-        </is>
-      </c>
-      <c r="CB18" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="CC18" s="3" t="inlineStr">
-        <is>
-          <t>TED</t>
-        </is>
-      </c>
-      <c r="CD18"/>
-      <c r="CE18" s="4" t="n">
-        <v>26785.0</v>
-      </c>
-      <c r="CF18" s="3" t="inlineStr">
-        <is>
-          <t>MALE</t>
-        </is>
-      </c>
-      <c r="CG18" s="3" t="inlineStr">
-        <is>
-          <t>237 N MAIN ST</t>
-        </is>
-      </c>
-      <c r="CH18"/>
-      <c r="CI18" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="CJ18" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="CK18" s="3" t="inlineStr">
-        <is>
-          <t>33413</t>
-        </is>
-      </c>
-      <c r="CL18" s="4" t="n">
-        <v>35503.0</v>
-      </c>
-      <c r="CM18" t="n">
-        <v>156.0</v>
-      </c>
-      <c r="CN18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="CO18" s="4" t="n">
-        <v>38425.0</v>
-      </c>
-      <c r="CP18" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="CQ18" s="4" t="n">
-        <v>43171.0</v>
-      </c>
-      <c r="CR18" s="4" t="n">
-        <v>43160.0</v>
-      </c>
-      <c r="CS18" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CT18" s="4" t="n">
-        <v>43161.0</v>
-      </c>
-      <c r="CU18" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CV18" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CW18" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="CX18" s="4" t="n">
-        <v>38473.0</v>
-      </c>
-      <c r="CY18" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="CZ18" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DA18" s="4" t="n">
-        <v>38480.0</v>
-      </c>
-      <c r="DB18" s="4" t="n">
-        <v>38511.0</v>
-      </c>
-      <c r="DC18" s="1" t="n">
-        <v>152.45</v>
-      </c>
-      <c r="DD18" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="DE18" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNum</t>
-        </is>
-      </c>
-      <c r="DF18" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuth</t>
-        </is>
-      </c>
-      <c r="DG18" s="3" t="inlineStr">
-        <is>
-          <t>PayerClaimControlNum</t>
-        </is>
-      </c>
-      <c r="DH18" s="3" t="inlineStr">
-        <is>
-          <t>ClaimIdForTransm</t>
-        </is>
-      </c>
-      <c r="DI18" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="DJ18" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="DK18" s="3" t="inlineStr">
-        <is>
-          <t>MedicalRecordNum</t>
-        </is>
-      </c>
-      <c r="DL18" s="3" t="inlineStr">
-        <is>
-          <t>DemonstrProjectId</t>
-        </is>
-      </c>
-      <c r="DM18" s="3" t="inlineStr">
-        <is>
-          <t>SURGERY WAS UNUSUALLY LONG</t>
-        </is>
-      </c>
-      <c r="DN18" s="3" t="inlineStr">
-        <is>
-          <t>J0300</t>
-        </is>
-      </c>
-      <c r="DO18" s="3" t="inlineStr">
-        <is>
-          <t>Z1159</t>
-        </is>
-      </c>
-      <c r="DP18"/>
-      <c r="DQ18"/>
-      <c r="DR18"/>
-      <c r="DS18" s="3" t="inlineStr">
-        <is>
-          <t>33414</t>
-        </is>
-      </c>
-      <c r="DT18" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="DU18" s="3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="DV18"/>
-      <c r="DW18" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="DX18" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="DY18" s="3" t="inlineStr">
-        <is>
-          <t>DMN0012</t>
-        </is>
-      </c>
-      <c r="DZ18"/>
-      <c r="EA18"/>
-      <c r="EB18"/>
-      <c r="EC18"/>
-      <c r="ED18"/>
-      <c r="EE18"/>
-      <c r="EF18" s="3" t="inlineStr">
-        <is>
-          <t>5234567805</t>
-        </is>
-      </c>
-      <c r="EG18" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EH18" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="EI18" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EJ18" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="EK18" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="EL18"/>
-      <c r="EM18"/>
-      <c r="EN18" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="EO18" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="EP18" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="EQ18" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="ER18" s="3" t="inlineStr">
-        <is>
-          <t>000000000X</t>
-        </is>
-      </c>
-      <c r="ES18" s="3" t="inlineStr">
-        <is>
-          <t>LOCATION_NUMBER</t>
-        </is>
-      </c>
-      <c r="ET18" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="EU18"/>
-      <c r="EV18"/>
-      <c r="EW18" s="3" t="inlineStr">
-        <is>
-          <t>000000004</t>
-        </is>
-      </c>
-      <c r="EX18" s="3" t="inlineStr">
-        <is>
-          <t>Service Facility</t>
-        </is>
-      </c>
-      <c r="EY18" s="3" t="inlineStr">
-        <is>
-          <t>123 FAKE STREET</t>
-        </is>
-      </c>
-      <c r="EZ18"/>
-      <c r="FA18" s="3" t="inlineStr">
-        <is>
-          <t>CITY</t>
-        </is>
-      </c>
-      <c r="FB18" s="3" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="FC18" s="3" t="inlineStr">
-        <is>
-          <t>123459999</t>
-        </is>
-      </c>
-      <c r="FD18"/>
-      <c r="FE18"/>
-      <c r="FF18"/>
-      <c r="FG18"/>
-      <c r="FH18"/>
-      <c r="FI18" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FJ18" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="FK18"/>
-      <c r="FL18"/>
-      <c r="FM18" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="FN18" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="FO18" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="FP18" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="FQ18" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="FR18" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
-      <c r="FS18"/>
-      <c r="FT18"/>
-      <c r="FU18"/>
-      <c r="FV18"/>
-      <c r="FW18"/>
-      <c r="FX18"/>
-      <c r="FY18"/>
-      <c r="FZ18"/>
-      <c r="GA18"/>
-      <c r="GB18"/>
-      <c r="GC18"/>
-      <c r="GD18"/>
-      <c r="GE18"/>
-      <c r="GF18" s="3" t="inlineStr">
-        <is>
-          <t>PRIMARY</t>
-        </is>
-      </c>
-      <c r="GG18" s="3" t="inlineStr">
-        <is>
-          <t>SELF</t>
-        </is>
-      </c>
-      <c r="GH18" s="3" t="inlineStr">
-        <is>
-          <t>000000</t>
-        </is>
-      </c>
-      <c r="GI18" s="3" t="inlineStr">
-        <is>
-          <t>PLAN NAME</t>
-        </is>
-      </c>
-      <c r="GJ18" s="3" t="inlineStr">
-        <is>
-          <t>MB</t>
-        </is>
-      </c>
-      <c r="GK18" s="3" t="inlineStr">
-        <is>
-          <t>MEMBER_ID</t>
-        </is>
-      </c>
-      <c r="GL18" s="3" t="inlineStr">
-        <is>
-          <t>JS00111223999</t>
-        </is>
-      </c>
-      <c r="GM18"/>
-      <c r="GN18" s="3" t="inlineStr">
-        <is>
-          <t>SMITH</t>
-        </is>
-      </c>
-      <c r="GO18" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="GP18"/>
-      <c r="GQ18" s="3" t="inlineStr">
-        <is>
-          <t>239 N MAIN ST</t>
-        </is>
-      </c>
-      <c r="GR18"/>
-      <c r="GS18" s="3" t="inlineStr">
-        <is>
-          <t>MIAMI</t>
-        </is>
-      </c>
-      <c r="GT18" s="3" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="GU18" s="3" t="inlineStr">
-        <is>
-          <t>33415</t>
-        </is>
-      </c>
-      <c r="GV18" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="GW18" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="GX18" s="1" t="n">
-        <v>21.89</v>
-      </c>
-      <c r="GY18"/>
-      <c r="GZ18" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT_RESPONSIBILITY</t>
-        </is>
-      </c>
-      <c r="HA18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="HB18" s="1" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="HC18"/>
-      <c r="HD18" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="HE18" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="HF18" s="1" t="n">
-        <v>55.0</v>
-      </c>
-      <c r="HG18" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="HH18" s="1" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="HI18" s="1" t="n">
-        <v>273.0</v>
-      </c>
-      <c r="HJ18" s="1" t="n">
-        <v>14.83</v>
-      </c>
-      <c r="HK18" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM99</t>
-        </is>
-      </c>
-      <c r="HL18" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="HM18" s="3" t="inlineStr">
-        <is>
-          <t>OTP</t>
-        </is>
-      </c>
-      <c r="HN18" s="3" t="inlineStr">
-        <is>
-          <t>987654321</t>
-        </is>
-      </c>
-      <c r="HO18" s="3" t="inlineStr">
-        <is>
-          <t>OTHER PAYER</t>
-        </is>
-      </c>
-      <c r="HP18" s="3" t="inlineStr">
-        <is>
-          <t>PO BOX 7901</t>
-        </is>
-      </c>
-      <c r="HQ18" s="3" t="inlineStr">
-        <is>
-          <t>DEP 2</t>
-        </is>
-      </c>
-      <c r="HR18" s="3" t="inlineStr">
-        <is>
-          <t>MADISON</t>
-        </is>
-      </c>
-      <c r="HS18" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="HT18" s="3" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="HU18" s="3" t="inlineStr">
-        <is>
-          <t>CLAIM_OFFICE_NUMBER</t>
-        </is>
-      </c>
-      <c r="HV18" s="3" t="inlineStr">
-        <is>
-          <t>98765</t>
-        </is>
-      </c>
-      <c r="HW18"/>
-      <c r="HX18"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -9512,7 +8998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:DS47"/>
+  <dimension ref="A1:DS46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -10135,7 +9621,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dca</t>
+          <t>6a04cc5a1ef26d534baf29f1</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -10338,7 +9824,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dca</t>
+          <t>6a04cc5a1ef26d534baf29f1</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -10505,7 +9991,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dca</t>
+          <t>6a04cc5a1ef26d534baf29f1</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -10672,7 +10158,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dca</t>
+          <t>6a04cc5a1ef26d534baf29f1</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -10839,7 +10325,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dfb</t>
+          <t>6a04cc5a1ef26d534baf2a22</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10994,7 +10480,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dfb</t>
+          <t>6a04cc5a1ef26d534baf2a22</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -11149,7 +10635,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dfb</t>
+          <t>6a04cc5a1ef26d534baf2a22</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -11304,7 +10790,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17dfb</t>
+          <t>6a04cc5a1ef26d534baf2a22</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -11459,7 +10945,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e25</t>
+          <t>6a04cc5a1ef26d534baf2a4c</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11614,7 +11100,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e6e</t>
+          <t>6a04cc5a1ef26d534baf2a95</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11773,7 +11259,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e6e</t>
+          <t>6a04cc5a1ef26d534baf2a95</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -11930,7 +11416,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17e6e</t>
+          <t>6a04cc5a1ef26d534baf2a95</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -12087,7 +11573,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ea6</t>
+          <t>6a04cc5a1ef26d534baf2ac4</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -12111,7 +11597,7 @@
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" s="1" t="n">
-        <v>100.0</v>
+        <v>40.0</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
@@ -12121,42 +11607,22 @@
       <c r="L14" t="n">
         <v>1.0</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>OFFICE</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="M14"/>
+      <c r="N14"/>
       <c r="O14" s="2" t="n">
         <v>1.0</v>
       </c>
       <c r="P14"/>
       <c r="Q14"/>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
       <c r="U14"/>
       <c r="V14" s="4" t="n">
-        <v>40943.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>40943.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X14"/>
       <c r="Y14"/>
@@ -12262,7 +11728,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ed5</t>
+          <t>6a04cc5a1ef26d534baf2ac4</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -12272,12 +11738,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E15"/>
@@ -12286,7 +11752,7 @@
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" s="1" t="n">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -12417,7 +11883,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ed5</t>
+          <t>6a04cc5a1ef26d534baf2ac4</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12427,12 +11893,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E16"/>
@@ -12441,7 +11907,7 @@
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" s="1" t="n">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
@@ -12454,7 +11920,7 @@
       <c r="M16"/>
       <c r="N16"/>
       <c r="O16" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P16"/>
       <c r="Q16"/>
@@ -12463,10 +11929,10 @@
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X16"/>
       <c r="Y16"/>
@@ -12572,22 +12038,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17ed5</t>
+          <t>6a04cc5a1ef26d534baf2b3b</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>26462967</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E17"/>
@@ -12596,7 +12062,7 @@
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" s="1" t="n">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -12609,7 +12075,7 @@
       <c r="M17"/>
       <c r="N17"/>
       <c r="O17" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P17"/>
       <c r="Q17"/>
@@ -12618,10 +12084,10 @@
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>39000.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X17"/>
       <c r="Y17"/>
@@ -12727,7 +12193,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4c</t>
+          <t>6a04cc5a1ef26d534baf2b3b</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12737,12 +12203,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E18"/>
@@ -12751,7 +12217,7 @@
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" s="1" t="n">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -12882,7 +12348,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4c</t>
+          <t>6a04cc5a1ef26d534baf2b3b</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -12892,12 +12358,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E19"/>
@@ -12906,7 +12372,7 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" s="1" t="n">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -12919,7 +12385,7 @@
       <c r="M19"/>
       <c r="N19"/>
       <c r="O19" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P19"/>
       <c r="Q19"/>
@@ -12928,10 +12394,10 @@
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X19"/>
       <c r="Y19"/>
@@ -13037,7 +12503,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4c</t>
+          <t>6a04cc5a1ef26d534baf2b3b</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -13047,12 +12513,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E20"/>
@@ -13061,7 +12527,7 @@
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" s="1" t="n">
-        <v>35.0</v>
+        <v>10.0</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -13192,22 +12658,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4c</t>
+          <t>6a04cc5a1ef26d534baf2b3c</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>26462967</t>
+          <t>125WILL</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>98940</t>
         </is>
       </c>
       <c r="E21"/>
@@ -13216,7 +12682,7 @@
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" s="1" t="n">
-        <v>10.0</v>
+        <v>145.5</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -13229,7 +12695,7 @@
       <c r="M21"/>
       <c r="N21"/>
       <c r="O21" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P21"/>
       <c r="Q21"/>
@@ -13238,10 +12704,10 @@
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21" s="4" t="n">
-        <v>39000.0</v>
+        <v>38398.0</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>39000.0</v>
+        <v>38398.0</v>
       </c>
       <c r="X21"/>
       <c r="Y21"/>
@@ -13347,39 +12813,51 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4d</t>
+          <t>6a04cc5a1ef26d534baf2b3d</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>125WILL</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="I22"/>
       <c r="J22" s="1" t="n">
-        <v>145.5</v>
+        <v>827.0</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M22"/>
       <c r="N22"/>
@@ -13393,10 +12871,10 @@
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22" s="4" t="n">
-        <v>38398.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>38398.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X22"/>
       <c r="Y22"/>
@@ -13502,7 +12980,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4e</t>
+          <t>6a04cc5a1ef26d534baf2b3d</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -13512,7 +12990,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -13560,10 +13038,10 @@
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23" s="4" t="n">
-        <v>38364.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>38364.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X23"/>
       <c r="Y23"/>
@@ -13669,51 +13147,39 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f4e</t>
+          <t>6a04cc5a1ef26d534baf2b70</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E24"/>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>QK</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>QS</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24"/>
       <c r="J24" s="1" t="n">
-        <v>827.0</v>
+        <v>40.0</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M24"/>
       <c r="N24"/>
@@ -13727,10 +13193,10 @@
       <c r="T24"/>
       <c r="U24"/>
       <c r="V24" s="4" t="n">
-        <v>38365.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>38365.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X24"/>
       <c r="Y24"/>
@@ -13836,7 +13302,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f81</t>
+          <t>6a04cc5a1ef26d534baf2b70</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -13846,12 +13312,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>87070</t>
         </is>
       </c>
       <c r="E25"/>
@@ -13860,7 +13326,7 @@
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" s="1" t="n">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -13991,7 +13457,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f81</t>
+          <t>6a04cc5a1ef26d534baf2b70</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -14001,12 +13467,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E26"/>
@@ -14015,7 +13481,7 @@
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" s="1" t="n">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -14028,7 +13494,7 @@
       <c r="M26"/>
       <c r="N26"/>
       <c r="O26" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P26"/>
       <c r="Q26"/>
@@ -14037,10 +13503,10 @@
       <c r="T26"/>
       <c r="U26"/>
       <c r="V26" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X26"/>
       <c r="Y26"/>
@@ -14146,7 +13612,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f81</t>
+          <t>6a04cc5a1ef26d534baf2b70</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -14156,12 +13622,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E27"/>
@@ -14170,7 +13636,7 @@
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" s="1" t="n">
-        <v>35.0</v>
+        <v>10.0</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
@@ -14301,44 +13767,56 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17f81</t>
+          <t>6a04cc5a1ef26d534baf2b9d</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>153829140</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>86663</t>
+          <t>00142</t>
         </is>
       </c>
       <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>QK</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="I28"/>
       <c r="J28" s="1" t="n">
-        <v>10.0</v>
+        <v>827.0</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>MINUTES</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.0</v>
+        <v>61.0</v>
       </c>
       <c r="M28"/>
       <c r="N28"/>
       <c r="O28" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="P28"/>
       <c r="Q28"/>
@@ -14347,10 +13825,10 @@
       <c r="T28"/>
       <c r="U28"/>
       <c r="V28" s="4" t="n">
-        <v>39000.0</v>
+        <v>38364.0</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>39000.0</v>
+        <v>38364.0</v>
       </c>
       <c r="X28"/>
       <c r="Y28"/>
@@ -14456,7 +13934,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17fae</t>
+          <t>6a04cc5a1ef26d534baf2b9d</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -14466,7 +13944,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -14514,10 +13992,10 @@
       <c r="T29"/>
       <c r="U29"/>
       <c r="V29" s="4" t="n">
-        <v>38364.0</v>
+        <v>38365.0</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>38364.0</v>
+        <v>38365.0</v>
       </c>
       <c r="X29"/>
       <c r="Y29"/>
@@ -14623,71 +14101,75 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17fae</t>
+          <t>6a04cc5a1ef26d534baf2bd8</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>153829140</t>
+          <t>SMI123</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>00142</t>
+          <t>K0001</t>
         </is>
       </c>
       <c r="E30"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>QK</t>
+          <t>RR</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="I30"/>
       <c r="J30" s="1" t="n">
-        <v>827.0</v>
+        <v>75.0</v>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>MINUTES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>61.0</v>
+        <v>1.0</v>
       </c>
       <c r="M30"/>
       <c r="N30"/>
       <c r="O30" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P30"/>
+      <c r="P30" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q30"/>
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
       <c r="U30"/>
       <c r="V30" s="4" t="n">
-        <v>38365.0</v>
+        <v>38432.0</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>38365.0</v>
+        <v>38432.0</v>
       </c>
       <c r="X30"/>
-      <c r="Y30"/>
+      <c r="Y30" s="4" t="n">
+        <v>38067.0</v>
+      </c>
       <c r="Z30"/>
       <c r="AA30"/>
       <c r="AB30"/>
@@ -14702,8 +14184,16 @@
       <c r="AK30"/>
       <c r="AL30"/>
       <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
       <c r="AP30"/>
       <c r="AQ30"/>
       <c r="AR30"/>
@@ -14757,22 +14247,70 @@
       <c r="CN30"/>
       <c r="CO30"/>
       <c r="CP30"/>
-      <c r="CQ30"/>
-      <c r="CR30"/>
-      <c r="CS30"/>
+      <c r="CQ30" s="3" t="inlineStr">
+        <is>
+          <t>1111155555</t>
+        </is>
+      </c>
+      <c r="CR30" s="3" t="inlineStr">
+        <is>
+          <t>WILSON</t>
+        </is>
+      </c>
+      <c r="CS30" s="3" t="inlineStr">
+        <is>
+          <t>RANDALL</t>
+        </is>
+      </c>
       <c r="CT30"/>
-      <c r="CU30"/>
+      <c r="CU30" s="3" t="inlineStr">
+        <is>
+          <t>1226 WEST RAILROAD STREET</t>
+        </is>
+      </c>
       <c r="CV30"/>
-      <c r="CW30"/>
-      <c r="CX30"/>
-      <c r="CY30"/>
-      <c r="CZ30"/>
-      <c r="DA30"/>
-      <c r="DB30"/>
+      <c r="CW30" s="3" t="inlineStr">
+        <is>
+          <t>LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="CX30" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="CY30" s="3" t="inlineStr">
+        <is>
+          <t>47905</t>
+        </is>
+      </c>
+      <c r="CZ30" s="3" t="inlineStr">
+        <is>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="DA30" s="3" t="inlineStr">
+        <is>
+          <t>PHONE</t>
+        </is>
+      </c>
+      <c r="DB30" s="3" t="inlineStr">
+        <is>
+          <t>7659259999</t>
+        </is>
+      </c>
       <c r="DC30"/>
       <c r="DD30"/>
-      <c r="DE30"/>
-      <c r="DF30"/>
+      <c r="DE30" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_UPIN_NUMBER</t>
+        </is>
+      </c>
+      <c r="DF30" s="3" t="inlineStr">
+        <is>
+          <t>M12345</t>
+        </is>
+      </c>
       <c r="DG30"/>
       <c r="DH30"/>
       <c r="DI30"/>
@@ -14790,12 +14328,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b17fe9</t>
+          <t>6a04cc5a1ef26d534baf2c08</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>SMI123</t>
+          <t>ABC123-RI</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -14805,7 +14343,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>K0001</t>
+          <t>E0570</t>
         </is>
       </c>
       <c r="E31"/>
@@ -14814,19 +14352,11 @@
           <t>RR</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>KH</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+      <c r="G31"/>
+      <c r="H31"/>
       <c r="I31"/>
       <c r="J31" s="1" t="n">
-        <v>75.0</v>
+        <v>25.0</v>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
@@ -14850,21 +14380,23 @@
       <c r="T31"/>
       <c r="U31"/>
       <c r="V31" s="4" t="n">
-        <v>38432.0</v>
+        <v>38486.0</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>38432.0</v>
+        <v>38486.0</v>
       </c>
       <c r="X31"/>
-      <c r="Y31" s="4" t="n">
-        <v>38067.0</v>
-      </c>
+      <c r="Y31"/>
       <c r="Z31"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31"/>
-      <c r="AE31"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>V123456</t>
+        </is>
+      </c>
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
@@ -14873,16 +14405,8 @@
       <c r="AK31"/>
       <c r="AL31"/>
       <c r="AM31"/>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
+      <c r="AN31"/>
+      <c r="AO31"/>
       <c r="AP31"/>
       <c r="AQ31"/>
       <c r="AR31"/>
@@ -14928,78 +14452,42 @@
       <c r="CF31"/>
       <c r="CG31"/>
       <c r="CH31"/>
-      <c r="CI31"/>
-      <c r="CJ31"/>
-      <c r="CK31"/>
+      <c r="CI31" s="3" t="inlineStr">
+        <is>
+          <t>9988776655</t>
+        </is>
+      </c>
+      <c r="CJ31" s="3" t="inlineStr">
+        <is>
+          <t>DOE</t>
+        </is>
+      </c>
+      <c r="CK31" s="3" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
       <c r="CL31"/>
       <c r="CM31"/>
       <c r="CN31"/>
       <c r="CO31"/>
       <c r="CP31"/>
-      <c r="CQ31" s="3" t="inlineStr">
-        <is>
-          <t>1111155555</t>
-        </is>
-      </c>
-      <c r="CR31" s="3" t="inlineStr">
-        <is>
-          <t>WILSON</t>
-        </is>
-      </c>
-      <c r="CS31" s="3" t="inlineStr">
-        <is>
-          <t>RANDALL</t>
-        </is>
-      </c>
+      <c r="CQ31"/>
+      <c r="CR31"/>
+      <c r="CS31"/>
       <c r="CT31"/>
-      <c r="CU31" s="3" t="inlineStr">
-        <is>
-          <t>1226 WEST RAILROAD STREET</t>
-        </is>
-      </c>
+      <c r="CU31"/>
       <c r="CV31"/>
-      <c r="CW31" s="3" t="inlineStr">
-        <is>
-          <t>LAFAYETTE</t>
-        </is>
-      </c>
-      <c r="CX31" s="3" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="CY31" s="3" t="inlineStr">
-        <is>
-          <t>47905</t>
-        </is>
-      </c>
-      <c r="CZ31" s="3" t="inlineStr">
-        <is>
-          <t>LEE</t>
-        </is>
-      </c>
-      <c r="DA31" s="3" t="inlineStr">
-        <is>
-          <t>PHONE</t>
-        </is>
-      </c>
-      <c r="DB31" s="3" t="inlineStr">
-        <is>
-          <t>7659259999</t>
-        </is>
-      </c>
+      <c r="CW31"/>
+      <c r="CX31"/>
+      <c r="CY31"/>
+      <c r="CZ31"/>
+      <c r="DA31"/>
+      <c r="DB31"/>
       <c r="DC31"/>
       <c r="DD31"/>
-      <c r="DE31" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_UPIN_NUMBER</t>
-        </is>
-      </c>
-      <c r="DF31" s="3" t="inlineStr">
-        <is>
-          <t>M12345</t>
-        </is>
-      </c>
+      <c r="DE31"/>
+      <c r="DF31"/>
       <c r="DG31"/>
       <c r="DH31"/>
       <c r="DI31"/>
@@ -15017,7 +14505,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18019</t>
+          <t>6a04cc5a1ef26d534baf2c08</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -15027,25 +14515,25 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>E0570</t>
+          <t>A7003</t>
         </is>
       </c>
       <c r="E32"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>RR</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32" s="1" t="n">
-        <v>25.0</v>
+        <v>3.75</v>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
@@ -15060,9 +14548,7 @@
       <c r="O32" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P32" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P32"/>
       <c r="Q32"/>
       <c r="R32"/>
       <c r="S32"/>
@@ -15081,11 +14567,7 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32"/>
-      <c r="AE32" s="3" t="inlineStr">
-        <is>
-          <t>V123456</t>
-        </is>
-      </c>
+      <c r="AE32"/>
       <c r="AF32"/>
       <c r="AG32"/>
       <c r="AH32"/>
@@ -15141,21 +14623,9 @@
       <c r="CF32"/>
       <c r="CG32"/>
       <c r="CH32"/>
-      <c r="CI32" s="3" t="inlineStr">
-        <is>
-          <t>9988776655</t>
-        </is>
-      </c>
-      <c r="CJ32" s="3" t="inlineStr">
-        <is>
-          <t>DOE</t>
-        </is>
-      </c>
-      <c r="CK32" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="CI32"/>
+      <c r="CJ32"/>
+      <c r="CK32"/>
       <c r="CL32"/>
       <c r="CM32"/>
       <c r="CN32"/>
@@ -15194,35 +14664,31 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18019</t>
+          <t>6a04cc5a1ef26d534baf2c43</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>ABC123-RI</t>
+          <t>26407789</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>A7003</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E33"/>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>NU</t>
-        </is>
-      </c>
+      <c r="F33"/>
       <c r="G33"/>
       <c r="H33"/>
       <c r="I33"/>
       <c r="J33" s="1" t="n">
-        <v>3.75</v>
+        <v>43.0</v>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
@@ -15237,17 +14703,21 @@
       <c r="O33" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P33"/>
-      <c r="Q33"/>
+      <c r="P33" s="2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>3.0</v>
+      </c>
       <c r="R33"/>
       <c r="S33"/>
       <c r="T33"/>
       <c r="U33"/>
       <c r="V33" s="4" t="n">
-        <v>38486.0</v>
+        <v>38628.0</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>38486.0</v>
+        <v>38628.0</v>
       </c>
       <c r="X33"/>
       <c r="Y33"/>
@@ -15353,7 +14823,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18054</t>
+          <t>6a04cc5a1ef26d534baf2c43</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -15363,12 +14833,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>96372</t>
         </is>
       </c>
       <c r="E34"/>
@@ -15377,7 +14847,7 @@
       <c r="H34"/>
       <c r="I34"/>
       <c r="J34" s="1" t="n">
-        <v>43.0</v>
+        <v>15.0</v>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
@@ -15395,9 +14865,7 @@
       <c r="P34" s="2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Q34" s="2" t="n">
-        <v>3.0</v>
-      </c>
+      <c r="Q34"/>
       <c r="R34"/>
       <c r="S34"/>
       <c r="T34"/>
@@ -15512,7 +14980,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18054</t>
+          <t>6a04cc5a1ef26d534baf2c43</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -15522,12 +14990,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>J3301</t>
         </is>
       </c>
       <c r="E35"/>
@@ -15536,7 +15004,7 @@
       <c r="H35"/>
       <c r="I35"/>
       <c r="J35" s="1" t="n">
-        <v>15.0</v>
+        <v>21.04</v>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
@@ -15669,22 +15137,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18054</t>
+          <t>6a04cc5a1ef26d534baf2c67</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>26407789</t>
+          <t>26463774</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>J3301</t>
+          <t>99213</t>
         </is>
       </c>
       <c r="E36"/>
@@ -15693,7 +15161,7 @@
       <c r="H36"/>
       <c r="I36"/>
       <c r="J36" s="1" t="n">
-        <v>21.04</v>
+        <v>40.0</v>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
@@ -15708,19 +15176,17 @@
       <c r="O36" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P36" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P36"/>
       <c r="Q36"/>
       <c r="R36"/>
       <c r="S36"/>
       <c r="T36"/>
       <c r="U36"/>
       <c r="V36" s="4" t="n">
-        <v>38628.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W36" s="4" t="n">
-        <v>38628.0</v>
+        <v>38993.0</v>
       </c>
       <c r="X36"/>
       <c r="Y36"/>
@@ -15826,12 +15292,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b18078</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>26463774</t>
+          <t>CLMNO12345</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -15841,7 +15307,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>99213</t>
+          <t>S9500</t>
         </is>
       </c>
       <c r="E37"/>
@@ -15850,7 +15316,7 @@
       <c r="H37"/>
       <c r="I37"/>
       <c r="J37" s="1" t="n">
-        <v>40.0</v>
+        <v>1400.0</v>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
@@ -15858,10 +15324,18 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M37"/>
-      <c r="N37"/>
+        <v>7.0</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="n">
         <v>1.0</v>
       </c>
@@ -15872,10 +15346,10 @@
       <c r="T37"/>
       <c r="U37"/>
       <c r="V37" s="4" t="n">
-        <v>38993.0</v>
+        <v>38018.0</v>
       </c>
       <c r="W37" s="4" t="n">
-        <v>38993.0</v>
+        <v>38024.0</v>
       </c>
       <c r="X37"/>
       <c r="Y37"/>
@@ -15948,9 +15422,21 @@
       <c r="CN37"/>
       <c r="CO37"/>
       <c r="CP37"/>
-      <c r="CQ37"/>
-      <c r="CR37"/>
-      <c r="CS37"/>
+      <c r="CQ37" s="3" t="inlineStr">
+        <is>
+          <t>1112223338</t>
+        </is>
+      </c>
+      <c r="CR37" s="3" t="inlineStr">
+        <is>
+          <t>Welby</t>
+        </is>
+      </c>
+      <c r="CS37" s="3" t="inlineStr">
+        <is>
+          <t>Marcus</t>
+        </is>
+      </c>
       <c r="CT37"/>
       <c r="CU37"/>
       <c r="CV37"/>
@@ -15981,7 +15467,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -15991,12 +15477,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>S9500</t>
+          <t>S5001</t>
         </is>
       </c>
       <c r="E38"/>
@@ -16005,7 +15491,7 @@
       <c r="H38"/>
       <c r="I38"/>
       <c r="J38" s="1" t="n">
-        <v>1400.0</v>
+        <v>682.5</v>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
@@ -16040,7 +15526,9 @@
       <c r="W38" s="4" t="n">
         <v>38024.0</v>
       </c>
-      <c r="X38"/>
+      <c r="X38" s="4" t="n">
+        <v>38016.0</v>
+      </c>
       <c r="Y38"/>
       <c r="Z38"/>
       <c r="AA38"/>
@@ -16052,10 +15540,24 @@
       <c r="AG38"/>
       <c r="AH38"/>
       <c r="AI38"/>
-      <c r="AJ38"/>
-      <c r="AK38"/>
-      <c r="AL38"/>
-      <c r="AM38"/>
+      <c r="AJ38" s="3" t="inlineStr">
+        <is>
+          <t>00003161201</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2530001</t>
+        </is>
+      </c>
       <c r="AN38"/>
       <c r="AO38"/>
       <c r="AP38"/>
@@ -16156,7 +15658,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -16166,12 +15668,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>S5001</t>
+          <t>S5000</t>
         </is>
       </c>
       <c r="E39"/>
@@ -16180,7 +15682,7 @@
       <c r="H39"/>
       <c r="I39"/>
       <c r="J39" s="1" t="n">
-        <v>682.5</v>
+        <v>15.12</v>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
@@ -16188,7 +15690,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -16231,11 +15733,11 @@
       <c r="AI39"/>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>00003161201</t>
+          <t>63323025510</t>
         </is>
       </c>
       <c r="AK39" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
@@ -16347,7 +15849,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -16357,7 +15859,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -16371,7 +15873,7 @@
       <c r="H40"/>
       <c r="I40"/>
       <c r="J40" s="1" t="n">
-        <v>15.12</v>
+        <v>67.69</v>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
@@ -16379,7 +15881,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -16422,11 +15924,11 @@
       <c r="AI40"/>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>63323025510</t>
+          <t>00338004938</t>
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
@@ -16538,7 +16040,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -16548,7 +16050,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -16562,7 +16064,7 @@
       <c r="H41"/>
       <c r="I41"/>
       <c r="J41" s="1" t="n">
-        <v>67.69</v>
+        <v>57.12</v>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
@@ -16570,7 +16072,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -16613,11 +16115,11 @@
       <c r="AI41"/>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>00338004938</t>
+          <t>08290326810</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
@@ -16626,7 +16128,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2530001</t>
+          <t>2530002</t>
         </is>
       </c>
       <c r="AN41"/>
@@ -16729,7 +16231,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2caf</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -16739,7 +16241,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -16753,7 +16255,7 @@
       <c r="H42"/>
       <c r="I42"/>
       <c r="J42" s="1" t="n">
-        <v>57.12</v>
+        <v>10.5</v>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
@@ -16761,7 +16263,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -16804,11 +16306,11 @@
       <c r="AI42"/>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>08290326810</t>
+          <t>829080357005</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
@@ -16817,7 +16319,7 @@
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2530002</t>
+          <t>2530003</t>
         </is>
       </c>
       <c r="AN42"/>
@@ -16920,31 +16422,47 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b180c0</t>
+          <t>6a04cc5a1ef26d534baf2d6d</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CLMNO12345</t>
+          <t>36463774</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>S5000</t>
+          <t>99299</t>
         </is>
       </c>
       <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="J43" s="1" t="n">
-        <v>10.5</v>
+        <v>40.0</v>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
@@ -16952,54 +16470,104 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>OFFICE</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P43"/>
+      <c r="P43" s="2" t="n">
+        <v>2.0</v>
+      </c>
       <c r="Q43"/>
-      <c r="R43"/>
-      <c r="S43"/>
-      <c r="T43"/>
-      <c r="U43"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V43" s="4" t="n">
-        <v>38018.0</v>
+        <v>38425.0</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>38024.0</v>
+        <v>38436.0</v>
       </c>
       <c r="X43" s="4" t="n">
-        <v>38016.0</v>
-      </c>
-      <c r="Y43"/>
-      <c r="Z43"/>
-      <c r="AA43"/>
-      <c r="AB43"/>
+        <v>38360.0</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="Z43" s="4" t="n">
+        <v>38360.0</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>38364.0</v>
+      </c>
+      <c r="AB43" s="4" t="n">
+        <v>38360.0</v>
+      </c>
       <c r="AC43"/>
-      <c r="AD43"/>
-      <c r="AE43"/>
-      <c r="AF43"/>
-      <c r="AG43"/>
-      <c r="AH43"/>
-      <c r="AI43"/>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>PriorAuthorization</t>
+        </is>
+      </c>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>ReferralNumber</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>Repriced</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>AdjRepriced</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr">
+        <is>
+          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
+        </is>
+      </c>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
+        </is>
+      </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>829080357005</t>
+          <t>00002143481</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>7.0</v>
+        <v>1.01</v>
       </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
@@ -17008,30 +16576,78 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2530003</t>
-        </is>
-      </c>
-      <c r="AN43"/>
-      <c r="AO43"/>
-      <c r="AP43"/>
-      <c r="AQ43"/>
-      <c r="AR43"/>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>OZ</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>BM</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>Line123</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="AS43"/>
       <c r="AT43"/>
       <c r="AU43"/>
       <c r="AV43"/>
-      <c r="AW43"/>
-      <c r="AX43"/>
-      <c r="AY43"/>
-      <c r="AZ43"/>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>1234567804</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>DOE LINE</t>
+        </is>
+      </c>
+      <c r="AY43" s="3" t="inlineStr">
+        <is>
+          <t>JANE</t>
+        </is>
+      </c>
+      <c r="AZ43" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="BA43"/>
       <c r="BB43"/>
       <c r="BC43"/>
       <c r="BD43"/>
       <c r="BE43"/>
-      <c r="BF43"/>
-      <c r="BG43"/>
-      <c r="BH43"/>
+      <c r="BF43" s="3" t="inlineStr">
+        <is>
+          <t>1234567809</t>
+        </is>
+      </c>
+      <c r="BG43" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="BH43" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="BI43"/>
       <c r="BJ43"/>
       <c r="BK43"/>
@@ -17050,12 +16666,36 @@
       <c r="BX43"/>
       <c r="BY43"/>
       <c r="BZ43"/>
-      <c r="CA43"/>
-      <c r="CB43"/>
-      <c r="CC43"/>
-      <c r="CD43"/>
-      <c r="CE43"/>
-      <c r="CF43"/>
+      <c r="CA43" s="3" t="inlineStr">
+        <is>
+          <t>SupProv</t>
+        </is>
+      </c>
+      <c r="CB43" s="3" t="inlineStr">
+        <is>
+          <t>Sup</t>
+        </is>
+      </c>
+      <c r="CC43" s="3" t="inlineStr">
+        <is>
+          <t>JONE</t>
+        </is>
+      </c>
+      <c r="CD43" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CE43" s="3" t="inlineStr">
+        <is>
+          <t>PROVIDER_COMMERCIAL_NUMBER</t>
+        </is>
+      </c>
+      <c r="CF43" s="3" t="inlineStr">
+        <is>
+          <t>12345</t>
+        </is>
+      </c>
       <c r="CG43"/>
       <c r="CH43"/>
       <c r="CI43"/>
@@ -17066,21 +16706,9 @@
       <c r="CN43"/>
       <c r="CO43"/>
       <c r="CP43"/>
-      <c r="CQ43" s="3" t="inlineStr">
-        <is>
-          <t>1112223338</t>
-        </is>
-      </c>
-      <c r="CR43" s="3" t="inlineStr">
-        <is>
-          <t>Welby</t>
-        </is>
-      </c>
-      <c r="CS43" s="3" t="inlineStr">
-        <is>
-          <t>Marcus</t>
-        </is>
-      </c>
+      <c r="CQ43"/>
+      <c r="CR43"/>
+      <c r="CS43"/>
       <c r="CT43"/>
       <c r="CU43"/>
       <c r="CV43"/>
@@ -17111,7 +16739,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b1817e</t>
+          <t>6a04cc5a1ef26d534baf2d6d</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -17121,37 +16749,21 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>99299</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="E44"/>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
       <c r="J44" s="1" t="n">
-        <v>40.0</v>
+        <v>15.0</v>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
@@ -17161,182 +16773,60 @@
       <c r="L44" t="n">
         <v>1.0</v>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>OFFICE</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="M44"/>
+      <c r="N44"/>
       <c r="O44" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="P44" s="2" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="P44"/>
       <c r="Q44"/>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+      <c r="U44"/>
       <c r="V44" s="4" t="n">
-        <v>38425.0</v>
+        <v>38993.0</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>38436.0</v>
-      </c>
-      <c r="X44" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="Y44" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="Z44" s="4" t="n">
-        <v>38360.0</v>
-      </c>
-      <c r="AA44" s="4" t="n">
-        <v>38364.0</v>
-      </c>
-      <c r="AB44" s="4" t="n">
-        <v>38360.0</v>
-      </c>
+        <v>38993.0</v>
+      </c>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+      <c r="AA44"/>
+      <c r="AB44"/>
       <c r="AC44"/>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>PriorAuthorization</t>
-        </is>
-      </c>
-      <c r="AE44" s="3" t="inlineStr">
-        <is>
-          <t>ReferralNumber</t>
-        </is>
-      </c>
-      <c r="AF44" s="3" t="inlineStr">
-        <is>
-          <t>Repriced</t>
-        </is>
-      </c>
-      <c r="AG44" s="3" t="inlineStr">
-        <is>
-          <t>AdjRepriced</t>
-        </is>
-      </c>
-      <c r="AH44" s="3" t="inlineStr">
-        <is>
-          <t>PATIENT GOAL TO BE OFF OXYGEN BY END OF MONTH</t>
-        </is>
-      </c>
-      <c r="AI44" s="3" t="inlineStr">
-        <is>
-          <t>STATE REGULATION 123 WAS APPLIED DURING THE PRICING OF THIS PROF CLAIM</t>
-        </is>
-      </c>
-      <c r="AJ44" s="3" t="inlineStr">
-        <is>
-          <t>00002143481</t>
-        </is>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AL44" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>OZ</t>
-        </is>
-      </c>
-      <c r="AO44" s="3" t="inlineStr">
-        <is>
-          <t>BM</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>Line123</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
+      <c r="AD44"/>
+      <c r="AE44"/>
+      <c r="AF44"/>
+      <c r="AG44"/>
+      <c r="AH44"/>
+      <c r="AI44"/>
+      <c r="AJ44"/>
+      <c r="AK44"/>
+      <c r="AL44"/>
+      <c r="AM44"/>
+      <c r="AN44"/>
+      <c r="AO44"/>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+      <c r="AR44"/>
       <c r="AS44"/>
       <c r="AT44"/>
       <c r="AU44"/>
       <c r="AV44"/>
-      <c r="AW44" s="3" t="inlineStr">
-        <is>
-          <t>1234567804</t>
-        </is>
-      </c>
-      <c r="AX44" s="3" t="inlineStr">
-        <is>
-          <t>DOE LINE</t>
-        </is>
-      </c>
-      <c r="AY44" s="3" t="inlineStr">
-        <is>
-          <t>JANE</t>
-        </is>
-      </c>
-      <c r="AZ44" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="AW44"/>
+      <c r="AX44"/>
+      <c r="AY44"/>
+      <c r="AZ44"/>
       <c r="BA44"/>
       <c r="BB44"/>
       <c r="BC44"/>
       <c r="BD44"/>
       <c r="BE44"/>
-      <c r="BF44" s="3" t="inlineStr">
-        <is>
-          <t>1234567809</t>
-        </is>
-      </c>
-      <c r="BG44" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="BH44" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="BF44"/>
+      <c r="BG44"/>
+      <c r="BH44"/>
       <c r="BI44"/>
       <c r="BJ44"/>
       <c r="BK44"/>
@@ -17355,36 +16845,12 @@
       <c r="BX44"/>
       <c r="BY44"/>
       <c r="BZ44"/>
-      <c r="CA44" s="3" t="inlineStr">
-        <is>
-          <t>SupProv</t>
-        </is>
-      </c>
-      <c r="CB44" s="3" t="inlineStr">
-        <is>
-          <t>Sup</t>
-        </is>
-      </c>
-      <c r="CC44" s="3" t="inlineStr">
-        <is>
-          <t>JONE</t>
-        </is>
-      </c>
-      <c r="CD44" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CE44" s="3" t="inlineStr">
-        <is>
-          <t>PROVIDER_COMMERCIAL_NUMBER</t>
-        </is>
-      </c>
-      <c r="CF44" s="3" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
+      <c r="CA44"/>
+      <c r="CB44"/>
+      <c r="CC44"/>
+      <c r="CD44"/>
+      <c r="CE44"/>
+      <c r="CF44"/>
       <c r="CG44"/>
       <c r="CH44"/>
       <c r="CI44"/>
@@ -17428,7 +16894,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b1817e</t>
+          <t>6a04cc5a1ef26d534baf2d6d</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -17438,12 +16904,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>87099</t>
+          <t>99214</t>
         </is>
       </c>
       <c r="E45"/>
@@ -17452,7 +16918,7 @@
       <c r="H45"/>
       <c r="I45"/>
       <c r="J45" s="1" t="n">
-        <v>15.0</v>
+        <v>35.0</v>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
@@ -17465,7 +16931,7 @@
       <c r="M45"/>
       <c r="N45"/>
       <c r="O45" s="2" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="P45"/>
       <c r="Q45"/>
@@ -17583,7 +17049,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6a04cb3a618f76c4f7b1817e</t>
+          <t>6a04cc5a1ef26d534baf2d6d</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -17593,12 +17059,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>99214</t>
+          <t>86663</t>
         </is>
       </c>
       <c r="E46"/>
@@ -17607,7 +17073,7 @@
       <c r="H46"/>
       <c r="I46"/>
       <c r="J46" s="1" t="n">
-        <v>35.0</v>
+        <v>10.0</v>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
@@ -17629,10 +17095,10 @@
       <c r="T46"/>
       <c r="U46"/>
       <c r="V46" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>38993.0</v>
+        <v>39000.0</v>
       </c>
       <c r="X46"/>
       <c r="Y46"/>
@@ -17646,9 +17112,19 @@
       <c r="AG46"/>
       <c r="AH46"/>
       <c r="AI46"/>
-      <c r="AJ46"/>
-      <c r="AK46"/>
-      <c r="AL46"/>
+      <c r="AJ46" s="3" t="inlineStr">
+        <is>
+          <t>01234567891</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
       <c r="AM46"/>
       <c r="AN46"/>
       <c r="AO46"/>
@@ -17735,171 +17211,6 @@
       <c r="DR46"/>
       <c r="DS46"/>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>6a04cb3a618f76c4f7b1817e</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>36463774</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>86663</t>
-        </is>
-      </c>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47"/>
-      <c r="J47" s="1" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47" s="2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="P47"/>
-      <c r="Q47"/>
-      <c r="R47"/>
-      <c r="S47"/>
-      <c r="T47"/>
-      <c r="U47"/>
-      <c r="V47" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="W47" s="4" t="n">
-        <v>39000.0</v>
-      </c>
-      <c r="X47"/>
-      <c r="Y47"/>
-      <c r="Z47"/>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47"/>
-      <c r="AD47"/>
-      <c r="AE47"/>
-      <c r="AF47"/>
-      <c r="AG47"/>
-      <c r="AH47"/>
-      <c r="AI47"/>
-      <c r="AJ47" s="3" t="inlineStr">
-        <is>
-          <t>01234567891</t>
-        </is>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AL47" s="3" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="AM47"/>
-      <c r="AN47"/>
-      <c r="AO47"/>
-      <c r="AP47"/>
-      <c r="AQ47"/>
-      <c r="AR47"/>
-      <c r="AS47"/>
-      <c r="AT47"/>
-      <c r="AU47"/>
-      <c r="AV47"/>
-      <c r="AW47"/>
-      <c r="AX47"/>
-      <c r="AY47"/>
-      <c r="AZ47"/>
-      <c r="BA47"/>
-      <c r="BB47"/>
-      <c r="BC47"/>
-      <c r="BD47"/>
-      <c r="BE47"/>
-      <c r="BF47"/>
-      <c r="BG47"/>
-      <c r="BH47"/>
-      <c r="BI47"/>
-      <c r="BJ47"/>
-      <c r="BK47"/>
-      <c r="BL47"/>
-      <c r="BM47"/>
-      <c r="BN47"/>
-      <c r="BO47"/>
-      <c r="BP47"/>
-      <c r="BQ47"/>
-      <c r="BR47"/>
-      <c r="BS47"/>
-      <c r="BT47"/>
-      <c r="BU47"/>
-      <c r="BV47"/>
-      <c r="BW47"/>
-      <c r="BX47"/>
-      <c r="BY47"/>
-      <c r="BZ47"/>
-      <c r="CA47"/>
-      <c r="CB47"/>
-      <c r="CC47"/>
-      <c r="CD47"/>
-      <c r="CE47"/>
-      <c r="CF47"/>
-      <c r="CG47"/>
-      <c r="CH47"/>
-      <c r="CI47"/>
-      <c r="CJ47"/>
-      <c r="CK47"/>
-      <c r="CL47"/>
-      <c r="CM47"/>
-      <c r="CN47"/>
-      <c r="CO47"/>
-      <c r="CP47"/>
-      <c r="CQ47"/>
-      <c r="CR47"/>
-      <c r="CS47"/>
-      <c r="CT47"/>
-      <c r="CU47"/>
-      <c r="CV47"/>
-      <c r="CW47"/>
-      <c r="CX47"/>
-      <c r="CY47"/>
-      <c r="CZ47"/>
-      <c r="DA47"/>
-      <c r="DB47"/>
-      <c r="DC47"/>
-      <c r="DD47"/>
-      <c r="DE47"/>
-      <c r="DF47"/>
-      <c r="DG47"/>
-      <c r="DH47"/>
-      <c r="DI47"/>
-      <c r="DJ47"/>
-      <c r="DK47"/>
-      <c r="DL47"/>
-      <c r="DM47"/>
-      <c r="DN47"/>
-      <c r="DO47"/>
-      <c r="DP47"/>
-      <c r="DQ47"/>
-      <c r="DR47"/>
-      <c r="DS47"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf29f1</t>
+          <t>6a0614ddf8d6a2fc7434784f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a22</t>
+          <t>6a0614ddf8d6a2fc74347880</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a4c</t>
+          <t>6a0614ddf8d6a2fc743478aa</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a95</t>
+          <t>6a0614ddf8d6a2fc743478f3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2ac4</t>
+          <t>6a0614ddf8d6a2fc74347922</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3610,7 +3610,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3b</t>
+          <t>6a0614ddf8d6a2fc74347999</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3c</t>
+          <t>6a0614ddf8d6a2fc7434799a</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4486,7 +4486,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3d</t>
+          <t>6a0614ddf8d6a2fc7434799b</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4940,7 +4940,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b70</t>
+          <t>6a0614ddf8d6a2fc743479ce</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b9d</t>
+          <t>6a0614ddf8d6a2fc743479fb</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5834,7 +5834,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2bd8</t>
+          <t>6a0614ddf8d6a2fc74347a36</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c08</t>
+          <t>6a0614ddf8d6a2fc74347a66</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6732,7 +6732,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c43</t>
+          <t>6a0614ddf8d6a2fc74347aa1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7296,7 +7296,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c67</t>
+          <t>6a0614ddf8d6a2fc74347ac5</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7712,7 +7712,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -8134,7 +8134,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2d6d</t>
+          <t>6a0614ddf8d6a2fc74347bcb</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf29f1</t>
+          <t>6a0614ddf8d6a2fc7434784f</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf29f1</t>
+          <t>6a0614ddf8d6a2fc7434784f</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf29f1</t>
+          <t>6a0614ddf8d6a2fc7434784f</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -10158,7 +10158,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf29f1</t>
+          <t>6a0614ddf8d6a2fc7434784f</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -10325,7 +10325,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a22</t>
+          <t>6a0614ddf8d6a2fc74347880</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10480,7 +10480,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a22</t>
+          <t>6a0614ddf8d6a2fc74347880</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -10635,7 +10635,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a22</t>
+          <t>6a0614ddf8d6a2fc74347880</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a22</t>
+          <t>6a0614ddf8d6a2fc74347880</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -10945,7 +10945,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a4c</t>
+          <t>6a0614ddf8d6a2fc743478aa</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11100,7 +11100,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a95</t>
+          <t>6a0614ddf8d6a2fc743478f3</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a95</t>
+          <t>6a0614ddf8d6a2fc743478f3</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2a95</t>
+          <t>6a0614ddf8d6a2fc743478f3</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -11573,7 +11573,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2ac4</t>
+          <t>6a0614ddf8d6a2fc74347922</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11728,7 +11728,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2ac4</t>
+          <t>6a0614ddf8d6a2fc74347922</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11883,7 +11883,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2ac4</t>
+          <t>6a0614ddf8d6a2fc74347922</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3b</t>
+          <t>6a0614ddf8d6a2fc74347999</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12193,7 +12193,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3b</t>
+          <t>6a0614ddf8d6a2fc74347999</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3b</t>
+          <t>6a0614ddf8d6a2fc74347999</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -12503,7 +12503,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3b</t>
+          <t>6a0614ddf8d6a2fc74347999</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12658,7 +12658,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3c</t>
+          <t>6a0614ddf8d6a2fc7434799a</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -12813,7 +12813,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3d</t>
+          <t>6a0614ddf8d6a2fc7434799b</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -12980,7 +12980,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b3d</t>
+          <t>6a0614ddf8d6a2fc7434799b</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b70</t>
+          <t>6a0614ddf8d6a2fc743479ce</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13302,7 +13302,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b70</t>
+          <t>6a0614ddf8d6a2fc743479ce</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -13457,7 +13457,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b70</t>
+          <t>6a0614ddf8d6a2fc743479ce</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -13612,7 +13612,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b70</t>
+          <t>6a0614ddf8d6a2fc743479ce</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -13767,7 +13767,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b9d</t>
+          <t>6a0614ddf8d6a2fc743479fb</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2b9d</t>
+          <t>6a0614ddf8d6a2fc743479fb</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -14101,7 +14101,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2bd8</t>
+          <t>6a0614ddf8d6a2fc74347a36</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -14328,7 +14328,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c08</t>
+          <t>6a0614ddf8d6a2fc74347a66</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -14505,7 +14505,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c08</t>
+          <t>6a0614ddf8d6a2fc74347a66</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -14664,7 +14664,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c43</t>
+          <t>6a0614ddf8d6a2fc74347aa1</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -14823,7 +14823,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c43</t>
+          <t>6a0614ddf8d6a2fc74347aa1</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14980,7 +14980,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c43</t>
+          <t>6a0614ddf8d6a2fc74347aa1</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -15137,7 +15137,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2c67</t>
+          <t>6a0614ddf8d6a2fc74347ac5</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -15292,7 +15292,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -15467,7 +15467,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -15658,7 +15658,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -15849,7 +15849,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -16040,7 +16040,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -16231,7 +16231,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2caf</t>
+          <t>6a0614ddf8d6a2fc74347b0d</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -16422,7 +16422,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2d6d</t>
+          <t>6a0614ddf8d6a2fc74347bcb</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -16739,7 +16739,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2d6d</t>
+          <t>6a0614ddf8d6a2fc74347bcb</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -16894,7 +16894,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2d6d</t>
+          <t>6a0614ddf8d6a2fc74347bcb</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -17049,7 +17049,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6a04cc5a1ef26d534baf2d6d</t>
+          <t>6a0614ddf8d6a2fc74347bcb</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">

--- a/converted_files/837/837P-all-files.xlsx
+++ b/converted_files/837/837P-all-files.xlsx
@@ -1228,7 +1228,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434784f</t>
+          <t>6a32cb6397613a0e49907eb3</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347880</t>
+          <t>6a32cb6397613a0e49907ee5</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478aa</t>
+          <t>6a32cb6397613a0e49907f12</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2393,9 +2393,21 @@
       </c>
       <c r="BR4"/>
       <c r="BS4"/>
-      <c r="BT4"/>
-      <c r="BU4"/>
-      <c r="BV4"/>
+      <c r="BT4" s="3" t="inlineStr">
+        <is>
+          <t>BALTIMORE</t>
+        </is>
+      </c>
+      <c r="BU4" s="3" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="BV4" s="3" t="inlineStr">
+        <is>
+          <t>21236</t>
+        </is>
+      </c>
       <c r="BW4"/>
       <c r="BX4"/>
       <c r="BY4"/>
@@ -2572,7 +2584,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478f3</t>
+          <t>6a32cb6397613a0e49907f5b</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3170,7 +3182,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347922</t>
+          <t>6a32cb6397613a0e49907f8b</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3610,7 +3622,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347999</t>
+          <t>6a32cb6397613a0e49908002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4054,7 +4066,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434799a</t>
+          <t>6a32cb6397613a0e49908003</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -4486,7 +4498,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434799b</t>
+          <t>6a32cb6397613a0e49908004</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -4940,7 +4952,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479ce</t>
+          <t>6a32cb6397613a0e49908037</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -5380,7 +5392,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479fb</t>
+          <t>6a32cb6397613a0e49908067</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -5424,7 +5436,7 @@
         </is>
       </c>
       <c r="J11" s="1" t="n">
-        <v>827.0</v>
+        <v>1654.0</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -5609,9 +5621,21 @@
       </c>
       <c r="BR11"/>
       <c r="BS11"/>
-      <c r="BT11"/>
-      <c r="BU11"/>
-      <c r="BV11"/>
+      <c r="BT11" s="3" t="inlineStr">
+        <is>
+          <t>NASHVILLE</t>
+        </is>
+      </c>
+      <c r="BU11" s="3" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="BV11" s="3" t="inlineStr">
+        <is>
+          <t>37232</t>
+        </is>
+      </c>
       <c r="BW11"/>
       <c r="BX11"/>
       <c r="BY11"/>
@@ -5834,7 +5858,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347a36</t>
+          <t>6a32cb6397613a0e499080a5</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6073,9 +6097,21 @@
       </c>
       <c r="BR12"/>
       <c r="BS12"/>
-      <c r="BT12"/>
-      <c r="BU12"/>
-      <c r="BV12"/>
+      <c r="BT12" s="3" t="inlineStr">
+        <is>
+          <t>LAFAYETTE</t>
+        </is>
+      </c>
+      <c r="BU12" s="3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="BV12" s="3" t="inlineStr">
+        <is>
+          <t>47904</t>
+        </is>
+      </c>
       <c r="BW12"/>
       <c r="BX12"/>
       <c r="BY12"/>
@@ -6250,7 +6286,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347a66</t>
+          <t>6a32cb6397613a0e499080d5</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6732,7 +6768,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347aa1</t>
+          <t>6a32cb6397613a0e49908110</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7296,7 +7332,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347ac5</t>
+          <t>6a32cb6397613a0e49908136</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7712,7 +7748,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -8134,7 +8170,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347bcb</t>
+          <t>6a32cb6397613a0e49908241</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -9621,7 +9657,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434784f</t>
+          <t>6a32cb6397613a0e49907eb3</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -9824,7 +9860,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434784f</t>
+          <t>6a32cb6397613a0e49907eb3</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -9991,7 +10027,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434784f</t>
+          <t>6a32cb6397613a0e49907eb3</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -10158,7 +10194,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434784f</t>
+          <t>6a32cb6397613a0e49907eb3</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -10325,7 +10361,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347880</t>
+          <t>6a32cb6397613a0e49907ee5</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -10480,7 +10516,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347880</t>
+          <t>6a32cb6397613a0e49907ee5</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -10635,7 +10671,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347880</t>
+          <t>6a32cb6397613a0e49907ee5</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -10790,7 +10826,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347880</t>
+          <t>6a32cb6397613a0e49907ee5</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -10945,7 +10981,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478aa</t>
+          <t>6a32cb6397613a0e49907f12</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -11100,7 +11136,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478f3</t>
+          <t>6a32cb6397613a0e49907f5b</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -11259,7 +11295,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478f3</t>
+          <t>6a32cb6397613a0e49907f5b</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -11416,7 +11452,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743478f3</t>
+          <t>6a32cb6397613a0e49907f5b</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -11573,7 +11609,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347922</t>
+          <t>6a32cb6397613a0e49907f8b</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -11728,7 +11764,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347922</t>
+          <t>6a32cb6397613a0e49907f8b</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -11883,7 +11919,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347922</t>
+          <t>6a32cb6397613a0e49907f8b</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -12038,7 +12074,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347999</t>
+          <t>6a32cb6397613a0e49908002</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -12193,7 +12229,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347999</t>
+          <t>6a32cb6397613a0e49908002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -12348,7 +12384,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347999</t>
+          <t>6a32cb6397613a0e49908002</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -12503,7 +12539,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347999</t>
+          <t>6a32cb6397613a0e49908002</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -12658,7 +12694,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434799a</t>
+          <t>6a32cb6397613a0e49908003</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -12813,7 +12849,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434799b</t>
+          <t>6a32cb6397613a0e49908004</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -12980,7 +13016,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc7434799b</t>
+          <t>6a32cb6397613a0e49908004</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -13147,7 +13183,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479ce</t>
+          <t>6a32cb6397613a0e49908037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13302,7 +13338,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479ce</t>
+          <t>6a32cb6397613a0e49908037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -13457,7 +13493,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479ce</t>
+          <t>6a32cb6397613a0e49908037</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -13612,7 +13648,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479ce</t>
+          <t>6a32cb6397613a0e49908037</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -13767,7 +13803,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479fb</t>
+          <t>6a32cb6397613a0e49908067</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -13934,7 +13970,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc743479fb</t>
+          <t>6a32cb6397613a0e49908067</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -14101,7 +14137,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347a36</t>
+          <t>6a32cb6397613a0e499080a5</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -14328,7 +14364,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347a66</t>
+          <t>6a32cb6397613a0e499080d5</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -14505,7 +14541,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347a66</t>
+          <t>6a32cb6397613a0e499080d5</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -14664,7 +14700,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347aa1</t>
+          <t>6a32cb6397613a0e49908110</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -14823,7 +14859,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347aa1</t>
+          <t>6a32cb6397613a0e49908110</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -14980,7 +15016,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347aa1</t>
+          <t>6a32cb6397613a0e49908110</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -15137,7 +15173,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347ac5</t>
+          <t>6a32cb6397613a0e49908136</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -15292,7 +15328,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -15467,7 +15503,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -15658,7 +15694,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -15849,7 +15885,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -16040,7 +16076,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -16231,7 +16267,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347b0d</t>
+          <t>6a32cb6397613a0e4990817e</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -16422,7 +16458,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347bcb</t>
+          <t>6a32cb6397613a0e49908241</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -16739,7 +16775,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347bcb</t>
+          <t>6a32cb6397613a0e49908241</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -16894,7 +16930,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347bcb</t>
+          <t>6a32cb6397613a0e49908241</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -17049,7 +17085,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6a0614ddf8d6a2fc74347bcb</t>
+          <t>6a32cb6397613a0e49908241</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
